--- a/jogos_2026-03-03.xlsx
+++ b/jogos_2026-03-03.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI10"/>
+  <dimension ref="A1:AI59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -618,12 +618,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -728,7 +728,7 @@
         <v>0</v>
       </c>
       <c r="AI2" s="3" t="n">
-        <v>46084.60416666666</v>
+        <v>46084.35416666666</v>
       </c>
     </row>
     <row r="3">
@@ -737,12 +737,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -847,7 +847,7 @@
         <v>0</v>
       </c>
       <c r="AI3" s="3" t="n">
-        <v>46084.60416666666</v>
+        <v>46084.375</v>
       </c>
     </row>
     <row r="4">
@@ -856,12 +856,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -966,7 +966,7 @@
         <v>0</v>
       </c>
       <c r="AI4" s="3" t="n">
-        <v>46084.60416666666</v>
+        <v>46084.375</v>
       </c>
     </row>
     <row r="5">
@@ -975,12 +975,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1085,7 +1085,7 @@
         <v>0</v>
       </c>
       <c r="AI5" s="3" t="n">
-        <v>46084.6875</v>
+        <v>46084.4375</v>
       </c>
     </row>
     <row r="6">
@@ -1094,12 +1094,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,76 +1135,76 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>6.95</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
-        <v>46084.69791666666</v>
+        <v>46084.4375</v>
       </c>
     </row>
     <row r="7">
@@ -1213,12 +1213,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,76 +1254,76 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2</v>
+        <v>1.81</v>
       </c>
       <c r="M7" t="n">
-        <v>3.25</v>
+        <v>3.04</v>
       </c>
       <c r="N7" t="n">
-        <v>3.5</v>
+        <v>4.55</v>
       </c>
       <c r="O7" t="n">
         <v>2.62</v>
       </c>
       <c r="P7" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.26</v>
+        <v>5.78</v>
       </c>
       <c r="R7" t="n">
-        <v>1.41</v>
+        <v>1.6</v>
       </c>
       <c r="S7" t="n">
-        <v>2.87</v>
+        <v>2.25</v>
       </c>
       <c r="T7" t="n">
-        <v>2.91</v>
+        <v>3.78</v>
       </c>
       <c r="U7" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="V7" t="n">
-        <v>7.1</v>
+        <v>11</v>
       </c>
       <c r="W7" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="X7" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.34</v>
+        <v>1.59</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.92</v>
+        <v>2.25</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.07</v>
+        <v>2.62</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.72</v>
+        <v>1.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.67</v>
+        <v>5.3</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.23</v>
+        <v>1.09</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.81</v>
+        <v>2.31</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.96</v>
+        <v>1.52</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.62</v>
+        <v>1.77</v>
       </c>
       <c r="AI7" s="3" t="n">
-        <v>46084.69791666666</v>
+        <v>46084.45833333334</v>
       </c>
     </row>
     <row r="8">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1369,80 +1369,80 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
-        <v>46084.69791666666</v>
+        <v>46084.45833333334</v>
       </c>
     </row>
     <row r="9">
@@ -1451,27 +1451,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1561,7 +1561,7 @@
         <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
-        <v>46084.875</v>
+        <v>46084.5</v>
       </c>
     </row>
     <row r="10">
@@ -1570,116 +1570,5947 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ethiopia Ethiopia Premier League</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Welwalo Adigrat Uni</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Shire Endaselassie</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" s="3" t="n">
+        <v>46084.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Bulgaria First League</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Botev Plovdiv</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Septemvri Sofia</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" s="3" t="n">
+        <v>46084.5625</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Italy Serie C Group A</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Pergolettese</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Pro Vercelli</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" s="3" t="n">
+        <v>46084.58333333334</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Italy Serie C Group A</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Lumezzane</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Arzignano Valchiampo</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="3" t="n">
+        <v>46084.58333333334</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Italy Serie C Group A</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Ospitaletto</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Pro Patria</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="3" t="n">
+        <v>46084.58333333334</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Italy Serie C Group A</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Alcione</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Giana Erminio</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" s="3" t="n">
+        <v>46084.58333333334</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>South Africa Premier Soccer League</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>TS Galaxy</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Orbit College</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" s="3" t="n">
+        <v>46084.60416666666</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>South Africa Premier Soccer League</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Siwelele</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Stellenbosch</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" s="3" t="n">
+        <v>46084.60416666666</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>South Africa Premier Soccer League</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Richards Bay</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Kaizer Chiefs</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI18" s="3" t="n">
+        <v>46084.60416666666</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Italy Serie B</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Calcio Padova</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Spezia</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI19" s="3" t="n">
+        <v>46084.625</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Germany 3. Liga</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Osnabrück</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Viktoria Köln</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI20" s="3" t="n">
+        <v>46084.625</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Germany 3. Liga</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Ulm</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Hoffenheim II</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI21" s="3" t="n">
+        <v>46084.625</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Germany 3. Liga</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Verl</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Jahn Regensburg</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI22" s="3" t="n">
+        <v>46084.625</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Germany 3. Liga</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Stuttgart II</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Energie Cottbus</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI23" s="3" t="n">
+        <v>46084.625</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Germany 3. Liga</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>1860 München</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Erzgebirge Aue</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI24" s="3" t="n">
+        <v>46084.625</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Jordan Jordanian Pro League</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Al Buqa'a</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Al Wihdat</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI25" s="3" t="n">
+        <v>46084.65625</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Jordan Jordanian Pro League</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Al Ramtha</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Al Salt</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI26" s="3" t="n">
+        <v>46084.65625</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Italy Serie B</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Cesena</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Monza</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI27" s="3" t="n">
+        <v>46084.66666666666</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Italy Serie B</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Reggiana</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Südtirol</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI28" s="3" t="n">
+        <v>46084.66666666666</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Italy Serie B</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Venezia</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Avellino</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI29" s="3" t="n">
+        <v>46084.66666666666</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Italy Serie B</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Virtus Entella</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Modena</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI30" s="3" t="n">
+        <v>46084.66666666666</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Netherlands Eerste Divisie</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Almere City</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="M31" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N31" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="O31" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="V31" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI31" s="3" t="n">
+        <v>46084.66666666666</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>England Premier League</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Leeds United</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Sunderland</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="M32" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="N32" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI32" s="3" t="n">
+        <v>46084.6875</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>England Premier League</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>AFC Bournemouth</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Brentford</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="M33" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N33" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI33" s="3" t="n">
+        <v>46084.6875</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>England Premier League</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Everton</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Burnley</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="M34" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="N34" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI34" s="3" t="n">
+        <v>46084.6875</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Italy Serie C Group A</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>AlbinoLeffe</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Union Brescia</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI35" s="3" t="n">
+        <v>46084.6875</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Italy Serie C Group A</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Lecco</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Renate</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI36" s="3" t="n">
+        <v>46084.6875</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Winterthur</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Servette</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI37" s="3" t="n">
+        <v>46084.6875</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Italy Serie C Group A</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Cittadella</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Inter II</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI38" s="3" t="n">
+        <v>46084.6875</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Italy Serie C Group A</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Triestina</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Dolomiti Bellunesi</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI39" s="3" t="n">
+        <v>46084.6875</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Italy Serie C Group A</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Vicenza</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Trento</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI40" s="3" t="n">
+        <v>46084.6875</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Italy Serie C Group A</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Virtus Verona</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Novara</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" t="n">
+        <v>0</v>
+      </c>
+      <c r="W41" t="n">
+        <v>0</v>
+      </c>
+      <c r="X41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI41" s="3" t="n">
+        <v>46084.6875</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Austria 2. Liga</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Rapid Wien II</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Austria Salzburg</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>suspended</t>
+        </is>
+      </c>
+      <c r="L42" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="M42" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N42" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="O42" t="n">
+        <v>3</v>
+      </c>
+      <c r="P42" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>3</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S42" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V42" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X42" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI42" s="3" t="n">
+        <v>46084.6875</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>England EFL League One</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Barnsley</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Wycombe Wanderers</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" t="n">
+        <v>0</v>
+      </c>
+      <c r="W43" t="n">
+        <v>0</v>
+      </c>
+      <c r="X43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI43" s="3" t="n">
+        <v>46084.69791666666</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>England EFL League One</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Rotherham United</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Mansfield Town</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>suspended</t>
+        </is>
+      </c>
+      <c r="L44" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="M44" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N44" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="O44" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="P44" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S44" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T44" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V44" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="W44" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X44" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI44" s="3" t="n">
+        <v>46084.69791666666</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>England Championship</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Ipswich Town</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Hull City</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="M45" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="N45" t="n">
+        <v>5.53</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
+      </c>
+      <c r="V45" t="n">
+        <v>0</v>
+      </c>
+      <c r="W45" t="n">
+        <v>0</v>
+      </c>
+      <c r="X45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI45" s="3" t="n">
+        <v>46084.69791666666</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Walsall</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Fleetwood Town</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>suspended</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M46" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="N46" t="n">
+        <v>4</v>
+      </c>
+      <c r="O46" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="P46" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="R46" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S46" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V46" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W46" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X46" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AI46" s="3" t="n">
+        <v>46084.69791666666</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>England EFL League One</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Exeter City</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Burton Albion</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>suspended</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="M47" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="N47" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="O47" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P47" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R47" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S47" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V47" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W47" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X47" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI47" s="3" t="n">
+        <v>46084.69791666666</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Scotland Championship</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Dunfermline Athletic</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Ross County</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>suspended</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
+        <v>2</v>
+      </c>
+      <c r="M48" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N48" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O48" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="P48" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="R48" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S48" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V48" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W48" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X48" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AI48" s="3" t="n">
+        <v>46084.69791666666</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Scotland Premiership</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Dundee United</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>St. Mirren</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L49" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="M49" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N49" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="O49" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P49" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R49" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S49" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V49" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="W49" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X49" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI49" s="3" t="n">
+        <v>46084.69791666666</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Grimsby Town</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Salford City</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>suspended</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="M50" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="N50" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
+      </c>
+      <c r="V50" t="n">
+        <v>0</v>
+      </c>
+      <c r="W50" t="n">
+        <v>0</v>
+      </c>
+      <c r="X50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI50" s="3" t="n">
+        <v>46084.69791666666</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Bromley</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Oldham Athletic</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>suspended</t>
+        </is>
+      </c>
+      <c r="L51" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="M51" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N51" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="O51" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="P51" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="R51" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S51" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V51" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="W51" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X51" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AI51" s="3" t="n">
+        <v>46084.69791666666</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Chesterfield</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Colchester United</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>suspended</t>
+        </is>
+      </c>
+      <c r="L52" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="M52" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N52" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="O52" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="P52" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="R52" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S52" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V52" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="W52" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X52" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG52" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AH52" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AI52" s="3" t="n">
+        <v>46084.69791666666</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Northern Ireland NIFL Premiership</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Glentoran</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Carrick Rangers</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L53" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="M53" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="N53" t="n">
+        <v>5</v>
+      </c>
+      <c r="O53" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="P53" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="R53" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S53" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V53" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W53" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X53" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AI53" s="3" t="n">
+        <v>46084.69791666666</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Newport County</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Tranmere Rovers</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L54" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="M54" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="N54" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="O54" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="P54" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R54" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S54" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="V54" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W54" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X54" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH54" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AI54" s="3" t="n">
+        <v>46084.69791666666</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Scotland Championship</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Arbroath</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Ayr United</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>suspended</t>
+        </is>
+      </c>
+      <c r="L55" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="M55" t="n">
+        <v>3</v>
+      </c>
+      <c r="N55" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O55" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="P55" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="R55" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S55" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V55" t="n">
+        <v>8</v>
+      </c>
+      <c r="W55" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X55" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH55" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AI55" s="3" t="n">
+        <v>46084.69791666666</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>England Premier League</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Liverpool</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L56" t="n">
+        <v>6.24</v>
+      </c>
+      <c r="M56" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="N56" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>0</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
+      </c>
+      <c r="V56" t="n">
+        <v>0</v>
+      </c>
+      <c r="W56" t="n">
+        <v>0</v>
+      </c>
+      <c r="X56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI56" s="3" t="n">
+        <v>46084.71875</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
           <t>21:00</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Italy Serie C Group B</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Rimini</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Città di Campobasso</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>canceled</t>
+        </is>
+      </c>
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>0</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
+      </c>
+      <c r="V57" t="n">
+        <v>0</v>
+      </c>
+      <c r="W57" t="n">
+        <v>0</v>
+      </c>
+      <c r="X57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI57" s="3" t="n">
+        <v>46084.875</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
         <is>
           <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>Kokand-1912</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>Pakhtakor</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="inlineStr">
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI10" s="3" t="n">
+      <c r="L58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>0</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
+      </c>
+      <c r="V58" t="n">
+        <v>0</v>
+      </c>
+      <c r="W58" t="n">
+        <v>0</v>
+      </c>
+      <c r="X58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI58" s="3" t="n">
+        <v>46084.875</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Uzbekistan Uzbekistan Super League</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Qizilqum</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Andijan</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L59" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>0</v>
+      </c>
+      <c r="R59" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>0</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
+      </c>
+      <c r="V59" t="n">
+        <v>0</v>
+      </c>
+      <c r="W59" t="n">
+        <v>0</v>
+      </c>
+      <c r="X59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI59" s="3" t="n">
         <v>46084.875</v>
       </c>
     </row>

--- a/jogos_2026-03-03.xlsx
+++ b/jogos_2026-03-03.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI59"/>
+  <dimension ref="A1:AI60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3355,12 +3355,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3392,17 +3392,17 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3465,7 +3465,7 @@
         <v>0</v>
       </c>
       <c r="AI25" s="3" t="n">
-        <v>46084.65625</v>
+        <v>46084.625</v>
       </c>
     </row>
     <row r="26">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3593,12 +3593,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3703,7 +3703,7 @@
         <v>0</v>
       </c>
       <c r="AI27" s="3" t="n">
-        <v>46084.66666666666</v>
+        <v>46084.65625</v>
       </c>
     </row>
     <row r="28">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46084.66666666666</v>
@@ -4188,12 +4188,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,76 +4229,76 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="M32" t="n">
-        <v>3.56</v>
+        <v>3.8</v>
       </c>
       <c r="N32" t="n">
-        <v>4.05</v>
+        <v>2.98</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.15</v>
+        <v>1.44</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.63</v>
+        <v>2.63</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI32" s="3" t="n">
-        <v>46084.6875</v>
+        <v>46084.66666666666</v>
       </c>
     </row>
     <row r="33">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>5.33</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4939,77 +4939,77 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46084.6875</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5415,77 +5415,77 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI42" s="3" t="n">
         <v>46084.6875</v>
@@ -5497,12 +5497,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5607,7 +5607,7 @@
         <v>0</v>
       </c>
       <c r="AI43" s="3" t="n">
-        <v>46084.69791666666</v>
+        <v>46084.6875</v>
       </c>
     </row>
     <row r="44">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5891,77 +5891,77 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AI46" s="3" t="n">
         <v>46084.69791666666</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,73 +6014,73 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="M47" t="n">
-        <v>3.38</v>
+        <v>3.26</v>
       </c>
       <c r="N47" t="n">
-        <v>3.08</v>
+        <v>4</v>
       </c>
       <c r="O47" t="n">
-        <v>2.8</v>
+        <v>2.46</v>
       </c>
       <c r="P47" t="n">
-        <v>2.19</v>
+        <v>2.09</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.5</v>
+        <v>4.25</v>
       </c>
       <c r="R47" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S47" t="n">
-        <v>2.81</v>
+        <v>2.87</v>
       </c>
       <c r="T47" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="U47" t="n">
         <v>1.36</v>
       </c>
       <c r="V47" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="W47" t="n">
         <v>1.03</v>
       </c>
       <c r="X47" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="Z47" t="n">
-        <v>3.24</v>
+        <v>3.05</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AC47" t="n">
-        <v>3.3</v>
+        <v>3.52</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AG47" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.55</v>
+        <v>1.88</v>
       </c>
       <c r="AI47" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,73 +6252,73 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.45</v>
+        <v>3.2</v>
       </c>
       <c r="M49" t="n">
-        <v>3.2</v>
+        <v>3.24</v>
       </c>
       <c r="N49" t="n">
-        <v>2.72</v>
+        <v>2.21</v>
       </c>
       <c r="O49" t="n">
-        <v>3.1</v>
+        <v>3.92</v>
       </c>
       <c r="P49" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="R49" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S49" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="U49" t="n">
         <v>1.39</v>
       </c>
-      <c r="S49" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="T49" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U49" t="n">
-        <v>1.41</v>
-      </c>
       <c r="V49" t="n">
-        <v>6.95</v>
+        <v>6.5</v>
       </c>
       <c r="W49" t="n">
         <v>1.04</v>
       </c>
       <c r="X49" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y49" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH49" t="n">
         <v>1.31</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE49" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF49" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG49" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH49" t="n">
-        <v>1.53</v>
       </c>
       <c r="AI49" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6605,7 +6605,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,73 +6728,73 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.53</v>
+        <v>2.45</v>
       </c>
       <c r="M53" t="n">
-        <v>3.95</v>
+        <v>3.2</v>
       </c>
       <c r="N53" t="n">
-        <v>5</v>
+        <v>2.72</v>
       </c>
       <c r="O53" t="n">
-        <v>2.06</v>
+        <v>3.1</v>
       </c>
       <c r="P53" t="n">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="Q53" t="n">
-        <v>5.65</v>
+        <v>3.5</v>
       </c>
       <c r="R53" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="S53" t="n">
-        <v>2.91</v>
+        <v>2.69</v>
       </c>
       <c r="T53" t="n">
-        <v>2.48</v>
+        <v>2.65</v>
       </c>
       <c r="U53" t="n">
         <v>1.41</v>
       </c>
       <c r="V53" t="n">
-        <v>6.5</v>
+        <v>6.95</v>
       </c>
       <c r="W53" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="X53" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="Z53" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.78</v>
+        <v>1.98</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.93</v>
+        <v>1.75</v>
       </c>
       <c r="AC53" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="AD53" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.84</v>
+        <v>1.73</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AG53" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AH53" t="n">
-        <v>2.31</v>
+        <v>1.53</v>
       </c>
       <c r="AI53" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,73 +6847,73 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>3.2</v>
+        <v>1.53</v>
       </c>
       <c r="M54" t="n">
-        <v>3.24</v>
+        <v>3.95</v>
       </c>
       <c r="N54" t="n">
-        <v>2.21</v>
+        <v>5</v>
       </c>
       <c r="O54" t="n">
-        <v>3.92</v>
+        <v>2.06</v>
       </c>
       <c r="P54" t="n">
-        <v>2.05</v>
+        <v>2.35</v>
       </c>
       <c r="Q54" t="n">
-        <v>2.8</v>
+        <v>5.65</v>
       </c>
       <c r="R54" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="S54" t="n">
-        <v>2.77</v>
+        <v>2.91</v>
       </c>
       <c r="T54" t="n">
-        <v>2.73</v>
+        <v>2.48</v>
       </c>
       <c r="U54" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="V54" t="n">
         <v>6.5</v>
       </c>
       <c r="W54" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="X54" t="n">
         <v>1.01</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="Z54" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AC54" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="AD54" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.7</v>
+        <v>1.84</v>
       </c>
       <c r="AF54" t="n">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="AG54" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AH54" t="n">
-        <v>1.31</v>
+        <v>2.31</v>
       </c>
       <c r="AI54" s="3" t="n">
         <v>46084.69791666666</v>
@@ -7044,12 +7044,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7081,80 +7081,80 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>6.24</v>
+        <v>2.1</v>
       </c>
       <c r="M56" t="n">
-        <v>4.72</v>
+        <v>3.38</v>
       </c>
       <c r="N56" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="O56" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P56" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R56" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S56" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V56" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W56" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X56" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG56" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AH56" t="n">
         <v>1.55</v>
       </c>
-      <c r="O56" t="n">
-        <v>0</v>
-      </c>
-      <c r="P56" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
-      <c r="R56" t="n">
-        <v>0</v>
-      </c>
-      <c r="S56" t="n">
-        <v>0</v>
-      </c>
-      <c r="T56" t="n">
-        <v>0</v>
-      </c>
-      <c r="U56" t="n">
-        <v>0</v>
-      </c>
-      <c r="V56" t="n">
-        <v>0</v>
-      </c>
-      <c r="W56" t="n">
-        <v>0</v>
-      </c>
-      <c r="X56" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AC56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH56" t="n">
-        <v>0</v>
-      </c>
       <c r="AI56" s="3" t="n">
-        <v>46084.71875</v>
+        <v>46084.69791666666</v>
       </c>
     </row>
     <row r="57">
@@ -7163,12 +7163,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7200,17 +7200,17 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>6.24</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7249,10 +7249,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -7273,7 +7273,7 @@
         <v>0</v>
       </c>
       <c r="AI57" s="3" t="n">
-        <v>46084.875</v>
+        <v>46084.71875</v>
       </c>
     </row>
     <row r="58">
@@ -7287,22 +7287,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7319,7 +7319,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L58" t="n">
@@ -7416,101 +7416,220 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
+          <t>Kokand-1912</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Pakhtakor</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L59" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>0</v>
+      </c>
+      <c r="R59" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>0</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
+      </c>
+      <c r="V59" t="n">
+        <v>0</v>
+      </c>
+      <c r="W59" t="n">
+        <v>0</v>
+      </c>
+      <c r="X59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI59" s="3" t="n">
+        <v>46084.875</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Uzbekistan Uzbekistan Super League</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
           <t>Qizilqum</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="F60" t="inlineStr">
         <is>
           <t>Andijan</t>
         </is>
       </c>
-      <c r="G59" t="n">
-        <v>0</v>
-      </c>
-      <c r="H59" t="n">
-        <v>0</v>
-      </c>
-      <c r="I59" t="n">
-        <v>0</v>
-      </c>
-      <c r="J59" t="n">
-        <v>0</v>
-      </c>
-      <c r="K59" t="inlineStr">
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L59" t="n">
-        <v>0</v>
-      </c>
-      <c r="M59" t="n">
-        <v>0</v>
-      </c>
-      <c r="N59" t="n">
-        <v>0</v>
-      </c>
-      <c r="O59" t="n">
-        <v>0</v>
-      </c>
-      <c r="P59" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
-      <c r="R59" t="n">
-        <v>0</v>
-      </c>
-      <c r="S59" t="n">
-        <v>0</v>
-      </c>
-      <c r="T59" t="n">
-        <v>0</v>
-      </c>
-      <c r="U59" t="n">
-        <v>0</v>
-      </c>
-      <c r="V59" t="n">
-        <v>0</v>
-      </c>
-      <c r="W59" t="n">
-        <v>0</v>
-      </c>
-      <c r="X59" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y59" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI59" s="3" t="n">
+      <c r="L60" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>0</v>
+      </c>
+      <c r="R60" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>0</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
+      </c>
+      <c r="V60" t="n">
+        <v>0</v>
+      </c>
+      <c r="W60" t="n">
+        <v>0</v>
+      </c>
+      <c r="X60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI60" s="3" t="n">
         <v>46084.875</v>
       </c>
     </row>

--- a/jogos_2026-03-03.xlsx
+++ b/jogos_2026-03-03.xlsx
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G42" t="n">

--- a/jogos_2026-03-03.xlsx
+++ b/jogos_2026-03-03.xlsx
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G31" t="n">

--- a/jogos_2026-03-03.xlsx
+++ b/jogos_2026-03-03.xlsx
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2678,17 +2678,17 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3392,17 +3392,17 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46084.66666666666</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46084.66666666666</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4939,77 +4939,77 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46084.6875</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5177,77 +5177,77 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.49</v>
+        <v>2.45</v>
       </c>
       <c r="M40" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="N40" t="n">
-        <v>2.86</v>
+        <v>2.43</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46084.6875</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>5.33</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,55 +5538,55 @@
         </is>
       </c>
       <c r="L43" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="M43" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N43" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" t="n">
+        <v>0</v>
+      </c>
+      <c r="W43" t="n">
+        <v>0</v>
+      </c>
+      <c r="X43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AB43" t="n">
         <v>2.05</v>
-      </c>
-      <c r="M43" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="N43" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="O43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
-      <c r="R43" t="n">
-        <v>0</v>
-      </c>
-      <c r="S43" t="n">
-        <v>0</v>
-      </c>
-      <c r="T43" t="n">
-        <v>0</v>
-      </c>
-      <c r="U43" t="n">
-        <v>0</v>
-      </c>
-      <c r="V43" t="n">
-        <v>0</v>
-      </c>
-      <c r="W43" t="n">
-        <v>0</v>
-      </c>
-      <c r="X43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>1.63</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5653,77 +5653,77 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.85</v>
+        <v>3.2</v>
       </c>
       <c r="M44" t="n">
-        <v>3.1</v>
+        <v>3.24</v>
       </c>
       <c r="N44" t="n">
-        <v>2.24</v>
+        <v>2.21</v>
       </c>
       <c r="O44" t="n">
-        <v>3.7</v>
+        <v>3.92</v>
       </c>
       <c r="P44" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="R44" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="S44" t="n">
         <v>2.77</v>
       </c>
       <c r="T44" t="n">
-        <v>3.04</v>
+        <v>2.73</v>
       </c>
       <c r="U44" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="V44" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W44" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X44" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD44" t="n">
         <v>1.33</v>
       </c>
-      <c r="V44" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="W44" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X44" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y44" t="n">
+      <c r="AE44" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AG44" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z44" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AE44" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AF44" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AG44" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AH44" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46084.69791666666</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5772,77 +5772,77 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.53</v>
+        <v>2.85</v>
       </c>
       <c r="M45" t="n">
-        <v>4.3</v>
+        <v>3.1</v>
       </c>
       <c r="N45" t="n">
-        <v>5.53</v>
+        <v>2.24</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.65</v>
+        <v>2.19</v>
       </c>
       <c r="AB45" t="n">
-        <v>2.1</v>
+        <v>1.71</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46084.69791666666</v>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5891,77 +5891,77 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH46" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI46" s="3" t="n">
         <v>46084.69791666666</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6010,77 +6010,77 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AI47" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6129,77 +6129,77 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2</v>
+        <v>1.53</v>
       </c>
       <c r="M48" t="n">
-        <v>3.25</v>
+        <v>3.95</v>
       </c>
       <c r="N48" t="n">
+        <v>5</v>
+      </c>
+      <c r="O48" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="P48" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="R48" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S48" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V48" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W48" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z48" t="n">
         <v>3.5</v>
       </c>
-      <c r="O48" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="P48" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>4.26</v>
-      </c>
-      <c r="R48" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S48" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="T48" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="U48" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V48" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W48" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X48" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>2.92</v>
-      </c>
       <c r="AA48" t="n">
-        <v>2.07</v>
+        <v>1.78</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.72</v>
+        <v>1.93</v>
       </c>
       <c r="AC48" t="n">
-        <v>3.67</v>
+        <v>3</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="AG48" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.62</v>
+        <v>2.31</v>
       </c>
       <c r="AI48" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,73 +6252,73 @@
         </is>
       </c>
       <c r="L49" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="M49" t="n">
         <v>3.2</v>
       </c>
-      <c r="M49" t="n">
-        <v>3.24</v>
-      </c>
       <c r="N49" t="n">
-        <v>2.21</v>
+        <v>2.72</v>
       </c>
       <c r="O49" t="n">
-        <v>3.92</v>
+        <v>3.1</v>
       </c>
       <c r="P49" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="R49" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S49" t="n">
-        <v>2.77</v>
+        <v>2.69</v>
       </c>
       <c r="T49" t="n">
-        <v>2.73</v>
+        <v>2.65</v>
       </c>
       <c r="U49" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="V49" t="n">
-        <v>6.5</v>
+        <v>6.95</v>
       </c>
       <c r="W49" t="n">
         <v>1.04</v>
       </c>
       <c r="X49" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="Z49" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC49" t="n">
         <v>3.2</v>
       </c>
-      <c r="AA49" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>3.3</v>
-      </c>
       <c r="AD49" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG49" t="n">
         <v>1.33</v>
       </c>
-      <c r="AE49" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AF49" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AG49" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH49" t="n">
-        <v>1.31</v>
+        <v>1.53</v>
       </c>
       <c r="AI49" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6367,77 +6367,77 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L50" t="n">
         <v>2.45</v>
       </c>
       <c r="M50" t="n">
-        <v>3.47</v>
+        <v>3.4</v>
       </c>
       <c r="N50" t="n">
-        <v>2.59</v>
+        <v>2.88</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG50" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH50" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AI50" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,37 +6490,37 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="M51" t="n">
-        <v>3.45</v>
+        <v>3.26</v>
       </c>
       <c r="N51" t="n">
-        <v>3.86</v>
+        <v>4</v>
       </c>
       <c r="O51" t="n">
-        <v>2.55</v>
+        <v>2.46</v>
       </c>
       <c r="P51" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="Q51" t="n">
         <v>4.25</v>
       </c>
       <c r="R51" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S51" t="n">
-        <v>2.69</v>
+        <v>2.87</v>
       </c>
       <c r="T51" t="n">
-        <v>2.65</v>
+        <v>2.9</v>
       </c>
       <c r="U51" t="n">
         <v>1.36</v>
       </c>
       <c r="V51" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="W51" t="n">
         <v>1.03</v>
@@ -6529,34 +6529,34 @@
         <v>1</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="Z51" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="AA51" t="n">
         <v>2</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="AC51" t="n">
-        <v>3.34</v>
+        <v>3.52</v>
       </c>
       <c r="AD51" t="n">
         <v>1.24</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.99</v>
+        <v>1.86</v>
       </c>
       <c r="AG51" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="AH51" t="n">
-        <v>1.73</v>
+        <v>1.88</v>
       </c>
       <c r="AI51" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6605,77 +6605,77 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L52" t="n">
         <v>2.45</v>
       </c>
       <c r="M52" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="N52" t="n">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="O52" t="n">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="P52" t="n">
         <v>2.05</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.67</v>
+        <v>3.42</v>
       </c>
       <c r="R52" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="S52" t="n">
-        <v>2.77</v>
+        <v>2.62</v>
       </c>
       <c r="T52" t="n">
-        <v>2.75</v>
+        <v>2.96</v>
       </c>
       <c r="U52" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="V52" t="n">
-        <v>6.75</v>
+        <v>8</v>
       </c>
       <c r="W52" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X52" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z52" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AC52" t="n">
-        <v>3.35</v>
+        <v>3.48</v>
       </c>
       <c r="AD52" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AF52" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AG52" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="AI52" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6724,77 +6724,77 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="M53" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N53" t="n">
-        <v>2.72</v>
+        <v>3.5</v>
       </c>
       <c r="O53" t="n">
-        <v>3.1</v>
+        <v>2.62</v>
       </c>
       <c r="P53" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.5</v>
+        <v>4.26</v>
       </c>
       <c r="R53" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="S53" t="n">
-        <v>2.69</v>
+        <v>2.87</v>
       </c>
       <c r="T53" t="n">
-        <v>2.65</v>
+        <v>2.91</v>
       </c>
       <c r="U53" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="V53" t="n">
-        <v>6.95</v>
+        <v>7.1</v>
       </c>
       <c r="W53" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X53" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="Z53" t="n">
-        <v>3.3</v>
+        <v>2.92</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.98</v>
+        <v>2.07</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AC53" t="n">
-        <v>3.2</v>
+        <v>3.67</v>
       </c>
       <c r="AD53" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AF53" t="n">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="AG53" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AH53" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AI53" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6843,77 +6843,77 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.53</v>
+        <v>2.45</v>
       </c>
       <c r="M54" t="n">
-        <v>3.95</v>
+        <v>3.47</v>
       </c>
       <c r="N54" t="n">
-        <v>5</v>
+        <v>2.59</v>
       </c>
       <c r="O54" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="U54" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="V54" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W54" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X54" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Z54" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD54" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG54" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AH54" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AI54" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,73 +6966,73 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.45</v>
+        <v>1.91</v>
       </c>
       <c r="M55" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="N55" t="n">
-        <v>2.7</v>
+        <v>3.86</v>
       </c>
       <c r="O55" t="n">
-        <v>2.95</v>
+        <v>2.55</v>
       </c>
       <c r="P55" t="n">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.42</v>
+        <v>4.25</v>
       </c>
       <c r="R55" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="S55" t="n">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="T55" t="n">
-        <v>2.96</v>
+        <v>2.65</v>
       </c>
       <c r="U55" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="V55" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="W55" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X55" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="Z55" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="AA55" t="n">
         <v>2</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="AC55" t="n">
-        <v>3.48</v>
+        <v>3.34</v>
       </c>
       <c r="AD55" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AF55" t="n">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="AG55" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.48</v>
+        <v>1.73</v>
       </c>
       <c r="AI55" s="3" t="n">
         <v>46084.69791666666</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7081,77 +7081,77 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L56" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="M56" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="N56" t="n">
+        <v>5.53</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>0</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
+      </c>
+      <c r="V56" t="n">
+        <v>0</v>
+      </c>
+      <c r="W56" t="n">
+        <v>0</v>
+      </c>
+      <c r="X56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB56" t="n">
         <v>2.1</v>
       </c>
-      <c r="M56" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="N56" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="O56" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="P56" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R56" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S56" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="T56" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U56" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V56" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W56" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X56" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z56" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AC56" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD56" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF56" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG56" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH56" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI56" s="3" t="n">
         <v>46084.69791666666</v>
@@ -7287,22 +7287,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7319,7 +7319,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L58" t="n">
@@ -7406,22 +7406,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L59" t="n">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G60" t="n">

--- a/jogos_2026-03-03.xlsx
+++ b/jogos_2026-03-03.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>6.13</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>

--- a/jogos_2026-03-03.xlsx
+++ b/jogos_2026-03-03.xlsx
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.81</v>
+        <v>2.5</v>
       </c>
       <c r="M7" t="n">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="N7" t="n">
-        <v>4.55</v>
+        <v>2.8</v>
       </c>
       <c r="O7" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.78</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46084.45833333334</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.5</v>
+        <v>1.81</v>
       </c>
       <c r="M8" t="n">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="N8" t="n">
-        <v>2.8</v>
+        <v>4.55</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>5.78</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46084.45833333334</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2678,17 +2678,17 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2916,17 +2916,17 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4344,77 +4344,77 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46084.6875</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>5.33</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5177,77 +5177,77 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46084.6875</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5653,77 +5653,77 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>3.2</v>
+        <v>2.85</v>
       </c>
       <c r="M44" t="n">
-        <v>3.24</v>
+        <v>3.1</v>
       </c>
       <c r="N44" t="n">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="O44" t="n">
-        <v>3.92</v>
+        <v>3.7</v>
       </c>
       <c r="P44" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="R44" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="S44" t="n">
         <v>2.77</v>
       </c>
       <c r="T44" t="n">
-        <v>2.73</v>
+        <v>3.04</v>
       </c>
       <c r="U44" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="V44" t="n">
-        <v>6.5</v>
+        <v>7.6</v>
       </c>
       <c r="W44" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X44" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z44" t="n">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.88</v>
+        <v>2.19</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.95</v>
+        <v>1.71</v>
       </c>
       <c r="AC44" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="AF44" t="n">
-        <v>2.02</v>
+        <v>1.9</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46084.69791666666</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,73 +5776,73 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.85</v>
+        <v>2.45</v>
       </c>
       <c r="M45" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="N45" t="n">
-        <v>2.24</v>
+        <v>2.7</v>
       </c>
       <c r="O45" t="n">
-        <v>3.7</v>
+        <v>2.95</v>
       </c>
       <c r="P45" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.1</v>
+        <v>3.42</v>
       </c>
       <c r="R45" t="n">
         <v>1.44</v>
       </c>
       <c r="S45" t="n">
-        <v>2.77</v>
+        <v>2.62</v>
       </c>
       <c r="T45" t="n">
-        <v>3.04</v>
+        <v>2.96</v>
       </c>
       <c r="U45" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="V45" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="W45" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X45" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z45" t="n">
-        <v>3.14</v>
+        <v>3.5</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.19</v>
+        <v>2</v>
       </c>
       <c r="AB45" t="n">
         <v>1.71</v>
       </c>
       <c r="AC45" t="n">
-        <v>3.55</v>
+        <v>3.48</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46084.69791666666</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,73 +5895,73 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="M46" t="n">
-        <v>3.38</v>
+        <v>3.25</v>
       </c>
       <c r="N46" t="n">
-        <v>3.08</v>
+        <v>3.5</v>
       </c>
       <c r="O46" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="P46" t="n">
-        <v>2.19</v>
+        <v>2</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.5</v>
+        <v>4.26</v>
       </c>
       <c r="R46" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="S46" t="n">
-        <v>2.81</v>
+        <v>2.87</v>
       </c>
       <c r="T46" t="n">
-        <v>2.75</v>
+        <v>2.91</v>
       </c>
       <c r="U46" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V46" t="n">
-        <v>6.5</v>
+        <v>7.1</v>
       </c>
       <c r="W46" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X46" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="Z46" t="n">
-        <v>3.24</v>
+        <v>2.92</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.03</v>
+        <v>2.07</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AC46" t="n">
-        <v>3.3</v>
+        <v>3.67</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AI46" s="3" t="n">
         <v>46084.69791666666</v>
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6010,77 +6010,77 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI47" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6129,77 +6129,77 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.53</v>
+        <v>2.45</v>
       </c>
       <c r="M48" t="n">
-        <v>3.95</v>
+        <v>3.47</v>
       </c>
       <c r="N48" t="n">
-        <v>5</v>
+        <v>2.59</v>
       </c>
       <c r="O48" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X48" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG48" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AH48" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AI48" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6248,29 +6248,29 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.45</v>
+        <v>1.91</v>
       </c>
       <c r="M49" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="N49" t="n">
-        <v>2.72</v>
+        <v>3.86</v>
       </c>
       <c r="O49" t="n">
-        <v>3.1</v>
+        <v>2.55</v>
       </c>
       <c r="P49" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.5</v>
+        <v>4.25</v>
       </c>
       <c r="R49" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S49" t="n">
         <v>2.69</v>
@@ -6279,46 +6279,46 @@
         <v>2.65</v>
       </c>
       <c r="U49" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="V49" t="n">
-        <v>6.95</v>
+        <v>7.4</v>
       </c>
       <c r="W49" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X49" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Z49" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AC49" t="n">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AE49" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AH49" t="n">
         <v>1.73</v>
-      </c>
-      <c r="AF49" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG49" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH49" t="n">
-        <v>1.53</v>
       </c>
       <c r="AI49" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6486,77 +6486,77 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U51" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V51" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="W51" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z51" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="AD51" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG51" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH51" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AI51" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6605,77 +6605,77 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.45</v>
+        <v>1.53</v>
       </c>
       <c r="M52" t="n">
-        <v>3</v>
+        <v>3.95</v>
       </c>
       <c r="N52" t="n">
-        <v>2.7</v>
+        <v>5</v>
       </c>
       <c r="O52" t="n">
-        <v>2.95</v>
+        <v>2.06</v>
       </c>
       <c r="P52" t="n">
-        <v>2.05</v>
+        <v>2.35</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.42</v>
+        <v>5.65</v>
       </c>
       <c r="R52" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="S52" t="n">
-        <v>2.62</v>
+        <v>2.91</v>
       </c>
       <c r="T52" t="n">
-        <v>2.96</v>
+        <v>2.48</v>
       </c>
       <c r="U52" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="V52" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="W52" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X52" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z52" t="n">
         <v>3.5</v>
       </c>
       <c r="AA52" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.71</v>
+        <v>1.93</v>
       </c>
       <c r="AC52" t="n">
-        <v>3.48</v>
+        <v>3</v>
       </c>
       <c r="AD52" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.67</v>
+        <v>1.84</v>
       </c>
       <c r="AF52" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AG52" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.48</v>
+        <v>2.31</v>
       </c>
       <c r="AI52" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6724,77 +6724,77 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2</v>
+        <v>1.53</v>
       </c>
       <c r="M53" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="N53" t="n">
-        <v>3.5</v>
+        <v>5.53</v>
       </c>
       <c r="O53" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>4.26</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="U53" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V53" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="W53" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X53" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>2.07</v>
+        <v>1.65</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.72</v>
+        <v>2.1</v>
       </c>
       <c r="AC53" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="AD53" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG53" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH53" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI53" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6843,77 +6843,77 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.45</v>
+        <v>3.2</v>
       </c>
       <c r="M54" t="n">
-        <v>3.47</v>
+        <v>3.24</v>
       </c>
       <c r="N54" t="n">
-        <v>2.59</v>
+        <v>2.21</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S54" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T54" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U54" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V54" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W54" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X54" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD54" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AG54" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH54" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AI54" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,37 +6966,37 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="M55" t="n">
-        <v>3.45</v>
+        <v>3.26</v>
       </c>
       <c r="N55" t="n">
-        <v>3.86</v>
+        <v>4</v>
       </c>
       <c r="O55" t="n">
-        <v>2.55</v>
+        <v>2.46</v>
       </c>
       <c r="P55" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="Q55" t="n">
         <v>4.25</v>
       </c>
       <c r="R55" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S55" t="n">
-        <v>2.69</v>
+        <v>2.87</v>
       </c>
       <c r="T55" t="n">
-        <v>2.65</v>
+        <v>2.9</v>
       </c>
       <c r="U55" t="n">
         <v>1.36</v>
       </c>
       <c r="V55" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="W55" t="n">
         <v>1.03</v>
@@ -7005,34 +7005,34 @@
         <v>1</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="Z55" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="AA55" t="n">
         <v>2</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="AC55" t="n">
-        <v>3.34</v>
+        <v>3.52</v>
       </c>
       <c r="AD55" t="n">
         <v>1.24</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.99</v>
+        <v>1.86</v>
       </c>
       <c r="AG55" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.73</v>
+        <v>1.88</v>
       </c>
       <c r="AI55" s="3" t="n">
         <v>46084.69791666666</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,73 +7085,73 @@
         </is>
       </c>
       <c r="L56" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="M56" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N56" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="O56" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P56" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R56" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S56" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V56" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="W56" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X56" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG56" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH56" t="n">
         <v>1.53</v>
-      </c>
-      <c r="M56" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="N56" t="n">
-        <v>5.53</v>
-      </c>
-      <c r="O56" t="n">
-        <v>0</v>
-      </c>
-      <c r="P56" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
-      <c r="R56" t="n">
-        <v>0</v>
-      </c>
-      <c r="S56" t="n">
-        <v>0</v>
-      </c>
-      <c r="T56" t="n">
-        <v>0</v>
-      </c>
-      <c r="U56" t="n">
-        <v>0</v>
-      </c>
-      <c r="V56" t="n">
-        <v>0</v>
-      </c>
-      <c r="W56" t="n">
-        <v>0</v>
-      </c>
-      <c r="X56" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH56" t="n">
-        <v>0</v>
       </c>
       <c r="AI56" s="3" t="n">
         <v>46084.69791666666</v>
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7406,22 +7406,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L59" t="n">
@@ -7525,22 +7525,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7557,7 +7557,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L60" t="n">

--- a/jogos_2026-03-03.xlsx
+++ b/jogos_2026-03-03.xlsx
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2797,17 +2797,17 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2916,17 +2916,17 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>5.33</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,73 +5657,73 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.85</v>
+        <v>2</v>
       </c>
       <c r="M44" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="N44" t="n">
-        <v>2.24</v>
+        <v>3.5</v>
       </c>
       <c r="O44" t="n">
-        <v>3.7</v>
+        <v>2.62</v>
       </c>
       <c r="P44" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.1</v>
+        <v>4.26</v>
       </c>
       <c r="R44" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="S44" t="n">
-        <v>2.77</v>
+        <v>2.87</v>
       </c>
       <c r="T44" t="n">
-        <v>3.04</v>
+        <v>2.91</v>
       </c>
       <c r="U44" t="n">
         <v>1.33</v>
       </c>
       <c r="V44" t="n">
-        <v>7.6</v>
+        <v>7.1</v>
       </c>
       <c r="W44" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X44" t="n">
         <v>1.02</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="Z44" t="n">
-        <v>3.14</v>
+        <v>2.92</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.19</v>
+        <v>2.07</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AC44" t="n">
-        <v>3.55</v>
+        <v>3.67</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AE44" t="n">
         <v>1.81</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.38</v>
+        <v>1.62</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46084.69791666666</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5891,77 +5891,77 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="M46" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="N46" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="O46" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P46" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q46" t="n">
         <v>3.5</v>
       </c>
-      <c r="O46" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="P46" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>4.26</v>
-      </c>
       <c r="R46" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S46" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U46" t="n">
         <v>1.41</v>
       </c>
-      <c r="S46" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="T46" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="U46" t="n">
+      <c r="V46" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="W46" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X46" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG46" t="n">
         <v>1.33</v>
       </c>
-      <c r="V46" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W46" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X46" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AE46" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AF46" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AG46" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AH46" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AI46" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,73 +6133,73 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.45</v>
+        <v>2.85</v>
       </c>
       <c r="M48" t="n">
-        <v>3.47</v>
+        <v>3.1</v>
       </c>
       <c r="N48" t="n">
-        <v>2.59</v>
+        <v>2.24</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH48" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI48" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6248,77 +6248,77 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U49" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V49" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="W49" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z49" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AG49" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI49" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6367,77 +6367,77 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.45</v>
+        <v>1.8</v>
       </c>
       <c r="M50" t="n">
-        <v>3.4</v>
+        <v>3.26</v>
       </c>
       <c r="N50" t="n">
-        <v>2.88</v>
+        <v>4</v>
       </c>
       <c r="O50" t="n">
-        <v>2.96</v>
+        <v>2.46</v>
       </c>
       <c r="P50" t="n">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.67</v>
+        <v>4.25</v>
       </c>
       <c r="R50" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S50" t="n">
-        <v>2.77</v>
+        <v>2.87</v>
       </c>
       <c r="T50" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="U50" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="V50" t="n">
-        <v>6.75</v>
+        <v>7.5</v>
       </c>
       <c r="W50" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X50" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="Z50" t="n">
-        <v>3.6</v>
+        <v>3.05</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AB50" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE50" t="n">
         <v>1.85</v>
       </c>
-      <c r="AC50" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AE50" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AF50" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AG50" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AH50" t="n">
-        <v>1.52</v>
+        <v>1.88</v>
       </c>
       <c r="AI50" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6486,17 +6486,17 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6605,77 +6605,77 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="M52" t="n">
-        <v>3.95</v>
+        <v>3.45</v>
       </c>
       <c r="N52" t="n">
-        <v>5</v>
+        <v>3.86</v>
       </c>
       <c r="O52" t="n">
-        <v>2.06</v>
+        <v>2.55</v>
       </c>
       <c r="P52" t="n">
-        <v>2.35</v>
+        <v>2.11</v>
       </c>
       <c r="Q52" t="n">
-        <v>5.65</v>
+        <v>4.25</v>
       </c>
       <c r="R52" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S52" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V52" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="W52" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X52" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y52" t="n">
         <v>1.33</v>
       </c>
-      <c r="S52" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="T52" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="U52" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="V52" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W52" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X52" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y52" t="n">
+      <c r="Z52" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AD52" t="n">
         <v>1.24</v>
       </c>
-      <c r="Z52" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AE52" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.85</v>
+        <v>1.99</v>
       </c>
       <c r="AG52" t="n">
-        <v>1.17</v>
+        <v>1.34</v>
       </c>
       <c r="AH52" t="n">
-        <v>2.31</v>
+        <v>1.73</v>
       </c>
       <c r="AI52" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,73 +6728,73 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.53</v>
+        <v>2.45</v>
       </c>
       <c r="M53" t="n">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="N53" t="n">
-        <v>5.53</v>
+        <v>2.88</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V53" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="W53" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.65</v>
+        <v>1.93</v>
       </c>
       <c r="AB53" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AD53" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG53" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH53" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AI53" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6962,77 +6962,77 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="M55" t="n">
-        <v>3.26</v>
+        <v>3.95</v>
       </c>
       <c r="N55" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O55" t="n">
-        <v>2.46</v>
+        <v>2.06</v>
       </c>
       <c r="P55" t="n">
-        <v>2.09</v>
+        <v>2.35</v>
       </c>
       <c r="Q55" t="n">
-        <v>4.25</v>
+        <v>5.65</v>
       </c>
       <c r="R55" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="S55" t="n">
-        <v>2.87</v>
+        <v>2.91</v>
       </c>
       <c r="T55" t="n">
-        <v>2.9</v>
+        <v>2.48</v>
       </c>
       <c r="U55" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="V55" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="W55" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="X55" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="Z55" t="n">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="AA55" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.67</v>
+        <v>1.93</v>
       </c>
       <c r="AC55" t="n">
-        <v>3.52</v>
+        <v>3</v>
       </c>
       <c r="AD55" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AE55" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AF55" t="n">
         <v>1.85</v>
       </c>
-      <c r="AF55" t="n">
-        <v>1.86</v>
-      </c>
       <c r="AG55" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.88</v>
+        <v>2.31</v>
       </c>
       <c r="AI55" s="3" t="n">
         <v>46084.69791666666</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,73 +7085,73 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.45</v>
+        <v>1.53</v>
       </c>
       <c r="M56" t="n">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="N56" t="n">
-        <v>2.72</v>
+        <v>5.53</v>
       </c>
       <c r="O56" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>0</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
+      </c>
+      <c r="V56" t="n">
+        <v>0</v>
+      </c>
+      <c r="W56" t="n">
+        <v>0</v>
+      </c>
+      <c r="X56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB56" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q56" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R56" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S56" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="T56" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U56" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="V56" t="n">
-        <v>6.95</v>
-      </c>
-      <c r="W56" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X56" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="Z56" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AC56" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AD56" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF56" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG56" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH56" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI56" s="3" t="n">
         <v>46084.69791666666</v>
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G59" t="n">

--- a/jogos_2026-03-03.xlsx
+++ b/jogos_2026-03-03.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2797,17 +2797,17 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2916,17 +2916,17 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4344,77 +4344,77 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46084.6875</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4582,77 +4582,77 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46084.6875</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.75</v>
+        <v>2.49</v>
       </c>
       <c r="M43" t="n">
-        <v>3.91</v>
+        <v>3.8</v>
       </c>
       <c r="N43" t="n">
-        <v>5.33</v>
+        <v>2.86</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5653,77 +5653,77 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="M44" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="N44" t="n">
-        <v>3.5</v>
+        <v>2.21</v>
       </c>
       <c r="O44" t="n">
-        <v>2.62</v>
+        <v>3.92</v>
       </c>
       <c r="P44" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q44" t="n">
-        <v>4.26</v>
+        <v>2.8</v>
       </c>
       <c r="R44" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="S44" t="n">
-        <v>2.87</v>
+        <v>2.77</v>
       </c>
       <c r="T44" t="n">
-        <v>2.91</v>
+        <v>2.73</v>
       </c>
       <c r="U44" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="V44" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W44" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X44" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD44" t="n">
         <v>1.33</v>
       </c>
-      <c r="V44" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W44" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X44" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AE44" t="n">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.62</v>
+        <v>1.31</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46084.69791666666</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,73 +5776,73 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.45</v>
+        <v>1.8</v>
       </c>
       <c r="M45" t="n">
-        <v>3</v>
+        <v>3.26</v>
       </c>
       <c r="N45" t="n">
-        <v>2.7</v>
+        <v>4</v>
       </c>
       <c r="O45" t="n">
-        <v>2.95</v>
+        <v>2.46</v>
       </c>
       <c r="P45" t="n">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.42</v>
+        <v>4.25</v>
       </c>
       <c r="R45" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="S45" t="n">
-        <v>2.62</v>
+        <v>2.87</v>
       </c>
       <c r="T45" t="n">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="U45" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="V45" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="W45" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X45" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="Z45" t="n">
-        <v>3.5</v>
+        <v>3.05</v>
       </c>
       <c r="AA45" t="n">
         <v>2</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AC45" t="n">
-        <v>3.48</v>
+        <v>3.52</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AF45" t="n">
-        <v>2.1</v>
+        <v>1.86</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.48</v>
+        <v>1.88</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46084.69791666666</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5891,77 +5891,77 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.45</v>
+        <v>2.85</v>
       </c>
       <c r="M46" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N46" t="n">
-        <v>2.72</v>
+        <v>2.24</v>
       </c>
       <c r="O46" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="P46" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q46" t="n">
         <v>3.1</v>
       </c>
-      <c r="P46" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>3.5</v>
-      </c>
       <c r="R46" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="S46" t="n">
-        <v>2.69</v>
+        <v>2.77</v>
       </c>
       <c r="T46" t="n">
-        <v>2.65</v>
+        <v>3.04</v>
       </c>
       <c r="U46" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="V46" t="n">
-        <v>6.95</v>
+        <v>7.6</v>
       </c>
       <c r="W46" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X46" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z46" t="n">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.98</v>
+        <v>2.19</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AC46" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="AD46" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AG46" t="n">
         <v>1.29</v>
       </c>
-      <c r="AE46" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF46" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG46" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH46" t="n">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="AI46" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,73 +6133,73 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.85</v>
+        <v>2.45</v>
       </c>
       <c r="M48" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="N48" t="n">
-        <v>2.24</v>
+        <v>2.7</v>
       </c>
       <c r="O48" t="n">
-        <v>3.7</v>
+        <v>2.95</v>
       </c>
       <c r="P48" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.1</v>
+        <v>3.42</v>
       </c>
       <c r="R48" t="n">
         <v>1.44</v>
       </c>
       <c r="S48" t="n">
-        <v>2.77</v>
+        <v>2.62</v>
       </c>
       <c r="T48" t="n">
-        <v>3.04</v>
+        <v>2.96</v>
       </c>
       <c r="U48" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="V48" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="W48" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X48" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z48" t="n">
-        <v>3.14</v>
+        <v>3.5</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.19</v>
+        <v>2</v>
       </c>
       <c r="AB48" t="n">
         <v>1.71</v>
       </c>
       <c r="AC48" t="n">
-        <v>3.55</v>
+        <v>3.48</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AG48" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="AI48" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6248,77 +6248,77 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH49" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI49" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,37 +6371,37 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="M50" t="n">
-        <v>3.26</v>
+        <v>3.45</v>
       </c>
       <c r="N50" t="n">
-        <v>4</v>
+        <v>3.86</v>
       </c>
       <c r="O50" t="n">
-        <v>2.46</v>
+        <v>2.55</v>
       </c>
       <c r="P50" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="Q50" t="n">
         <v>4.25</v>
       </c>
       <c r="R50" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S50" t="n">
-        <v>2.87</v>
+        <v>2.69</v>
       </c>
       <c r="T50" t="n">
-        <v>2.9</v>
+        <v>2.65</v>
       </c>
       <c r="U50" t="n">
         <v>1.36</v>
       </c>
       <c r="V50" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="W50" t="n">
         <v>1.03</v>
@@ -6410,34 +6410,34 @@
         <v>1</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="Z50" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="AA50" t="n">
         <v>2</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.67</v>
+        <v>1.81</v>
       </c>
       <c r="AC50" t="n">
-        <v>3.52</v>
+        <v>3.34</v>
       </c>
       <c r="AD50" t="n">
         <v>1.24</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.86</v>
+        <v>1.99</v>
       </c>
       <c r="AG50" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="AH50" t="n">
-        <v>1.88</v>
+        <v>1.73</v>
       </c>
       <c r="AI50" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6605,77 +6605,77 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U52" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V52" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="W52" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z52" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD52" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AG52" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI52" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,73 +6728,73 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.45</v>
+        <v>1.53</v>
       </c>
       <c r="M53" t="n">
-        <v>3.4</v>
+        <v>3.95</v>
       </c>
       <c r="N53" t="n">
-        <v>2.88</v>
+        <v>5</v>
       </c>
       <c r="O53" t="n">
-        <v>2.96</v>
+        <v>2.06</v>
       </c>
       <c r="P53" t="n">
-        <v>2.05</v>
+        <v>2.35</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.67</v>
+        <v>5.65</v>
       </c>
       <c r="R53" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="S53" t="n">
-        <v>2.77</v>
+        <v>2.91</v>
       </c>
       <c r="T53" t="n">
-        <v>2.75</v>
+        <v>2.48</v>
       </c>
       <c r="U53" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="V53" t="n">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
       <c r="W53" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="X53" t="n">
         <v>1.01</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="Z53" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AA53" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AB53" t="n">
         <v>1.93</v>
       </c>
-      <c r="AB53" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AC53" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="AD53" t="n">
         <v>1.32</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.7</v>
+        <v>1.84</v>
       </c>
       <c r="AF53" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AG53" t="n">
-        <v>1.31</v>
+        <v>1.17</v>
       </c>
       <c r="AH53" t="n">
-        <v>1.52</v>
+        <v>2.31</v>
       </c>
       <c r="AI53" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,22 +6847,22 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>3.2</v>
+        <v>2.45</v>
       </c>
       <c r="M54" t="n">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="N54" t="n">
-        <v>2.21</v>
+        <v>2.88</v>
       </c>
       <c r="O54" t="n">
-        <v>3.92</v>
+        <v>2.96</v>
       </c>
       <c r="P54" t="n">
         <v>2.05</v>
       </c>
       <c r="Q54" t="n">
-        <v>2.8</v>
+        <v>3.67</v>
       </c>
       <c r="R54" t="n">
         <v>1.38</v>
@@ -6871,13 +6871,13 @@
         <v>2.77</v>
       </c>
       <c r="T54" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="U54" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="V54" t="n">
-        <v>6.5</v>
+        <v>6.75</v>
       </c>
       <c r="W54" t="n">
         <v>1.04</v>
@@ -6886,34 +6886,34 @@
         <v>1.01</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="Z54" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AC54" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AD54" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AE54" t="n">
         <v>1.7</v>
       </c>
       <c r="AF54" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AG54" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AH54" t="n">
-        <v>1.31</v>
+        <v>1.52</v>
       </c>
       <c r="AI54" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,73 +6966,73 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.53</v>
+        <v>2.45</v>
       </c>
       <c r="M55" t="n">
-        <v>3.95</v>
+        <v>3.2</v>
       </c>
       <c r="N55" t="n">
-        <v>5</v>
+        <v>2.72</v>
       </c>
       <c r="O55" t="n">
-        <v>2.06</v>
+        <v>3.1</v>
       </c>
       <c r="P55" t="n">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="Q55" t="n">
-        <v>5.65</v>
+        <v>3.5</v>
       </c>
       <c r="R55" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="S55" t="n">
-        <v>2.91</v>
+        <v>2.69</v>
       </c>
       <c r="T55" t="n">
-        <v>2.48</v>
+        <v>2.65</v>
       </c>
       <c r="U55" t="n">
         <v>1.41</v>
       </c>
       <c r="V55" t="n">
-        <v>6.5</v>
+        <v>6.95</v>
       </c>
       <c r="W55" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="X55" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="Z55" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.78</v>
+        <v>1.98</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.93</v>
+        <v>1.75</v>
       </c>
       <c r="AC55" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="AD55" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.84</v>
+        <v>1.73</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AG55" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AH55" t="n">
-        <v>2.31</v>
+        <v>1.53</v>
       </c>
       <c r="AI55" s="3" t="n">
         <v>46084.69791666666</v>
@@ -7406,22 +7406,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L59" t="n">
@@ -7525,22 +7525,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7557,7 +7557,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L60" t="n">

--- a/jogos_2026-03-03.xlsx
+++ b/jogos_2026-03-03.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2916,17 +2916,17 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3392,17 +3392,17 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>7.03</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4582,77 +4582,77 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.45</v>
+        <v>1.75</v>
       </c>
       <c r="M35" t="n">
-        <v>3.3</v>
+        <v>3.91</v>
       </c>
       <c r="N35" t="n">
-        <v>2.43</v>
+        <v>5.33</v>
       </c>
       <c r="O35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AB35" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46084.6875</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>5.33</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5177,77 +5177,77 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46084.6875</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.49</v>
+        <v>4.28</v>
       </c>
       <c r="M43" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="N43" t="n">
-        <v>2.86</v>
+        <v>1.66</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5653,77 +5653,77 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>3.2</v>
+        <v>2.85</v>
       </c>
       <c r="M44" t="n">
-        <v>3.24</v>
+        <v>3.1</v>
       </c>
       <c r="N44" t="n">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="O44" t="n">
-        <v>3.92</v>
+        <v>3.7</v>
       </c>
       <c r="P44" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="R44" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="S44" t="n">
         <v>2.77</v>
       </c>
       <c r="T44" t="n">
-        <v>2.73</v>
+        <v>3.04</v>
       </c>
       <c r="U44" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="V44" t="n">
-        <v>6.5</v>
+        <v>7.6</v>
       </c>
       <c r="W44" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X44" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z44" t="n">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.88</v>
+        <v>2.19</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.95</v>
+        <v>1.71</v>
       </c>
       <c r="AC44" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="AF44" t="n">
-        <v>2.02</v>
+        <v>1.9</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46084.69791666666</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,73 +5776,73 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="M45" t="n">
-        <v>3.26</v>
+        <v>3.38</v>
       </c>
       <c r="N45" t="n">
-        <v>4</v>
+        <v>3.08</v>
       </c>
       <c r="O45" t="n">
-        <v>2.46</v>
+        <v>2.8</v>
       </c>
       <c r="P45" t="n">
-        <v>2.09</v>
+        <v>2.19</v>
       </c>
       <c r="Q45" t="n">
-        <v>4.25</v>
+        <v>3.5</v>
       </c>
       <c r="R45" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S45" t="n">
-        <v>2.87</v>
+        <v>2.81</v>
       </c>
       <c r="T45" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="U45" t="n">
         <v>1.36</v>
       </c>
       <c r="V45" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="W45" t="n">
         <v>1.03</v>
       </c>
       <c r="X45" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="Z45" t="n">
-        <v>3.05</v>
+        <v>3.24</v>
       </c>
       <c r="AA45" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AC45" t="n">
-        <v>3.52</v>
+        <v>3.3</v>
       </c>
       <c r="AD45" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG45" t="n">
         <v>1.24</v>
       </c>
-      <c r="AE45" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF45" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AG45" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AH45" t="n">
-        <v>1.88</v>
+        <v>1.55</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46084.69791666666</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5891,77 +5891,77 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.85</v>
+        <v>2.45</v>
       </c>
       <c r="M46" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="N46" t="n">
-        <v>2.24</v>
+        <v>2.88</v>
       </c>
       <c r="O46" t="n">
-        <v>3.7</v>
+        <v>2.96</v>
       </c>
       <c r="P46" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.1</v>
+        <v>3.67</v>
       </c>
       <c r="R46" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="S46" t="n">
         <v>2.77</v>
       </c>
       <c r="T46" t="n">
-        <v>3.04</v>
+        <v>2.75</v>
       </c>
       <c r="U46" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="V46" t="n">
-        <v>7.6</v>
+        <v>6.75</v>
       </c>
       <c r="W46" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X46" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Z46" t="n">
-        <v>3.14</v>
+        <v>3.6</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.19</v>
+        <v>1.93</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.71</v>
+        <v>1.85</v>
       </c>
       <c r="AC46" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.38</v>
+        <v>1.52</v>
       </c>
       <c r="AI46" s="3" t="n">
         <v>46084.69791666666</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,73 +6014,73 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="M47" t="n">
-        <v>3.38</v>
+        <v>3.45</v>
       </c>
       <c r="N47" t="n">
-        <v>3.08</v>
+        <v>3.86</v>
       </c>
       <c r="O47" t="n">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="P47" t="n">
-        <v>2.19</v>
+        <v>2.11</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.5</v>
+        <v>4.25</v>
       </c>
       <c r="R47" t="n">
         <v>1.38</v>
       </c>
       <c r="S47" t="n">
-        <v>2.81</v>
+        <v>2.69</v>
       </c>
       <c r="T47" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="U47" t="n">
         <v>1.36</v>
       </c>
       <c r="V47" t="n">
-        <v>6.5</v>
+        <v>7.4</v>
       </c>
       <c r="W47" t="n">
         <v>1.03</v>
       </c>
       <c r="X47" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z47" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AB47" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AH47" t="n">
         <v>1.73</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE47" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF47" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG47" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AH47" t="n">
-        <v>1.55</v>
       </c>
       <c r="AI47" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6129,77 +6129,77 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L48" t="n">
         <v>2.45</v>
       </c>
       <c r="M48" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="N48" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="O48" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="P48" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="R48" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="S48" t="n">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="T48" t="n">
-        <v>2.96</v>
+        <v>2.65</v>
       </c>
       <c r="U48" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="V48" t="n">
-        <v>8</v>
+        <v>6.95</v>
       </c>
       <c r="W48" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X48" t="n">
         <v>1.06</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="Z48" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AA48" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AC48" t="n">
-        <v>3.48</v>
+        <v>3.2</v>
       </c>
       <c r="AD48" t="n">
         <v>1.29</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AF48" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AG48" t="n">
         <v>1.33</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AI48" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6248,77 +6248,77 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="M49" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="N49" t="n">
-        <v>3.5</v>
+        <v>2.21</v>
       </c>
       <c r="O49" t="n">
-        <v>2.62</v>
+        <v>3.92</v>
       </c>
       <c r="P49" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q49" t="n">
-        <v>4.26</v>
+        <v>2.8</v>
       </c>
       <c r="R49" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="S49" t="n">
-        <v>2.87</v>
+        <v>2.77</v>
       </c>
       <c r="T49" t="n">
-        <v>2.91</v>
+        <v>2.73</v>
       </c>
       <c r="U49" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="V49" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W49" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD49" t="n">
         <v>1.33</v>
       </c>
-      <c r="V49" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W49" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X49" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AE49" t="n">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="AG49" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.62</v>
+        <v>1.31</v>
       </c>
       <c r="AI49" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,73 +6371,73 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="M50" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="N50" t="n">
-        <v>3.86</v>
+        <v>3.5</v>
       </c>
       <c r="O50" t="n">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="P50" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="Q50" t="n">
-        <v>4.25</v>
+        <v>4.26</v>
       </c>
       <c r="R50" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="S50" t="n">
-        <v>2.69</v>
+        <v>2.87</v>
       </c>
       <c r="T50" t="n">
-        <v>2.65</v>
+        <v>2.91</v>
       </c>
       <c r="U50" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V50" t="n">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
       <c r="W50" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X50" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Z50" t="n">
-        <v>3.25</v>
+        <v>2.92</v>
       </c>
       <c r="AA50" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AB50" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AE50" t="n">
         <v>1.81</v>
       </c>
-      <c r="AC50" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE50" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AF50" t="n">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="AG50" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="AH50" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AI50" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6731,70 +6731,70 @@
         <v>1.53</v>
       </c>
       <c r="M53" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="N53" t="n">
-        <v>5</v>
+        <v>5.53</v>
       </c>
       <c r="O53" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="U53" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="V53" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W53" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X53" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AC53" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD53" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG53" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AH53" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AI53" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6843,77 +6843,77 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L54" t="n">
         <v>2.45</v>
       </c>
       <c r="M54" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="N54" t="n">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="O54" t="n">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="P54" t="n">
         <v>2.05</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.67</v>
+        <v>3.42</v>
       </c>
       <c r="R54" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="S54" t="n">
-        <v>2.77</v>
+        <v>2.62</v>
       </c>
       <c r="T54" t="n">
-        <v>2.75</v>
+        <v>2.96</v>
       </c>
       <c r="U54" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="V54" t="n">
-        <v>6.75</v>
+        <v>8</v>
       </c>
       <c r="W54" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X54" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z54" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AC54" t="n">
-        <v>3.35</v>
+        <v>3.48</v>
       </c>
       <c r="AD54" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AF54" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AG54" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AH54" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="AI54" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,73 +6966,73 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.45</v>
+        <v>1.53</v>
       </c>
       <c r="M55" t="n">
-        <v>3.2</v>
+        <v>3.95</v>
       </c>
       <c r="N55" t="n">
-        <v>2.72</v>
+        <v>5</v>
       </c>
       <c r="O55" t="n">
-        <v>3.1</v>
+        <v>2.06</v>
       </c>
       <c r="P55" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.5</v>
+        <v>5.65</v>
       </c>
       <c r="R55" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="S55" t="n">
-        <v>2.69</v>
+        <v>2.91</v>
       </c>
       <c r="T55" t="n">
-        <v>2.65</v>
+        <v>2.48</v>
       </c>
       <c r="U55" t="n">
         <v>1.41</v>
       </c>
       <c r="V55" t="n">
-        <v>6.95</v>
+        <v>6.5</v>
       </c>
       <c r="W55" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="X55" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="Z55" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.98</v>
+        <v>1.78</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.75</v>
+        <v>1.93</v>
       </c>
       <c r="AC55" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AD55" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="AF55" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AG55" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.53</v>
+        <v>2.31</v>
       </c>
       <c r="AI55" s="3" t="n">
         <v>46084.69791666666</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7081,77 +7081,77 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="M56" t="n">
-        <v>4.3</v>
+        <v>3.26</v>
       </c>
       <c r="N56" t="n">
-        <v>5.53</v>
+        <v>4</v>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S56" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="T56" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U56" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V56" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W56" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="AB56" t="n">
-        <v>2.1</v>
+        <v>1.67</v>
       </c>
       <c r="AC56" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AD56" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE56" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF56" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG56" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH56" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AI56" s="3" t="n">
         <v>46084.69791666666</v>
@@ -7287,22 +7287,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7319,7 +7319,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L58" t="n">
@@ -7406,22 +7406,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L59" t="n">

--- a/jogos_2026-03-03.xlsx
+++ b/jogos_2026-03-03.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI60"/>
+  <dimension ref="A1:AI61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -975,12 +975,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1085,7 +1085,7 @@
         <v>0</v>
       </c>
       <c r="AI5" s="3" t="n">
-        <v>46084.4375</v>
+        <v>46084.41666666666</v>
       </c>
     </row>
     <row r="6">
@@ -1213,12 +1213,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1323,7 +1323,7 @@
         <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
-        <v>46084.45833333334</v>
+        <v>46084.4375</v>
       </c>
     </row>
     <row r="8">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.81</v>
+        <v>2.5</v>
       </c>
       <c r="M8" t="n">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="N8" t="n">
-        <v>4.55</v>
+        <v>2.8</v>
       </c>
       <c r="O8" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.78</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46084.45833333334</v>
@@ -1451,12 +1451,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,76 +1492,76 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>5.78</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AI9" s="3" t="n">
-        <v>46084.5</v>
+        <v>46084.45833333334</v>
       </c>
     </row>
     <row r="10">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>6.13</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1799,7 +1799,7 @@
         <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
-        <v>46084.5625</v>
+        <v>46084.5</v>
       </c>
     </row>
     <row r="12">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>6.13</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1918,7 +1918,7 @@
         <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
-        <v>46084.58333333334</v>
+        <v>46084.5625</v>
       </c>
     </row>
     <row r="13">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2394,7 +2394,7 @@
         <v>0</v>
       </c>
       <c r="AI16" s="3" t="n">
-        <v>46084.60416666666</v>
+        <v>46084.58333333334</v>
       </c>
     </row>
     <row r="17">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2751,7 +2751,7 @@
         <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
-        <v>46084.625</v>
+        <v>46084.60416666666</v>
       </c>
     </row>
     <row r="20">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3273,17 +3273,17 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3392,17 +3392,17 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3474,12 +3474,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3584,7 +3584,7 @@
         <v>0</v>
       </c>
       <c r="AI26" s="3" t="n">
-        <v>46084.65625</v>
+        <v>46084.625</v>
       </c>
     </row>
     <row r="27">
@@ -3712,12 +3712,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,76 +3753,76 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI28" s="3" t="n">
-        <v>46084.66666666666</v>
+        <v>46084.65625</v>
       </c>
     </row>
     <row r="29">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.4</v>
+        <v>3.72</v>
       </c>
       <c r="M30" t="n">
-        <v>4.6</v>
+        <v>3.15</v>
       </c>
       <c r="N30" t="n">
-        <v>7.03</v>
+        <v>2.05</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.72</v>
+        <v>2.65</v>
       </c>
       <c r="M31" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="N31" t="n">
-        <v>2.05</v>
+        <v>2.65</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.65</v>
+        <v>1.4</v>
       </c>
       <c r="M32" t="n">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="N32" t="n">
-        <v>2.65</v>
+        <v>7.03</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4307,12 +4307,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,76 +4348,76 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI33" s="3" t="n">
-        <v>46084.6875</v>
+        <v>46084.66666666666</v>
       </c>
     </row>
     <row r="34">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4582,77 +4582,77 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.75</v>
+        <v>2.45</v>
       </c>
       <c r="M35" t="n">
-        <v>3.91</v>
+        <v>3.3</v>
       </c>
       <c r="N35" t="n">
-        <v>5.33</v>
+        <v>2.43</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46084.6875</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5177,77 +5177,77 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46084.6875</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>4.28</v>
+        <v>1.75</v>
       </c>
       <c r="M43" t="n">
-        <v>4.2</v>
+        <v>3.91</v>
       </c>
       <c r="N43" t="n">
-        <v>1.66</v>
+        <v>5.33</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5616,12 +5616,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5653,80 +5653,80 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.85</v>
+        <v>2.05</v>
       </c>
       <c r="M44" t="n">
-        <v>3.1</v>
+        <v>3.56</v>
       </c>
       <c r="N44" t="n">
-        <v>2.24</v>
+        <v>4.05</v>
       </c>
       <c r="O44" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" t="n">
+        <v>0</v>
+      </c>
+      <c r="W44" t="n">
+        <v>0</v>
+      </c>
+      <c r="X44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA44" t="n">
         <v>2.15</v>
       </c>
-      <c r="Q44" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R44" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S44" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T44" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="U44" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V44" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="W44" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X44" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>2.19</v>
-      </c>
       <c r="AB44" t="n">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="AC44" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AI44" s="3" t="n">
-        <v>46084.69791666666</v>
+        <v>46084.6875</v>
       </c>
     </row>
     <row r="45">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5891,77 +5891,77 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.45</v>
+        <v>2.85</v>
       </c>
       <c r="M46" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="N46" t="n">
-        <v>2.88</v>
+        <v>2.24</v>
       </c>
       <c r="O46" t="n">
-        <v>2.96</v>
+        <v>3.7</v>
       </c>
       <c r="P46" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.67</v>
+        <v>3.1</v>
       </c>
       <c r="R46" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="S46" t="n">
         <v>2.77</v>
       </c>
       <c r="T46" t="n">
-        <v>2.75</v>
+        <v>3.04</v>
       </c>
       <c r="U46" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V46" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="W46" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X46" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH46" t="n">
         <v>1.38</v>
-      </c>
-      <c r="V46" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="W46" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X46" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AE46" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AF46" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG46" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AH46" t="n">
-        <v>1.52</v>
       </c>
       <c r="AI46" s="3" t="n">
         <v>46084.69791666666</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6010,77 +6010,77 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.91</v>
+        <v>1.53</v>
       </c>
       <c r="M47" t="n">
-        <v>3.45</v>
+        <v>3.95</v>
       </c>
       <c r="N47" t="n">
-        <v>3.86</v>
+        <v>5</v>
       </c>
       <c r="O47" t="n">
-        <v>2.55</v>
+        <v>2.06</v>
       </c>
       <c r="P47" t="n">
-        <v>2.11</v>
+        <v>2.35</v>
       </c>
       <c r="Q47" t="n">
-        <v>4.25</v>
+        <v>5.65</v>
       </c>
       <c r="R47" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="S47" t="n">
-        <v>2.69</v>
+        <v>2.91</v>
       </c>
       <c r="T47" t="n">
-        <v>2.65</v>
+        <v>2.48</v>
       </c>
       <c r="U47" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="V47" t="n">
-        <v>7.4</v>
+        <v>6.5</v>
       </c>
       <c r="W47" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="X47" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="Z47" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="AA47" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.81</v>
+        <v>1.93</v>
       </c>
       <c r="AC47" t="n">
-        <v>3.34</v>
+        <v>3</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.99</v>
+        <v>1.85</v>
       </c>
       <c r="AG47" t="n">
-        <v>1.34</v>
+        <v>1.17</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.73</v>
+        <v>2.31</v>
       </c>
       <c r="AI47" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,73 +6133,73 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>6.95</v>
+        <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X48" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG48" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI48" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6248,77 +6248,77 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>3.2</v>
+        <v>2.45</v>
       </c>
       <c r="M49" t="n">
-        <v>3.24</v>
+        <v>3.47</v>
       </c>
       <c r="N49" t="n">
-        <v>2.21</v>
+        <v>2.59</v>
       </c>
       <c r="O49" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="U49" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V49" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W49" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X49" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z49" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF49" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AG49" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AI49" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6367,77 +6367,77 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="M50" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="N50" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="O50" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P50" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q50" t="n">
         <v>3.5</v>
       </c>
-      <c r="O50" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="P50" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>4.26</v>
-      </c>
       <c r="R50" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S50" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U50" t="n">
         <v>1.41</v>
       </c>
-      <c r="S50" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="T50" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="U50" t="n">
+      <c r="V50" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="W50" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X50" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG50" t="n">
         <v>1.33</v>
       </c>
-      <c r="V50" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W50" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X50" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AE50" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AF50" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AG50" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AH50" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AI50" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,73 +6490,73 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="M51" t="n">
-        <v>3.47</v>
+        <v>3.25</v>
       </c>
       <c r="N51" t="n">
-        <v>2.59</v>
+        <v>3.5</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S51" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="T51" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U51" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V51" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="W51" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X51" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC51" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="AD51" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG51" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH51" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI51" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>5.53</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6724,77 +6724,77 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.53</v>
+        <v>2.45</v>
       </c>
       <c r="M53" t="n">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="N53" t="n">
-        <v>5.53</v>
+        <v>2.7</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V53" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W53" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="AB53" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF53" t="n">
         <v>2.1</v>
       </c>
-      <c r="AC53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF53" t="n">
-        <v>0</v>
-      </c>
       <c r="AG53" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH53" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AI53" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,73 +6847,73 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.45</v>
+        <v>1.8</v>
       </c>
       <c r="M54" t="n">
-        <v>3</v>
+        <v>3.26</v>
       </c>
       <c r="N54" t="n">
-        <v>2.7</v>
+        <v>4</v>
       </c>
       <c r="O54" t="n">
-        <v>2.95</v>
+        <v>2.46</v>
       </c>
       <c r="P54" t="n">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.42</v>
+        <v>4.25</v>
       </c>
       <c r="R54" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="S54" t="n">
-        <v>2.62</v>
+        <v>2.87</v>
       </c>
       <c r="T54" t="n">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="U54" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="V54" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="W54" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X54" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="Z54" t="n">
-        <v>3.5</v>
+        <v>3.05</v>
       </c>
       <c r="AA54" t="n">
         <v>2</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AC54" t="n">
-        <v>3.48</v>
+        <v>3.52</v>
       </c>
       <c r="AD54" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AF54" t="n">
-        <v>2.1</v>
+        <v>1.86</v>
       </c>
       <c r="AG54" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AH54" t="n">
-        <v>1.48</v>
+        <v>1.88</v>
       </c>
       <c r="AI54" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,73 +6966,73 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.53</v>
+        <v>3.2</v>
       </c>
       <c r="M55" t="n">
-        <v>3.95</v>
+        <v>3.24</v>
       </c>
       <c r="N55" t="n">
-        <v>5</v>
+        <v>2.21</v>
       </c>
       <c r="O55" t="n">
-        <v>2.06</v>
+        <v>3.92</v>
       </c>
       <c r="P55" t="n">
-        <v>2.35</v>
+        <v>2.05</v>
       </c>
       <c r="Q55" t="n">
-        <v>5.65</v>
+        <v>2.8</v>
       </c>
       <c r="R55" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="S55" t="n">
-        <v>2.91</v>
+        <v>2.77</v>
       </c>
       <c r="T55" t="n">
-        <v>2.48</v>
+        <v>2.73</v>
       </c>
       <c r="U55" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="V55" t="n">
         <v>6.5</v>
       </c>
       <c r="W55" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="X55" t="n">
         <v>1.01</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Z55" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AC55" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="AD55" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.85</v>
+        <v>2.02</v>
       </c>
       <c r="AG55" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AH55" t="n">
-        <v>2.31</v>
+        <v>1.31</v>
       </c>
       <c r="AI55" s="3" t="n">
         <v>46084.69791666666</v>
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,37 +7085,37 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="M56" t="n">
-        <v>3.26</v>
+        <v>3.45</v>
       </c>
       <c r="N56" t="n">
-        <v>4</v>
+        <v>3.86</v>
       </c>
       <c r="O56" t="n">
-        <v>2.46</v>
+        <v>2.55</v>
       </c>
       <c r="P56" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="Q56" t="n">
         <v>4.25</v>
       </c>
       <c r="R56" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S56" t="n">
-        <v>2.87</v>
+        <v>2.69</v>
       </c>
       <c r="T56" t="n">
-        <v>2.9</v>
+        <v>2.65</v>
       </c>
       <c r="U56" t="n">
         <v>1.36</v>
       </c>
       <c r="V56" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="W56" t="n">
         <v>1.03</v>
@@ -7124,34 +7124,34 @@
         <v>1</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="Z56" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="AA56" t="n">
         <v>2</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.67</v>
+        <v>1.81</v>
       </c>
       <c r="AC56" t="n">
-        <v>3.52</v>
+        <v>3.34</v>
       </c>
       <c r="AD56" t="n">
         <v>1.24</v>
       </c>
       <c r="AE56" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AF56" t="n">
-        <v>1.86</v>
+        <v>1.99</v>
       </c>
       <c r="AG56" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="AH56" t="n">
-        <v>1.88</v>
+        <v>1.73</v>
       </c>
       <c r="AI56" s="3" t="n">
         <v>46084.69791666666</v>
@@ -7163,12 +7163,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,76 +7204,76 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>6.24</v>
+        <v>2.45</v>
       </c>
       <c r="M57" t="n">
-        <v>4.72</v>
+        <v>3.4</v>
       </c>
       <c r="N57" t="n">
-        <v>1.55</v>
+        <v>2.88</v>
       </c>
       <c r="O57" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S57" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T57" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U57" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V57" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="W57" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X57" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y57" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z57" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.55</v>
+        <v>1.93</v>
       </c>
       <c r="AB57" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="AC57" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AD57" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE57" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG57" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH57" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AI57" s="3" t="n">
-        <v>46084.71875</v>
+        <v>46084.69791666666</v>
       </c>
     </row>
     <row r="58">
@@ -7282,12 +7282,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7319,17 +7319,17 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>6.24</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,10 +7368,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -7392,7 +7392,7 @@
         <v>0</v>
       </c>
       <c r="AI58" s="3" t="n">
-        <v>46084.875</v>
+        <v>46084.71875</v>
       </c>
     </row>
     <row r="59">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7630,6 +7630,125 @@
         <v>0</v>
       </c>
       <c r="AI60" s="3" t="n">
+        <v>46084.875</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Italy Serie C Group B</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Rimini</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Città di Campobasso</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>canceled</t>
+        </is>
+      </c>
+      <c r="L61" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>0</v>
+      </c>
+      <c r="R61" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" t="n">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>0</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
+      </c>
+      <c r="V61" t="n">
+        <v>0</v>
+      </c>
+      <c r="W61" t="n">
+        <v>0</v>
+      </c>
+      <c r="X61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI61" s="3" t="n">
         <v>46084.875</v>
       </c>
     </row>

--- a/jogos_2026-03-03.xlsx
+++ b/jogos_2026-03-03.xlsx
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.47</v>
+        <v>2.65</v>
       </c>
       <c r="M29" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N29" t="n">
-        <v>2.11</v>
+        <v>2.65</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.72</v>
+        <v>1.4</v>
       </c>
       <c r="M30" t="n">
-        <v>3.15</v>
+        <v>4.6</v>
       </c>
       <c r="N30" t="n">
-        <v>2.05</v>
+        <v>7.03</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.65</v>
+        <v>3.47</v>
       </c>
       <c r="M31" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N31" t="n">
-        <v>2.65</v>
+        <v>2.11</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="M32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N32" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="O32" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P32" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="V32" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE32" t="n">
         <v>1.4</v>
       </c>
-      <c r="M32" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="N32" t="n">
-        <v>7.03</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" t="n">
-        <v>0</v>
-      </c>
-      <c r="W32" t="n">
-        <v>0</v>
-      </c>
-      <c r="X32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>0</v>
-      </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46084.66666666666</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.87</v>
+        <v>3.72</v>
       </c>
       <c r="M33" t="n">
-        <v>3.8</v>
+        <v>3.15</v>
       </c>
       <c r="N33" t="n">
-        <v>2.98</v>
+        <v>2.05</v>
       </c>
       <c r="O33" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46084.66666666666</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5772,77 +5772,77 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46084.69791666666</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5891,77 +5891,77 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.85</v>
+        <v>1.53</v>
       </c>
       <c r="M46" t="n">
-        <v>3.1</v>
+        <v>4.3</v>
       </c>
       <c r="N46" t="n">
-        <v>2.24</v>
+        <v>5.53</v>
       </c>
       <c r="O46" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.19</v>
+        <v>1.65</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.71</v>
+        <v>2.1</v>
       </c>
       <c r="AC46" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AI46" s="3" t="n">
         <v>46084.69791666666</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6010,77 +6010,77 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.53</v>
+        <v>2.1</v>
       </c>
       <c r="M47" t="n">
-        <v>3.95</v>
+        <v>3.38</v>
       </c>
       <c r="N47" t="n">
-        <v>5</v>
+        <v>3.08</v>
       </c>
       <c r="O47" t="n">
-        <v>2.06</v>
+        <v>2.8</v>
       </c>
       <c r="P47" t="n">
-        <v>2.35</v>
+        <v>2.19</v>
       </c>
       <c r="Q47" t="n">
-        <v>5.65</v>
+        <v>3.5</v>
       </c>
       <c r="R47" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="S47" t="n">
-        <v>2.91</v>
+        <v>2.81</v>
       </c>
       <c r="T47" t="n">
-        <v>2.48</v>
+        <v>2.75</v>
       </c>
       <c r="U47" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="V47" t="n">
         <v>6.5</v>
       </c>
       <c r="W47" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="X47" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y47" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG47" t="n">
         <v>1.24</v>
       </c>
-      <c r="Z47" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AE47" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AF47" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG47" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AH47" t="n">
-        <v>2.31</v>
+        <v>1.55</v>
       </c>
       <c r="AI47" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6129,77 +6129,77 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH48" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI48" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6255,70 +6255,70 @@
         <v>2.45</v>
       </c>
       <c r="M49" t="n">
-        <v>3.47</v>
+        <v>3</v>
       </c>
       <c r="N49" t="n">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH49" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AI49" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6374,70 +6374,70 @@
         <v>2.45</v>
       </c>
       <c r="M50" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="N50" t="n">
-        <v>2.72</v>
+        <v>2.88</v>
       </c>
       <c r="O50" t="n">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="P50" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.5</v>
+        <v>3.67</v>
       </c>
       <c r="R50" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S50" t="n">
-        <v>2.69</v>
+        <v>2.77</v>
       </c>
       <c r="T50" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="U50" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="V50" t="n">
-        <v>6.95</v>
+        <v>6.75</v>
       </c>
       <c r="W50" t="n">
         <v>1.04</v>
       </c>
       <c r="X50" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y50" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG50" t="n">
         <v>1.31</v>
       </c>
-      <c r="Z50" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE50" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF50" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG50" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH50" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AI50" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6486,77 +6486,77 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2</v>
+        <v>1.53</v>
       </c>
       <c r="M51" t="n">
-        <v>3.25</v>
+        <v>3.95</v>
       </c>
       <c r="N51" t="n">
+        <v>5</v>
+      </c>
+      <c r="O51" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="P51" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="R51" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S51" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V51" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W51" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X51" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z51" t="n">
         <v>3.5</v>
       </c>
-      <c r="O51" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="P51" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>4.26</v>
-      </c>
-      <c r="R51" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S51" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="T51" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="U51" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V51" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W51" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X51" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>2.92</v>
-      </c>
       <c r="AA51" t="n">
-        <v>2.07</v>
+        <v>1.78</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.72</v>
+        <v>1.93</v>
       </c>
       <c r="AC51" t="n">
-        <v>3.67</v>
+        <v>3</v>
       </c>
       <c r="AD51" t="n">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="AG51" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AH51" t="n">
-        <v>1.62</v>
+        <v>2.31</v>
       </c>
       <c r="AI51" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,73 +6609,73 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="M52" t="n">
-        <v>4.3</v>
+        <v>3.45</v>
       </c>
       <c r="N52" t="n">
-        <v>5.53</v>
+        <v>3.86</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S52" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="T52" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U52" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V52" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="W52" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="AB52" t="n">
-        <v>2.1</v>
+        <v>1.81</v>
       </c>
       <c r="AC52" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD52" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AG52" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH52" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI52" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6724,77 +6724,77 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L53" t="n">
         <v>2.45</v>
       </c>
       <c r="M53" t="n">
-        <v>3</v>
+        <v>3.47</v>
       </c>
       <c r="N53" t="n">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="O53" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="U53" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V53" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W53" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X53" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="AD53" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG53" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH53" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AI53" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,73 +6847,73 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="M54" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="N54" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="O54" t="n">
-        <v>2.46</v>
+        <v>2.62</v>
       </c>
       <c r="P54" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="Q54" t="n">
-        <v>4.25</v>
+        <v>4.26</v>
       </c>
       <c r="R54" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="S54" t="n">
         <v>2.87</v>
       </c>
       <c r="T54" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="U54" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V54" t="n">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
       <c r="W54" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X54" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="Z54" t="n">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="AA54" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AC54" t="n">
-        <v>3.52</v>
+        <v>3.67</v>
       </c>
       <c r="AD54" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.86</v>
+        <v>1.96</v>
       </c>
       <c r="AG54" t="n">
         <v>1.27</v>
       </c>
       <c r="AH54" t="n">
-        <v>1.88</v>
+        <v>1.62</v>
       </c>
       <c r="AI54" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6962,7 +6962,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7081,29 +7081,29 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.91</v>
+        <v>2.45</v>
       </c>
       <c r="M56" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="N56" t="n">
-        <v>3.86</v>
+        <v>2.72</v>
       </c>
       <c r="O56" t="n">
-        <v>2.55</v>
+        <v>3.1</v>
       </c>
       <c r="P56" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="Q56" t="n">
-        <v>4.25</v>
+        <v>3.5</v>
       </c>
       <c r="R56" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S56" t="n">
         <v>2.69</v>
@@ -7112,46 +7112,46 @@
         <v>2.65</v>
       </c>
       <c r="U56" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="V56" t="n">
-        <v>7.4</v>
+        <v>6.95</v>
       </c>
       <c r="W56" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X56" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y56" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG56" t="n">
         <v>1.33</v>
       </c>
-      <c r="Z56" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AC56" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AD56" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE56" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF56" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AG56" t="n">
-        <v>1.34</v>
-      </c>
       <c r="AH56" t="n">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="AI56" s="3" t="n">
         <v>46084.69791666666</v>
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,73 +7204,73 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.45</v>
+        <v>1.8</v>
       </c>
       <c r="M57" t="n">
-        <v>3.4</v>
+        <v>3.26</v>
       </c>
       <c r="N57" t="n">
-        <v>2.88</v>
+        <v>4</v>
       </c>
       <c r="O57" t="n">
-        <v>2.96</v>
+        <v>2.46</v>
       </c>
       <c r="P57" t="n">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.67</v>
+        <v>4.25</v>
       </c>
       <c r="R57" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S57" t="n">
-        <v>2.77</v>
+        <v>2.87</v>
       </c>
       <c r="T57" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="U57" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="V57" t="n">
-        <v>6.75</v>
+        <v>7.5</v>
       </c>
       <c r="W57" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X57" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="Z57" t="n">
-        <v>3.6</v>
+        <v>3.05</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AB57" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE57" t="n">
         <v>1.85</v>
       </c>
-      <c r="AC57" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AD57" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AE57" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AF57" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AG57" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AH57" t="n">
-        <v>1.52</v>
+        <v>1.88</v>
       </c>
       <c r="AI57" s="3" t="n">
         <v>46084.69791666666</v>

--- a/jogos_2026-03-03.xlsx
+++ b/jogos_2026-03-03.xlsx
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.5</v>
+        <v>1.81</v>
       </c>
       <c r="M8" t="n">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="N8" t="n">
-        <v>2.8</v>
+        <v>4.55</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>5.78</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46084.45833333334</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.81</v>
+        <v>2.5</v>
       </c>
       <c r="M9" t="n">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="N9" t="n">
-        <v>4.55</v>
+        <v>2.8</v>
       </c>
       <c r="O9" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.78</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46084.45833333334</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3273,17 +3273,17 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.65</v>
+        <v>1.4</v>
       </c>
       <c r="M29" t="n">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="N29" t="n">
-        <v>2.65</v>
+        <v>7.03</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.4</v>
+        <v>3.72</v>
       </c>
       <c r="M30" t="n">
-        <v>4.6</v>
+        <v>3.15</v>
       </c>
       <c r="N30" t="n">
-        <v>7.03</v>
+        <v>2.05</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.47</v>
+        <v>2.65</v>
       </c>
       <c r="M31" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N31" t="n">
-        <v>2.11</v>
+        <v>2.65</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.72</v>
+        <v>3.47</v>
       </c>
       <c r="M33" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="N33" t="n">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4463,77 +4463,77 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46084.6875</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4582,77 +4582,77 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.45</v>
+        <v>2.05</v>
       </c>
       <c r="M35" t="n">
-        <v>3.3</v>
+        <v>3.56</v>
       </c>
       <c r="N35" t="n">
-        <v>2.43</v>
+        <v>4.05</v>
       </c>
       <c r="O35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.67</v>
+        <v>2.15</v>
       </c>
       <c r="AB35" t="n">
-        <v>2.1</v>
+        <v>1.63</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46084.6875</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.49</v>
+        <v>1.75</v>
       </c>
       <c r="M36" t="n">
-        <v>3.8</v>
+        <v>3.91</v>
       </c>
       <c r="N36" t="n">
-        <v>2.86</v>
+        <v>5.33</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="AB36" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>5.33</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5772,77 +5772,77 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46084.69791666666</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5898,70 +5898,70 @@
         <v>1.53</v>
       </c>
       <c r="M46" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="N46" t="n">
-        <v>5.53</v>
+        <v>5</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="AB46" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH46" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AI46" s="3" t="n">
         <v>46084.69791666666</v>
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,73 +6014,73 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.1</v>
+        <v>2.85</v>
       </c>
       <c r="M47" t="n">
-        <v>3.38</v>
+        <v>3.1</v>
       </c>
       <c r="N47" t="n">
-        <v>3.08</v>
+        <v>2.24</v>
       </c>
       <c r="O47" t="n">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="P47" t="n">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="R47" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="S47" t="n">
-        <v>2.81</v>
+        <v>2.77</v>
       </c>
       <c r="T47" t="n">
-        <v>2.75</v>
+        <v>3.04</v>
       </c>
       <c r="U47" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V47" t="n">
-        <v>6.5</v>
+        <v>7.6</v>
       </c>
       <c r="W47" t="n">
         <v>1.03</v>
       </c>
       <c r="X47" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y47" t="n">
         <v>1.3</v>
       </c>
       <c r="Z47" t="n">
-        <v>3.24</v>
+        <v>3.14</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.03</v>
+        <v>2.19</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AC47" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="AD47" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AG47" t="n">
         <v>1.29</v>
       </c>
-      <c r="AE47" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF47" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG47" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AH47" t="n">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="AI47" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,73 +6133,73 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.85</v>
+        <v>2.1</v>
       </c>
       <c r="M48" t="n">
-        <v>3.1</v>
+        <v>3.38</v>
       </c>
       <c r="N48" t="n">
-        <v>2.24</v>
+        <v>3.08</v>
       </c>
       <c r="O48" t="n">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="P48" t="n">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="R48" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="S48" t="n">
-        <v>2.77</v>
+        <v>2.81</v>
       </c>
       <c r="T48" t="n">
-        <v>3.04</v>
+        <v>2.75</v>
       </c>
       <c r="U48" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V48" t="n">
-        <v>7.6</v>
+        <v>6.5</v>
       </c>
       <c r="W48" t="n">
         <v>1.03</v>
       </c>
       <c r="X48" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y48" t="n">
         <v>1.3</v>
       </c>
       <c r="Z48" t="n">
-        <v>3.14</v>
+        <v>3.24</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.19</v>
+        <v>2.03</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AC48" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AG48" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="AI48" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6248,77 +6248,77 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L49" t="n">
         <v>2.45</v>
       </c>
       <c r="M49" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="N49" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="O49" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="P49" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="R49" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="S49" t="n">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="T49" t="n">
-        <v>2.96</v>
+        <v>2.65</v>
       </c>
       <c r="U49" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="V49" t="n">
-        <v>8</v>
+        <v>6.95</v>
       </c>
       <c r="W49" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X49" t="n">
         <v>1.06</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="Z49" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AA49" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AC49" t="n">
-        <v>3.48</v>
+        <v>3.2</v>
       </c>
       <c r="AD49" t="n">
         <v>1.29</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AF49" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AG49" t="n">
         <v>1.33</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AI49" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,73 +6371,73 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.45</v>
+        <v>1.91</v>
       </c>
       <c r="M50" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="N50" t="n">
-        <v>2.88</v>
+        <v>3.86</v>
       </c>
       <c r="O50" t="n">
-        <v>2.96</v>
+        <v>2.55</v>
       </c>
       <c r="P50" t="n">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.67</v>
+        <v>4.25</v>
       </c>
       <c r="R50" t="n">
         <v>1.38</v>
       </c>
       <c r="S50" t="n">
-        <v>2.77</v>
+        <v>2.69</v>
       </c>
       <c r="T50" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="U50" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="V50" t="n">
-        <v>6.75</v>
+        <v>7.4</v>
       </c>
       <c r="W50" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X50" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="Z50" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AC50" t="n">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AF50" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AG50" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AH50" t="n">
-        <v>1.52</v>
+        <v>1.73</v>
       </c>
       <c r="AI50" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,73 +6490,73 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="M51" t="n">
-        <v>3.95</v>
+        <v>3.26</v>
       </c>
       <c r="N51" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O51" t="n">
-        <v>2.06</v>
+        <v>2.46</v>
       </c>
       <c r="P51" t="n">
-        <v>2.35</v>
+        <v>2.09</v>
       </c>
       <c r="Q51" t="n">
-        <v>5.65</v>
+        <v>4.25</v>
       </c>
       <c r="R51" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="S51" t="n">
-        <v>2.91</v>
+        <v>2.87</v>
       </c>
       <c r="T51" t="n">
-        <v>2.48</v>
+        <v>2.9</v>
       </c>
       <c r="U51" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="V51" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="W51" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="X51" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y51" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AD51" t="n">
         <v>1.24</v>
       </c>
-      <c r="Z51" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AE51" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AG51" t="n">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="AH51" t="n">
-        <v>2.31</v>
+        <v>1.88</v>
       </c>
       <c r="AI51" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,73 +6609,73 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U52" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V52" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="W52" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z52" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD52" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AG52" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI52" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6724,77 +6724,77 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="M53" t="n">
-        <v>3.47</v>
+        <v>3.25</v>
       </c>
       <c r="N53" t="n">
-        <v>2.59</v>
+        <v>3.5</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V53" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="W53" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="AD53" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG53" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH53" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI53" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6843,77 +6843,77 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2</v>
+        <v>1.53</v>
       </c>
       <c r="M54" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="N54" t="n">
-        <v>3.5</v>
+        <v>5.53</v>
       </c>
       <c r="O54" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>4.26</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="U54" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V54" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="W54" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X54" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z54" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>2.07</v>
+        <v>1.65</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.72</v>
+        <v>2.1</v>
       </c>
       <c r="AC54" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="AD54" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG54" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH54" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI54" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6962,77 +6962,77 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>3.2</v>
+        <v>2.45</v>
       </c>
       <c r="M55" t="n">
-        <v>3.24</v>
+        <v>3.47</v>
       </c>
       <c r="N55" t="n">
-        <v>2.21</v>
+        <v>2.59</v>
       </c>
       <c r="O55" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="U55" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V55" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W55" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X55" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z55" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD55" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF55" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AG55" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AI55" s="3" t="n">
         <v>46084.69791666666</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7088,70 +7088,70 @@
         <v>2.45</v>
       </c>
       <c r="M56" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="N56" t="n">
-        <v>2.72</v>
+        <v>2.88</v>
       </c>
       <c r="O56" t="n">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="P56" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.5</v>
+        <v>3.67</v>
       </c>
       <c r="R56" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S56" t="n">
-        <v>2.69</v>
+        <v>2.77</v>
       </c>
       <c r="T56" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="U56" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="V56" t="n">
-        <v>6.95</v>
+        <v>6.75</v>
       </c>
       <c r="W56" t="n">
         <v>1.04</v>
       </c>
       <c r="X56" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y56" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG56" t="n">
         <v>1.31</v>
       </c>
-      <c r="Z56" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC56" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD56" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE56" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF56" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG56" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH56" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AI56" s="3" t="n">
         <v>46084.69791666666</v>
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7200,77 +7200,77 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.8</v>
+        <v>3.2</v>
       </c>
       <c r="M57" t="n">
-        <v>3.26</v>
+        <v>3.24</v>
       </c>
       <c r="N57" t="n">
-        <v>4</v>
+        <v>2.21</v>
       </c>
       <c r="O57" t="n">
-        <v>2.46</v>
+        <v>3.92</v>
       </c>
       <c r="P57" t="n">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="Q57" t="n">
-        <v>4.25</v>
+        <v>2.8</v>
       </c>
       <c r="R57" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S57" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="U57" t="n">
         <v>1.39</v>
       </c>
-      <c r="S57" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="T57" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U57" t="n">
-        <v>1.36</v>
-      </c>
       <c r="V57" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="W57" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X57" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="Z57" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="AA57" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="AC57" t="n">
-        <v>3.52</v>
+        <v>3.3</v>
       </c>
       <c r="AD57" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AF57" t="n">
-        <v>1.86</v>
+        <v>2.02</v>
       </c>
       <c r="AG57" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AH57" t="n">
-        <v>1.88</v>
+        <v>1.31</v>
       </c>
       <c r="AI57" s="3" t="n">
         <v>46084.69791666666</v>
@@ -7406,22 +7406,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L59" t="n">
@@ -7644,22 +7644,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L61" t="n">

--- a/jogos_2026-03-03.xlsx
+++ b/jogos_2026-03-03.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.8</v>
+        <v>4.5</v>
       </c>
       <c r="M26" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N26" t="n">
-        <v>2.5</v>
+        <v>1.62</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="M29" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N29" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="O29" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="V29" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE29" t="n">
         <v>1.4</v>
       </c>
-      <c r="M29" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="N29" t="n">
-        <v>7.03</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" t="n">
-        <v>0</v>
-      </c>
-      <c r="W29" t="n">
-        <v>0</v>
-      </c>
-      <c r="X29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>0</v>
-      </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46084.66666666666</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.72</v>
+        <v>3.47</v>
       </c>
       <c r="M30" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="N30" t="n">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.65</v>
+        <v>3.72</v>
       </c>
       <c r="M31" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="N31" t="n">
-        <v>2.65</v>
+        <v>2.05</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.87</v>
+        <v>2.65</v>
       </c>
       <c r="M32" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="N32" t="n">
-        <v>2.98</v>
+        <v>2.65</v>
       </c>
       <c r="O32" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46084.66666666666</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.47</v>
+        <v>1.4</v>
       </c>
       <c r="M33" t="n">
-        <v>3.2</v>
+        <v>4.6</v>
       </c>
       <c r="N33" t="n">
-        <v>2.11</v>
+        <v>7.03</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4463,77 +4463,77 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46084.6875</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4701,77 +4701,77 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.75</v>
+        <v>2.45</v>
       </c>
       <c r="M36" t="n">
-        <v>3.91</v>
+        <v>3.3</v>
       </c>
       <c r="N36" t="n">
-        <v>5.33</v>
+        <v>2.43</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46084.6875</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.49</v>
+        <v>2.05</v>
       </c>
       <c r="M39" t="n">
-        <v>3.8</v>
+        <v>3.56</v>
       </c>
       <c r="N39" t="n">
-        <v>2.86</v>
+        <v>4.05</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.68</v>
+        <v>2.15</v>
       </c>
       <c r="AB39" t="n">
-        <v>2.05</v>
+        <v>1.63</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>4.28</v>
+        <v>1.75</v>
       </c>
       <c r="M40" t="n">
-        <v>4.2</v>
+        <v>3.91</v>
       </c>
       <c r="N40" t="n">
-        <v>1.66</v>
+        <v>5.33</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5772,77 +5772,77 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.45</v>
+        <v>1.91</v>
       </c>
       <c r="M45" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="N45" t="n">
-        <v>2.7</v>
+        <v>3.86</v>
       </c>
       <c r="O45" t="n">
-        <v>2.95</v>
+        <v>2.55</v>
       </c>
       <c r="P45" t="n">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.42</v>
+        <v>4.25</v>
       </c>
       <c r="R45" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="S45" t="n">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="T45" t="n">
-        <v>2.96</v>
+        <v>2.65</v>
       </c>
       <c r="U45" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="V45" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="W45" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X45" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="Z45" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="AA45" t="n">
         <v>2</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="AC45" t="n">
-        <v>3.48</v>
+        <v>3.34</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AF45" t="n">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.48</v>
+        <v>1.73</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46084.69791666666</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5891,77 +5891,77 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.53</v>
+        <v>2.45</v>
       </c>
       <c r="M46" t="n">
-        <v>3.95</v>
+        <v>3</v>
       </c>
       <c r="N46" t="n">
-        <v>5</v>
+        <v>2.7</v>
       </c>
       <c r="O46" t="n">
-        <v>2.06</v>
+        <v>2.95</v>
       </c>
       <c r="P46" t="n">
-        <v>2.35</v>
+        <v>2.05</v>
       </c>
       <c r="Q46" t="n">
-        <v>5.65</v>
+        <v>3.42</v>
       </c>
       <c r="R46" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="S46" t="n">
-        <v>2.91</v>
+        <v>2.62</v>
       </c>
       <c r="T46" t="n">
-        <v>2.48</v>
+        <v>2.96</v>
       </c>
       <c r="U46" t="n">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="V46" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="W46" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X46" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z46" t="n">
         <v>3.5</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.93</v>
+        <v>1.71</v>
       </c>
       <c r="AC46" t="n">
-        <v>3</v>
+        <v>3.48</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.84</v>
+        <v>1.67</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AH46" t="n">
-        <v>2.31</v>
+        <v>1.48</v>
       </c>
       <c r="AI46" s="3" t="n">
         <v>46084.69791666666</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6010,77 +6010,77 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.85</v>
+        <v>1.53</v>
       </c>
       <c r="M47" t="n">
-        <v>3.1</v>
+        <v>4.3</v>
       </c>
       <c r="N47" t="n">
-        <v>2.24</v>
+        <v>5.53</v>
       </c>
       <c r="O47" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.19</v>
+        <v>1.65</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.71</v>
+        <v>2.1</v>
       </c>
       <c r="AC47" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AI47" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6129,77 +6129,77 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X48" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG48" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI48" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6255,70 +6255,70 @@
         <v>2.45</v>
       </c>
       <c r="M49" t="n">
-        <v>3.2</v>
+        <v>3.47</v>
       </c>
       <c r="N49" t="n">
-        <v>2.72</v>
+        <v>2.59</v>
       </c>
       <c r="O49" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U49" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="V49" t="n">
-        <v>6.95</v>
+        <v>0</v>
       </c>
       <c r="W49" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X49" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z49" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF49" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG49" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI49" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6367,77 +6367,77 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="M50" t="n">
-        <v>3.45</v>
+        <v>3.38</v>
       </c>
       <c r="N50" t="n">
-        <v>3.86</v>
+        <v>3.08</v>
       </c>
       <c r="O50" t="n">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="P50" t="n">
-        <v>2.11</v>
+        <v>2.19</v>
       </c>
       <c r="Q50" t="n">
-        <v>4.25</v>
+        <v>3.5</v>
       </c>
       <c r="R50" t="n">
         <v>1.38</v>
       </c>
       <c r="S50" t="n">
-        <v>2.69</v>
+        <v>2.81</v>
       </c>
       <c r="T50" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="U50" t="n">
         <v>1.36</v>
       </c>
       <c r="V50" t="n">
-        <v>7.4</v>
+        <v>6.5</v>
       </c>
       <c r="W50" t="n">
         <v>1.03</v>
       </c>
       <c r="X50" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z50" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="AA50" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="AC50" t="n">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="AD50" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG50" t="n">
         <v>1.24</v>
       </c>
-      <c r="AE50" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF50" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AG50" t="n">
-        <v>1.34</v>
-      </c>
       <c r="AH50" t="n">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="AI50" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,73 +6490,73 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.8</v>
+        <v>2.45</v>
       </c>
       <c r="M51" t="n">
-        <v>3.26</v>
+        <v>3.4</v>
       </c>
       <c r="N51" t="n">
-        <v>4</v>
+        <v>2.88</v>
       </c>
       <c r="O51" t="n">
-        <v>2.46</v>
+        <v>2.96</v>
       </c>
       <c r="P51" t="n">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="Q51" t="n">
-        <v>4.25</v>
+        <v>3.67</v>
       </c>
       <c r="R51" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S51" t="n">
-        <v>2.87</v>
+        <v>2.77</v>
       </c>
       <c r="T51" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="U51" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="V51" t="n">
-        <v>7.5</v>
+        <v>6.75</v>
       </c>
       <c r="W51" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X51" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="Z51" t="n">
-        <v>3.05</v>
+        <v>3.6</v>
       </c>
       <c r="AA51" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF51" t="n">
         <v>2</v>
       </c>
-      <c r="AB51" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE51" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF51" t="n">
-        <v>1.86</v>
-      </c>
       <c r="AG51" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AH51" t="n">
-        <v>1.88</v>
+        <v>1.52</v>
       </c>
       <c r="AI51" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,73 +6609,73 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S52" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="T52" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U52" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V52" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W52" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC52" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AD52" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG52" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH52" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AI52" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,73 +6728,73 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2</v>
+        <v>2.85</v>
       </c>
       <c r="M53" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="N53" t="n">
-        <v>3.5</v>
+        <v>2.24</v>
       </c>
       <c r="O53" t="n">
-        <v>2.62</v>
+        <v>3.7</v>
       </c>
       <c r="P53" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="Q53" t="n">
-        <v>4.26</v>
+        <v>3.1</v>
       </c>
       <c r="R53" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="S53" t="n">
-        <v>2.87</v>
+        <v>2.77</v>
       </c>
       <c r="T53" t="n">
-        <v>2.91</v>
+        <v>3.04</v>
       </c>
       <c r="U53" t="n">
         <v>1.33</v>
       </c>
       <c r="V53" t="n">
-        <v>7.1</v>
+        <v>7.6</v>
       </c>
       <c r="W53" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X53" t="n">
         <v>1.02</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="Z53" t="n">
-        <v>2.92</v>
+        <v>3.14</v>
       </c>
       <c r="AA53" t="n">
-        <v>2.07</v>
+        <v>2.19</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AC53" t="n">
-        <v>3.67</v>
+        <v>3.55</v>
       </c>
       <c r="AD53" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AE53" t="n">
         <v>1.81</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="AG53" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AH53" t="n">
-        <v>1.62</v>
+        <v>1.38</v>
       </c>
       <c r="AI53" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,73 +6847,73 @@
         </is>
       </c>
       <c r="L54" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="M54" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N54" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="O54" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P54" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R54" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S54" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V54" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="W54" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X54" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH54" t="n">
         <v>1.53</v>
-      </c>
-      <c r="M54" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="N54" t="n">
-        <v>5.53</v>
-      </c>
-      <c r="O54" t="n">
-        <v>0</v>
-      </c>
-      <c r="P54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
-      <c r="R54" t="n">
-        <v>0</v>
-      </c>
-      <c r="S54" t="n">
-        <v>0</v>
-      </c>
-      <c r="T54" t="n">
-        <v>0</v>
-      </c>
-      <c r="U54" t="n">
-        <v>0</v>
-      </c>
-      <c r="V54" t="n">
-        <v>0</v>
-      </c>
-      <c r="W54" t="n">
-        <v>0</v>
-      </c>
-      <c r="X54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB54" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH54" t="n">
-        <v>0</v>
       </c>
       <c r="AI54" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6962,77 +6962,77 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.45</v>
+        <v>3.2</v>
       </c>
       <c r="M55" t="n">
-        <v>3.47</v>
+        <v>3.24</v>
       </c>
       <c r="N55" t="n">
-        <v>2.59</v>
+        <v>2.21</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S55" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T55" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U55" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V55" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W55" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X55" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC55" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD55" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AG55" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH55" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AI55" s="3" t="n">
         <v>46084.69791666666</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7081,77 +7081,77 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="M56" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="N56" t="n">
-        <v>2.88</v>
+        <v>3.5</v>
       </c>
       <c r="O56" t="n">
-        <v>2.96</v>
+        <v>2.62</v>
       </c>
       <c r="P56" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q56" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="R56" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S56" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V56" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W56" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X56" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC56" t="n">
         <v>3.67</v>
       </c>
-      <c r="R56" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S56" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T56" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U56" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V56" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="W56" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X56" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z56" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC56" t="n">
-        <v>3.35</v>
-      </c>
       <c r="AD56" t="n">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="AE56" t="n">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="AF56" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AG56" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AH56" t="n">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="AI56" s="3" t="n">
         <v>46084.69791666666</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7200,77 +7200,77 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>3.2</v>
+        <v>1.53</v>
       </c>
       <c r="M57" t="n">
-        <v>3.24</v>
+        <v>3.95</v>
       </c>
       <c r="N57" t="n">
-        <v>2.21</v>
+        <v>5</v>
       </c>
       <c r="O57" t="n">
-        <v>3.92</v>
+        <v>2.06</v>
       </c>
       <c r="P57" t="n">
-        <v>2.05</v>
+        <v>2.35</v>
       </c>
       <c r="Q57" t="n">
-        <v>2.8</v>
+        <v>5.65</v>
       </c>
       <c r="R57" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="S57" t="n">
-        <v>2.77</v>
+        <v>2.91</v>
       </c>
       <c r="T57" t="n">
-        <v>2.73</v>
+        <v>2.48</v>
       </c>
       <c r="U57" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="V57" t="n">
         <v>6.5</v>
       </c>
       <c r="W57" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="X57" t="n">
         <v>1.01</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="Z57" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AC57" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="AD57" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.7</v>
+        <v>1.84</v>
       </c>
       <c r="AF57" t="n">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="AG57" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AH57" t="n">
-        <v>1.31</v>
+        <v>2.31</v>
       </c>
       <c r="AI57" s="3" t="n">
         <v>46084.69791666666</v>
@@ -7406,22 +7406,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L59" t="n">
@@ -7525,22 +7525,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7557,7 +7557,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L60" t="n">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G61" t="n">

--- a/jogos_2026-03-03.xlsx
+++ b/jogos_2026-03-03.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.87</v>
+        <v>1.4</v>
       </c>
       <c r="M29" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="N29" t="n">
-        <v>2.98</v>
+        <v>7.03</v>
       </c>
       <c r="O29" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46084.66666666666</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.47</v>
+        <v>1.87</v>
       </c>
       <c r="M30" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="N30" t="n">
-        <v>2.11</v>
+        <v>2.98</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46084.66666666666</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.72</v>
+        <v>3.47</v>
       </c>
       <c r="M31" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="N31" t="n">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.65</v>
+        <v>3.72</v>
       </c>
       <c r="M32" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="N32" t="n">
-        <v>2.65</v>
+        <v>2.05</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.4</v>
+        <v>2.65</v>
       </c>
       <c r="M33" t="n">
-        <v>4.6</v>
+        <v>3.1</v>
       </c>
       <c r="N33" t="n">
-        <v>7.03</v>
+        <v>2.65</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4701,77 +4701,77 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46084.6875</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="M39" t="n">
-        <v>3.56</v>
+        <v>3.91</v>
       </c>
       <c r="N39" t="n">
-        <v>4.05</v>
+        <v>5.33</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.63</v>
+        <v>1.85</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.75</v>
+        <v>4.28</v>
       </c>
       <c r="M40" t="n">
-        <v>3.91</v>
+        <v>4.2</v>
       </c>
       <c r="N40" t="n">
-        <v>5.33</v>
+        <v>1.66</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5296,77 +5296,77 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.49</v>
+        <v>2.45</v>
       </c>
       <c r="M41" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="N41" t="n">
-        <v>2.86</v>
+        <v>2.43</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AB41" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46084.6875</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5772,77 +5772,77 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.91</v>
+        <v>3.2</v>
       </c>
       <c r="M45" t="n">
-        <v>3.45</v>
+        <v>3.24</v>
       </c>
       <c r="N45" t="n">
-        <v>3.86</v>
+        <v>2.21</v>
       </c>
       <c r="O45" t="n">
-        <v>2.55</v>
+        <v>3.92</v>
       </c>
       <c r="P45" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="Q45" t="n">
-        <v>4.25</v>
+        <v>2.8</v>
       </c>
       <c r="R45" t="n">
         <v>1.38</v>
       </c>
       <c r="S45" t="n">
-        <v>2.69</v>
+        <v>2.77</v>
       </c>
       <c r="T45" t="n">
-        <v>2.65</v>
+        <v>2.73</v>
       </c>
       <c r="U45" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="V45" t="n">
-        <v>7.4</v>
+        <v>6.5</v>
       </c>
       <c r="W45" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X45" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y45" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD45" t="n">
         <v>1.33</v>
       </c>
-      <c r="Z45" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AE45" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.73</v>
+        <v>1.31</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46084.69791666666</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5891,77 +5891,77 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.45</v>
+        <v>1.53</v>
       </c>
       <c r="M46" t="n">
-        <v>3</v>
+        <v>3.95</v>
       </c>
       <c r="N46" t="n">
-        <v>2.7</v>
+        <v>5</v>
       </c>
       <c r="O46" t="n">
-        <v>2.95</v>
+        <v>2.06</v>
       </c>
       <c r="P46" t="n">
-        <v>2.05</v>
+        <v>2.35</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.42</v>
+        <v>5.65</v>
       </c>
       <c r="R46" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="S46" t="n">
-        <v>2.62</v>
+        <v>2.91</v>
       </c>
       <c r="T46" t="n">
-        <v>2.96</v>
+        <v>2.48</v>
       </c>
       <c r="U46" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="V46" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="W46" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X46" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z46" t="n">
         <v>3.5</v>
       </c>
       <c r="AA46" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.71</v>
+        <v>1.93</v>
       </c>
       <c r="AC46" t="n">
-        <v>3.48</v>
+        <v>3</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.67</v>
+        <v>1.84</v>
       </c>
       <c r="AF46" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.48</v>
+        <v>2.31</v>
       </c>
       <c r="AI46" s="3" t="n">
         <v>46084.69791666666</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6010,77 +6010,77 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.53</v>
+        <v>2.45</v>
       </c>
       <c r="M47" t="n">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="N47" t="n">
-        <v>5.53</v>
+        <v>2.7</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="AB47" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF47" t="n">
         <v>2.1</v>
       </c>
-      <c r="AC47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF47" t="n">
-        <v>0</v>
-      </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AI47" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,73 +6133,73 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH48" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AI48" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6248,77 +6248,77 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="M49" t="n">
-        <v>3.47</v>
+        <v>3.38</v>
       </c>
       <c r="N49" t="n">
-        <v>2.59</v>
+        <v>3.08</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH49" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI49" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,73 +6371,73 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.1</v>
+        <v>2.85</v>
       </c>
       <c r="M50" t="n">
-        <v>3.38</v>
+        <v>3.1</v>
       </c>
       <c r="N50" t="n">
-        <v>3.08</v>
+        <v>2.24</v>
       </c>
       <c r="O50" t="n">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="P50" t="n">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="R50" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="S50" t="n">
-        <v>2.81</v>
+        <v>2.77</v>
       </c>
       <c r="T50" t="n">
-        <v>2.75</v>
+        <v>3.04</v>
       </c>
       <c r="U50" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V50" t="n">
-        <v>6.5</v>
+        <v>7.6</v>
       </c>
       <c r="W50" t="n">
         <v>1.03</v>
       </c>
       <c r="X50" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y50" t="n">
         <v>1.3</v>
       </c>
       <c r="Z50" t="n">
-        <v>3.24</v>
+        <v>3.14</v>
       </c>
       <c r="AA50" t="n">
-        <v>2.03</v>
+        <v>2.19</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AC50" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="AD50" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AG50" t="n">
         <v>1.29</v>
       </c>
-      <c r="AE50" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF50" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG50" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AH50" t="n">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="AI50" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,73 +6609,73 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.8</v>
+        <v>2.45</v>
       </c>
       <c r="M52" t="n">
-        <v>3.26</v>
+        <v>3.2</v>
       </c>
       <c r="N52" t="n">
-        <v>4</v>
+        <v>2.72</v>
       </c>
       <c r="O52" t="n">
-        <v>2.46</v>
+        <v>3.1</v>
       </c>
       <c r="P52" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="Q52" t="n">
-        <v>4.25</v>
+        <v>3.5</v>
       </c>
       <c r="R52" t="n">
         <v>1.39</v>
       </c>
       <c r="S52" t="n">
-        <v>2.87</v>
+        <v>2.69</v>
       </c>
       <c r="T52" t="n">
-        <v>2.9</v>
+        <v>2.65</v>
       </c>
       <c r="U52" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="V52" t="n">
-        <v>7.5</v>
+        <v>6.95</v>
       </c>
       <c r="W52" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X52" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="Z52" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="AA52" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AC52" t="n">
-        <v>3.52</v>
+        <v>3.2</v>
       </c>
       <c r="AD52" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.86</v>
+        <v>2.05</v>
       </c>
       <c r="AG52" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.88</v>
+        <v>1.53</v>
       </c>
       <c r="AI52" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6724,77 +6724,77 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.85</v>
+        <v>1.91</v>
       </c>
       <c r="M53" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="N53" t="n">
-        <v>2.24</v>
+        <v>3.86</v>
       </c>
       <c r="O53" t="n">
-        <v>3.7</v>
+        <v>2.55</v>
       </c>
       <c r="P53" t="n">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.1</v>
+        <v>4.25</v>
       </c>
       <c r="R53" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="S53" t="n">
-        <v>2.77</v>
+        <v>2.69</v>
       </c>
       <c r="T53" t="n">
-        <v>3.04</v>
+        <v>2.65</v>
       </c>
       <c r="U53" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V53" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="W53" t="n">
         <v>1.03</v>
       </c>
       <c r="X53" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z53" t="n">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="AA53" t="n">
-        <v>2.19</v>
+        <v>2</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="AC53" t="n">
-        <v>3.55</v>
+        <v>3.34</v>
       </c>
       <c r="AD53" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.9</v>
+        <v>1.99</v>
       </c>
       <c r="AG53" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AH53" t="n">
-        <v>1.38</v>
+        <v>1.73</v>
       </c>
       <c r="AI53" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,73 +6847,73 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U54" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="V54" t="n">
-        <v>6.95</v>
+        <v>0</v>
       </c>
       <c r="W54" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X54" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z54" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AD54" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF54" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG54" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH54" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI54" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6962,77 +6962,77 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>3.2</v>
+        <v>1.53</v>
       </c>
       <c r="M55" t="n">
-        <v>3.24</v>
+        <v>4.3</v>
       </c>
       <c r="N55" t="n">
-        <v>2.21</v>
+        <v>5.53</v>
       </c>
       <c r="O55" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="U55" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V55" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W55" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X55" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z55" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.88</v>
+        <v>1.65</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AC55" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD55" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF55" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AG55" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AI55" s="3" t="n">
         <v>46084.69791666666</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,73 +7204,73 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.53</v>
+        <v>2.45</v>
       </c>
       <c r="M57" t="n">
-        <v>3.95</v>
+        <v>3.47</v>
       </c>
       <c r="N57" t="n">
-        <v>5</v>
+        <v>2.59</v>
       </c>
       <c r="O57" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="T57" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="U57" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="V57" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W57" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X57" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Z57" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC57" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD57" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF57" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG57" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AH57" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AI57" s="3" t="n">
         <v>46084.69791666666</v>
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7525,22 +7525,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7557,7 +7557,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L60" t="n">
@@ -7644,22 +7644,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L61" t="n">

--- a/jogos_2026-03-03.xlsx
+++ b/jogos_2026-03-03.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="M29" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N29" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="O29" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="V29" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE29" t="n">
         <v>1.4</v>
       </c>
-      <c r="M29" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="N29" t="n">
-        <v>7.03</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" t="n">
-        <v>0</v>
-      </c>
-      <c r="W29" t="n">
-        <v>0</v>
-      </c>
-      <c r="X29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>0</v>
-      </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46084.66666666666</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.87</v>
+        <v>1.4</v>
       </c>
       <c r="M30" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="N30" t="n">
-        <v>2.98</v>
+        <v>7.03</v>
       </c>
       <c r="O30" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46084.66666666666</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.47</v>
+        <v>2.65</v>
       </c>
       <c r="M31" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N31" t="n">
-        <v>2.11</v>
+        <v>2.65</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.65</v>
+        <v>3.47</v>
       </c>
       <c r="M33" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N33" t="n">
-        <v>2.65</v>
+        <v>2.11</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4463,77 +4463,77 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46084.6875</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5296,77 +5296,77 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46084.6875</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.05</v>
+        <v>4.28</v>
       </c>
       <c r="M43" t="n">
-        <v>3.56</v>
+        <v>4.2</v>
       </c>
       <c r="N43" t="n">
-        <v>4.05</v>
+        <v>1.66</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,73 +5776,73 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>3.2</v>
+        <v>2.45</v>
       </c>
       <c r="M45" t="n">
-        <v>3.24</v>
+        <v>3</v>
       </c>
       <c r="N45" t="n">
-        <v>2.21</v>
+        <v>2.7</v>
       </c>
       <c r="O45" t="n">
-        <v>3.92</v>
+        <v>2.95</v>
       </c>
       <c r="P45" t="n">
         <v>2.05</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.8</v>
+        <v>3.42</v>
       </c>
       <c r="R45" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="S45" t="n">
-        <v>2.77</v>
+        <v>2.62</v>
       </c>
       <c r="T45" t="n">
-        <v>2.73</v>
+        <v>2.96</v>
       </c>
       <c r="U45" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="V45" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="W45" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X45" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z45" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.95</v>
+        <v>1.71</v>
       </c>
       <c r="AC45" t="n">
-        <v>3.3</v>
+        <v>3.48</v>
       </c>
       <c r="AD45" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG45" t="n">
         <v>1.33</v>
       </c>
-      <c r="AE45" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AF45" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AG45" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH45" t="n">
-        <v>1.31</v>
+        <v>1.48</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46084.69791666666</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5891,77 +5891,77 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.53</v>
+        <v>2</v>
       </c>
       <c r="M46" t="n">
-        <v>3.95</v>
+        <v>3.25</v>
       </c>
       <c r="N46" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="O46" t="n">
-        <v>2.06</v>
+        <v>2.62</v>
       </c>
       <c r="P46" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="Q46" t="n">
-        <v>5.65</v>
+        <v>4.26</v>
       </c>
       <c r="R46" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S46" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="U46" t="n">
         <v>1.33</v>
       </c>
-      <c r="S46" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="T46" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="U46" t="n">
-        <v>1.41</v>
-      </c>
       <c r="V46" t="n">
-        <v>6.5</v>
+        <v>7.1</v>
       </c>
       <c r="W46" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X46" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.24</v>
+        <v>1.34</v>
       </c>
       <c r="Z46" t="n">
-        <v>3.5</v>
+        <v>2.92</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.78</v>
+        <v>2.07</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.93</v>
+        <v>1.72</v>
       </c>
       <c r="AC46" t="n">
-        <v>3</v>
+        <v>3.67</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="AH46" t="n">
-        <v>2.31</v>
+        <v>1.62</v>
       </c>
       <c r="AI46" s="3" t="n">
         <v>46084.69791666666</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6010,77 +6010,77 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L47" t="n">
         <v>2.45</v>
       </c>
       <c r="M47" t="n">
-        <v>3</v>
+        <v>3.47</v>
       </c>
       <c r="N47" t="n">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="O47" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AI47" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,73 +6133,73 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.8</v>
+        <v>2.45</v>
       </c>
       <c r="M48" t="n">
-        <v>3.26</v>
+        <v>3.4</v>
       </c>
       <c r="N48" t="n">
-        <v>4</v>
+        <v>2.88</v>
       </c>
       <c r="O48" t="n">
-        <v>2.46</v>
+        <v>2.96</v>
       </c>
       <c r="P48" t="n">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="Q48" t="n">
-        <v>4.25</v>
+        <v>3.67</v>
       </c>
       <c r="R48" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S48" t="n">
-        <v>2.87</v>
+        <v>2.77</v>
       </c>
       <c r="T48" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="U48" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="V48" t="n">
-        <v>7.5</v>
+        <v>6.75</v>
       </c>
       <c r="W48" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X48" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="Z48" t="n">
-        <v>3.05</v>
+        <v>3.6</v>
       </c>
       <c r="AA48" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF48" t="n">
         <v>2</v>
       </c>
-      <c r="AB48" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE48" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF48" t="n">
-        <v>1.86</v>
-      </c>
       <c r="AG48" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.88</v>
+        <v>1.52</v>
       </c>
       <c r="AI48" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6248,77 +6248,77 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="M49" t="n">
-        <v>3.38</v>
+        <v>3.45</v>
       </c>
       <c r="N49" t="n">
-        <v>3.08</v>
+        <v>3.86</v>
       </c>
       <c r="O49" t="n">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="P49" t="n">
-        <v>2.19</v>
+        <v>2.11</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.5</v>
+        <v>4.25</v>
       </c>
       <c r="R49" t="n">
         <v>1.38</v>
       </c>
       <c r="S49" t="n">
-        <v>2.81</v>
+        <v>2.69</v>
       </c>
       <c r="T49" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="U49" t="n">
         <v>1.36</v>
       </c>
       <c r="V49" t="n">
-        <v>6.5</v>
+        <v>7.4</v>
       </c>
       <c r="W49" t="n">
         <v>1.03</v>
       </c>
       <c r="X49" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z49" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AB49" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AH49" t="n">
         <v>1.73</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE49" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF49" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG49" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AH49" t="n">
-        <v>1.55</v>
       </c>
       <c r="AI49" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6367,77 +6367,77 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.85</v>
+        <v>1.8</v>
       </c>
       <c r="M50" t="n">
-        <v>3.1</v>
+        <v>3.26</v>
       </c>
       <c r="N50" t="n">
-        <v>2.24</v>
+        <v>4</v>
       </c>
       <c r="O50" t="n">
-        <v>3.7</v>
+        <v>2.46</v>
       </c>
       <c r="P50" t="n">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.1</v>
+        <v>4.25</v>
       </c>
       <c r="R50" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="S50" t="n">
-        <v>2.77</v>
+        <v>2.87</v>
       </c>
       <c r="T50" t="n">
-        <v>3.04</v>
+        <v>2.9</v>
       </c>
       <c r="U50" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V50" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="W50" t="n">
         <v>1.03</v>
       </c>
       <c r="X50" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="Z50" t="n">
-        <v>3.14</v>
+        <v>3.05</v>
       </c>
       <c r="AA50" t="n">
-        <v>2.19</v>
+        <v>2</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AC50" t="n">
-        <v>3.55</v>
+        <v>3.52</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AG50" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AH50" t="n">
-        <v>1.38</v>
+        <v>1.88</v>
       </c>
       <c r="AI50" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,73 +6490,73 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.45</v>
+        <v>1.53</v>
       </c>
       <c r="M51" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="N51" t="n">
-        <v>2.88</v>
+        <v>5.53</v>
       </c>
       <c r="O51" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U51" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V51" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="W51" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X51" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z51" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.93</v>
+        <v>1.65</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AC51" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AD51" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF51" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG51" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH51" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AI51" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6605,77 +6605,77 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="M52" t="n">
-        <v>3.2</v>
+        <v>3.38</v>
       </c>
       <c r="N52" t="n">
-        <v>2.72</v>
+        <v>3.08</v>
       </c>
       <c r="O52" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="P52" t="n">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="Q52" t="n">
         <v>3.5</v>
       </c>
       <c r="R52" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S52" t="n">
-        <v>2.69</v>
+        <v>2.81</v>
       </c>
       <c r="T52" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="U52" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="V52" t="n">
-        <v>6.95</v>
+        <v>6.5</v>
       </c>
       <c r="W52" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X52" t="n">
         <v>1.06</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z52" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC52" t="n">
         <v>3.3</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>3.2</v>
       </c>
       <c r="AD52" t="n">
         <v>1.29</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AF52" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AG52" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AI52" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6724,77 +6724,77 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.91</v>
+        <v>2.85</v>
       </c>
       <c r="M53" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="N53" t="n">
-        <v>3.86</v>
+        <v>2.24</v>
       </c>
       <c r="O53" t="n">
-        <v>2.55</v>
+        <v>3.7</v>
       </c>
       <c r="P53" t="n">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="Q53" t="n">
-        <v>4.25</v>
+        <v>3.1</v>
       </c>
       <c r="R53" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="S53" t="n">
-        <v>2.69</v>
+        <v>2.77</v>
       </c>
       <c r="T53" t="n">
-        <v>2.65</v>
+        <v>3.04</v>
       </c>
       <c r="U53" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V53" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="W53" t="n">
         <v>1.03</v>
       </c>
       <c r="X53" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z53" t="n">
-        <v>3.25</v>
+        <v>3.14</v>
       </c>
       <c r="AA53" t="n">
-        <v>2</v>
+        <v>2.19</v>
       </c>
       <c r="AB53" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE53" t="n">
         <v>1.81</v>
       </c>
-      <c r="AC53" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE53" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AF53" t="n">
-        <v>1.99</v>
+        <v>1.9</v>
       </c>
       <c r="AG53" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AH53" t="n">
-        <v>1.73</v>
+        <v>1.38</v>
       </c>
       <c r="AI53" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6843,77 +6843,77 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S54" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T54" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U54" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V54" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W54" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X54" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD54" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AG54" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH54" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AI54" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6969,70 +6969,70 @@
         <v>1.53</v>
       </c>
       <c r="M55" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="N55" t="n">
-        <v>5.53</v>
+        <v>5</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S55" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="T55" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U55" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V55" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W55" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X55" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="AB55" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AC55" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD55" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG55" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH55" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AI55" s="3" t="n">
         <v>46084.69791666666</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7081,77 +7081,77 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>4.26</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="U56" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V56" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="W56" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X56" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z56" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC56" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="AD56" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF56" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG56" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH56" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI56" s="3" t="n">
         <v>46084.69791666666</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7207,70 +7207,70 @@
         <v>2.45</v>
       </c>
       <c r="M57" t="n">
-        <v>3.47</v>
+        <v>3.2</v>
       </c>
       <c r="N57" t="n">
-        <v>2.59</v>
+        <v>2.72</v>
       </c>
       <c r="O57" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S57" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="T57" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U57" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V57" t="n">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="W57" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X57" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y57" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z57" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC57" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD57" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE57" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF57" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG57" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH57" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI57" s="3" t="n">
         <v>46084.69791666666</v>
@@ -7525,22 +7525,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7557,7 +7557,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L60" t="n">
@@ -7644,22 +7644,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L61" t="n">

--- a/jogos_2026-03-03.xlsx
+++ b/jogos_2026-03-03.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.87</v>
+        <v>3.47</v>
       </c>
       <c r="M29" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="N29" t="n">
-        <v>2.98</v>
+        <v>2.11</v>
       </c>
       <c r="O29" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46084.66666666666</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.4</v>
+        <v>3.72</v>
       </c>
       <c r="M30" t="n">
-        <v>4.6</v>
+        <v>3.15</v>
       </c>
       <c r="N30" t="n">
-        <v>7.03</v>
+        <v>2.05</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.65</v>
+        <v>1.87</v>
       </c>
       <c r="M31" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="N31" t="n">
-        <v>2.65</v>
+        <v>2.98</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46084.66666666666</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.72</v>
+        <v>1.4</v>
       </c>
       <c r="M32" t="n">
-        <v>3.15</v>
+        <v>4.6</v>
       </c>
       <c r="N32" t="n">
-        <v>2.05</v>
+        <v>7.03</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.47</v>
+        <v>2.65</v>
       </c>
       <c r="M33" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N33" t="n">
-        <v>2.11</v>
+        <v>2.65</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4463,77 +4463,77 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.45</v>
+        <v>2.05</v>
       </c>
       <c r="M34" t="n">
-        <v>3.3</v>
+        <v>3.56</v>
       </c>
       <c r="N34" t="n">
-        <v>2.43</v>
+        <v>4.05</v>
       </c>
       <c r="O34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.67</v>
+        <v>2.15</v>
       </c>
       <c r="AB34" t="n">
-        <v>2.1</v>
+        <v>1.63</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46084.6875</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,55 +4824,55 @@
         </is>
       </c>
       <c r="L37" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="M37" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N37" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AB37" t="n">
         <v>2.05</v>
-      </c>
-      <c r="M37" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="N37" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
-      <c r="R37" t="n">
-        <v>0</v>
-      </c>
-      <c r="S37" t="n">
-        <v>0</v>
-      </c>
-      <c r="T37" t="n">
-        <v>0</v>
-      </c>
-      <c r="U37" t="n">
-        <v>0</v>
-      </c>
-      <c r="V37" t="n">
-        <v>0</v>
-      </c>
-      <c r="W37" t="n">
-        <v>0</v>
-      </c>
-      <c r="X37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.63</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>5.33</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5534,77 +5534,77 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>4.28</v>
+        <v>2.45</v>
       </c>
       <c r="M43" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="N43" t="n">
-        <v>1.66</v>
+        <v>2.43</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>46084.6875</v>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5772,77 +5772,77 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L45" t="n">
         <v>2.45</v>
       </c>
       <c r="M45" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="N45" t="n">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="O45" t="n">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="P45" t="n">
         <v>2.05</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.42</v>
+        <v>3.67</v>
       </c>
       <c r="R45" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="S45" t="n">
-        <v>2.62</v>
+        <v>2.77</v>
       </c>
       <c r="T45" t="n">
-        <v>2.96</v>
+        <v>2.75</v>
       </c>
       <c r="U45" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V45" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AD45" t="n">
         <v>1.32</v>
       </c>
-      <c r="V45" t="n">
-        <v>8</v>
-      </c>
-      <c r="W45" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X45" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA45" t="n">
+      <c r="AE45" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF45" t="n">
         <v>2</v>
       </c>
-      <c r="AB45" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE45" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF45" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AG45" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46084.69791666666</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,73 +5895,73 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="M46" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="N46" t="n">
-        <v>3.5</v>
+        <v>2.21</v>
       </c>
       <c r="O46" t="n">
-        <v>2.62</v>
+        <v>3.92</v>
       </c>
       <c r="P46" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q46" t="n">
-        <v>4.26</v>
+        <v>2.8</v>
       </c>
       <c r="R46" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="S46" t="n">
-        <v>2.87</v>
+        <v>2.77</v>
       </c>
       <c r="T46" t="n">
-        <v>2.91</v>
+        <v>2.73</v>
       </c>
       <c r="U46" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="V46" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W46" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD46" t="n">
         <v>1.33</v>
       </c>
-      <c r="V46" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W46" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X46" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AE46" t="n">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.62</v>
+        <v>1.31</v>
       </c>
       <c r="AI46" s="3" t="n">
         <v>46084.69791666666</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6010,77 +6010,77 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="M47" t="n">
-        <v>3.47</v>
+        <v>3.25</v>
       </c>
       <c r="N47" t="n">
-        <v>2.59</v>
+        <v>3.5</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI47" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,73 +6133,73 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.45</v>
+        <v>1.91</v>
       </c>
       <c r="M48" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="N48" t="n">
-        <v>2.88</v>
+        <v>3.86</v>
       </c>
       <c r="O48" t="n">
-        <v>2.96</v>
+        <v>2.55</v>
       </c>
       <c r="P48" t="n">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.67</v>
+        <v>4.25</v>
       </c>
       <c r="R48" t="n">
         <v>1.38</v>
       </c>
       <c r="S48" t="n">
-        <v>2.77</v>
+        <v>2.69</v>
       </c>
       <c r="T48" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="U48" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="V48" t="n">
-        <v>6.75</v>
+        <v>7.4</v>
       </c>
       <c r="W48" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X48" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="Z48" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AC48" t="n">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AF48" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AG48" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.52</v>
+        <v>1.73</v>
       </c>
       <c r="AI48" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,37 +6252,37 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="M49" t="n">
-        <v>3.45</v>
+        <v>3.26</v>
       </c>
       <c r="N49" t="n">
-        <v>3.86</v>
+        <v>4</v>
       </c>
       <c r="O49" t="n">
-        <v>2.55</v>
+        <v>2.46</v>
       </c>
       <c r="P49" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="Q49" t="n">
         <v>4.25</v>
       </c>
       <c r="R49" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S49" t="n">
-        <v>2.69</v>
+        <v>2.87</v>
       </c>
       <c r="T49" t="n">
-        <v>2.65</v>
+        <v>2.9</v>
       </c>
       <c r="U49" t="n">
         <v>1.36</v>
       </c>
       <c r="V49" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="W49" t="n">
         <v>1.03</v>
@@ -6291,34 +6291,34 @@
         <v>1</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="Z49" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="AA49" t="n">
         <v>2</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="AC49" t="n">
-        <v>3.34</v>
+        <v>3.52</v>
       </c>
       <c r="AD49" t="n">
         <v>1.24</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.99</v>
+        <v>1.86</v>
       </c>
       <c r="AG49" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.73</v>
+        <v>1.88</v>
       </c>
       <c r="AI49" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,73 +6371,73 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="M50" t="n">
-        <v>3.26</v>
+        <v>3.95</v>
       </c>
       <c r="N50" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O50" t="n">
-        <v>2.46</v>
+        <v>2.06</v>
       </c>
       <c r="P50" t="n">
-        <v>2.09</v>
+        <v>2.35</v>
       </c>
       <c r="Q50" t="n">
-        <v>4.25</v>
+        <v>5.65</v>
       </c>
       <c r="R50" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="S50" t="n">
-        <v>2.87</v>
+        <v>2.91</v>
       </c>
       <c r="T50" t="n">
-        <v>2.9</v>
+        <v>2.48</v>
       </c>
       <c r="U50" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="V50" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="W50" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="X50" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="Z50" t="n">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="AA50" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.67</v>
+        <v>1.93</v>
       </c>
       <c r="AC50" t="n">
-        <v>3.52</v>
+        <v>3</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AE50" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AF50" t="n">
         <v>1.85</v>
       </c>
-      <c r="AF50" t="n">
-        <v>1.86</v>
-      </c>
       <c r="AG50" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AH50" t="n">
-        <v>1.88</v>
+        <v>2.31</v>
       </c>
       <c r="AI50" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6486,77 +6486,77 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.53</v>
+        <v>2.1</v>
       </c>
       <c r="M51" t="n">
-        <v>4.3</v>
+        <v>3.38</v>
       </c>
       <c r="N51" t="n">
-        <v>5.53</v>
+        <v>3.08</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S51" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="T51" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U51" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V51" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W51" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X51" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.65</v>
+        <v>2.03</v>
       </c>
       <c r="AB51" t="n">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="AC51" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD51" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG51" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH51" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI51" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6605,77 +6605,77 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="M52" t="n">
-        <v>3.38</v>
+        <v>3.47</v>
       </c>
       <c r="N52" t="n">
-        <v>3.08</v>
+        <v>2.59</v>
       </c>
       <c r="O52" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U52" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V52" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W52" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X52" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z52" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD52" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG52" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI52" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6724,77 +6724,77 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.85</v>
+        <v>1.53</v>
       </c>
       <c r="M53" t="n">
-        <v>3.1</v>
+        <v>4.3</v>
       </c>
       <c r="N53" t="n">
-        <v>2.24</v>
+        <v>5.53</v>
       </c>
       <c r="O53" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="U53" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V53" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="W53" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X53" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>2.19</v>
+        <v>1.65</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.71</v>
+        <v>2.1</v>
       </c>
       <c r="AC53" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AD53" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG53" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH53" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AI53" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,73 +6847,73 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>3.2</v>
+        <v>2.85</v>
       </c>
       <c r="M54" t="n">
-        <v>3.24</v>
+        <v>3.1</v>
       </c>
       <c r="N54" t="n">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="O54" t="n">
-        <v>3.92</v>
+        <v>3.7</v>
       </c>
       <c r="P54" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="Q54" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="R54" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="S54" t="n">
         <v>2.77</v>
       </c>
       <c r="T54" t="n">
-        <v>2.73</v>
+        <v>3.04</v>
       </c>
       <c r="U54" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="V54" t="n">
-        <v>6.5</v>
+        <v>7.6</v>
       </c>
       <c r="W54" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X54" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z54" t="n">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.88</v>
+        <v>2.19</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.95</v>
+        <v>1.71</v>
       </c>
       <c r="AC54" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="AD54" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="AF54" t="n">
-        <v>2.02</v>
+        <v>1.9</v>
       </c>
       <c r="AG54" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AH54" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="AI54" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6962,77 +6962,77 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.53</v>
+        <v>2.45</v>
       </c>
       <c r="M55" t="n">
-        <v>3.95</v>
+        <v>3</v>
       </c>
       <c r="N55" t="n">
-        <v>5</v>
+        <v>2.7</v>
       </c>
       <c r="O55" t="n">
-        <v>2.06</v>
+        <v>2.95</v>
       </c>
       <c r="P55" t="n">
-        <v>2.35</v>
+        <v>2.05</v>
       </c>
       <c r="Q55" t="n">
-        <v>5.65</v>
+        <v>3.42</v>
       </c>
       <c r="R55" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="S55" t="n">
-        <v>2.91</v>
+        <v>2.62</v>
       </c>
       <c r="T55" t="n">
-        <v>2.48</v>
+        <v>2.96</v>
       </c>
       <c r="U55" t="n">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="V55" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="W55" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X55" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z55" t="n">
         <v>3.5</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.93</v>
+        <v>1.71</v>
       </c>
       <c r="AC55" t="n">
-        <v>3</v>
+        <v>3.48</v>
       </c>
       <c r="AD55" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.84</v>
+        <v>1.67</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AG55" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AH55" t="n">
-        <v>2.31</v>
+        <v>1.48</v>
       </c>
       <c r="AI55" s="3" t="n">
         <v>46084.69791666666</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,73 +7085,73 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S56" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="T56" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U56" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V56" t="n">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="W56" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X56" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC56" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD56" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE56" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF56" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG56" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH56" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI56" s="3" t="n">
         <v>46084.69791666666</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,73 +7204,73 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="T57" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U57" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="V57" t="n">
-        <v>6.95</v>
+        <v>0</v>
       </c>
       <c r="W57" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X57" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z57" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC57" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AD57" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF57" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG57" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH57" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI57" s="3" t="n">
         <v>46084.69791666666</v>
@@ -7406,22 +7406,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L59" t="n">
@@ -7525,22 +7525,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7557,7 +7557,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L60" t="n">

--- a/jogos_2026-03-03.xlsx
+++ b/jogos_2026-03-03.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.81</v>
+        <v>2.5</v>
       </c>
       <c r="M8" t="n">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="N8" t="n">
-        <v>4.55</v>
+        <v>2.8</v>
       </c>
       <c r="O8" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.78</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46084.45833333334</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.5</v>
+        <v>1.81</v>
       </c>
       <c r="M9" t="n">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="N9" t="n">
-        <v>2.8</v>
+        <v>4.55</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>5.78</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46084.45833333334</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.87</v>
+        <v>2.65</v>
       </c>
       <c r="M31" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="N31" t="n">
-        <v>2.98</v>
+        <v>2.65</v>
       </c>
       <c r="O31" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46084.66666666666</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="M32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N32" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="O32" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P32" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="V32" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE32" t="n">
         <v>1.4</v>
       </c>
-      <c r="M32" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="N32" t="n">
-        <v>7.03</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" t="n">
-        <v>0</v>
-      </c>
-      <c r="W32" t="n">
-        <v>0</v>
-      </c>
-      <c r="X32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>0</v>
-      </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46084.66666666666</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.65</v>
+        <v>1.4</v>
       </c>
       <c r="M33" t="n">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="N33" t="n">
-        <v>2.65</v>
+        <v>7.03</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>5.33</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5058,77 +5058,77 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46084.6875</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>4.28</v>
+        <v>1.75</v>
       </c>
       <c r="M40" t="n">
-        <v>4.2</v>
+        <v>3.91</v>
       </c>
       <c r="N40" t="n">
-        <v>1.66</v>
+        <v>5.33</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5534,77 +5534,77 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.45</v>
+        <v>4.28</v>
       </c>
       <c r="M43" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="N43" t="n">
-        <v>2.43</v>
+        <v>1.66</v>
       </c>
       <c r="O43" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF43" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>46084.6875</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,73 +5776,73 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.45</v>
+        <v>1.8</v>
       </c>
       <c r="M45" t="n">
-        <v>3.4</v>
+        <v>3.26</v>
       </c>
       <c r="N45" t="n">
-        <v>2.88</v>
+        <v>4</v>
       </c>
       <c r="O45" t="n">
-        <v>2.96</v>
+        <v>2.46</v>
       </c>
       <c r="P45" t="n">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.67</v>
+        <v>4.25</v>
       </c>
       <c r="R45" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S45" t="n">
-        <v>2.77</v>
+        <v>2.87</v>
       </c>
       <c r="T45" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="U45" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="V45" t="n">
-        <v>6.75</v>
+        <v>7.5</v>
       </c>
       <c r="W45" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X45" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="Z45" t="n">
-        <v>3.6</v>
+        <v>3.05</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AB45" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE45" t="n">
         <v>1.85</v>
       </c>
-      <c r="AC45" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AE45" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AF45" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.52</v>
+        <v>1.88</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46084.69791666666</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,73 +5895,73 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="M46" t="n">
-        <v>3.24</v>
+        <v>3.38</v>
       </c>
       <c r="N46" t="n">
-        <v>2.21</v>
+        <v>3.08</v>
       </c>
       <c r="O46" t="n">
-        <v>3.92</v>
+        <v>2.8</v>
       </c>
       <c r="P46" t="n">
-        <v>2.05</v>
+        <v>2.19</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="R46" t="n">
         <v>1.38</v>
       </c>
       <c r="S46" t="n">
-        <v>2.77</v>
+        <v>2.81</v>
       </c>
       <c r="T46" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="U46" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="V46" t="n">
         <v>6.5</v>
       </c>
       <c r="W46" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X46" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z46" t="n">
-        <v>3.2</v>
+        <v>3.24</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.88</v>
+        <v>2.03</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="AC46" t="n">
         <v>3.3</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AF46" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.31</v>
+        <v>1.55</v>
       </c>
       <c r="AI46" s="3" t="n">
         <v>46084.69791666666</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,73 +6014,73 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2</v>
+        <v>2.85</v>
       </c>
       <c r="M47" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="N47" t="n">
-        <v>3.5</v>
+        <v>2.24</v>
       </c>
       <c r="O47" t="n">
-        <v>2.62</v>
+        <v>3.7</v>
       </c>
       <c r="P47" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="Q47" t="n">
-        <v>4.26</v>
+        <v>3.1</v>
       </c>
       <c r="R47" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="S47" t="n">
-        <v>2.87</v>
+        <v>2.77</v>
       </c>
       <c r="T47" t="n">
-        <v>2.91</v>
+        <v>3.04</v>
       </c>
       <c r="U47" t="n">
         <v>1.33</v>
       </c>
       <c r="V47" t="n">
-        <v>7.1</v>
+        <v>7.6</v>
       </c>
       <c r="W47" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X47" t="n">
         <v>1.02</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="Z47" t="n">
-        <v>2.92</v>
+        <v>3.14</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.07</v>
+        <v>2.19</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AC47" t="n">
-        <v>3.67</v>
+        <v>3.55</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AE47" t="n">
         <v>1.81</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="AG47" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.62</v>
+        <v>1.38</v>
       </c>
       <c r="AI47" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,73 +6133,73 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.91</v>
+        <v>1.53</v>
       </c>
       <c r="M48" t="n">
-        <v>3.45</v>
+        <v>3.95</v>
       </c>
       <c r="N48" t="n">
-        <v>3.86</v>
+        <v>5</v>
       </c>
       <c r="O48" t="n">
-        <v>2.55</v>
+        <v>2.06</v>
       </c>
       <c r="P48" t="n">
-        <v>2.11</v>
+        <v>2.35</v>
       </c>
       <c r="Q48" t="n">
-        <v>4.25</v>
+        <v>5.65</v>
       </c>
       <c r="R48" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="S48" t="n">
-        <v>2.69</v>
+        <v>2.91</v>
       </c>
       <c r="T48" t="n">
-        <v>2.65</v>
+        <v>2.48</v>
       </c>
       <c r="U48" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="V48" t="n">
-        <v>7.4</v>
+        <v>6.5</v>
       </c>
       <c r="W48" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="X48" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="Z48" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="AA48" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.81</v>
+        <v>1.93</v>
       </c>
       <c r="AC48" t="n">
-        <v>3.34</v>
+        <v>3</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.99</v>
+        <v>1.85</v>
       </c>
       <c r="AG48" t="n">
-        <v>1.34</v>
+        <v>1.17</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.73</v>
+        <v>2.31</v>
       </c>
       <c r="AI48" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6248,77 +6248,77 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.8</v>
+        <v>3.2</v>
       </c>
       <c r="M49" t="n">
-        <v>3.26</v>
+        <v>3.24</v>
       </c>
       <c r="N49" t="n">
-        <v>4</v>
+        <v>2.21</v>
       </c>
       <c r="O49" t="n">
-        <v>2.46</v>
+        <v>3.92</v>
       </c>
       <c r="P49" t="n">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="Q49" t="n">
-        <v>4.25</v>
+        <v>2.8</v>
       </c>
       <c r="R49" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S49" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="U49" t="n">
         <v>1.39</v>
       </c>
-      <c r="S49" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="T49" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U49" t="n">
-        <v>1.36</v>
-      </c>
       <c r="V49" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="W49" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X49" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="Z49" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="AA49" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="AC49" t="n">
-        <v>3.52</v>
+        <v>3.3</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.86</v>
+        <v>2.02</v>
       </c>
       <c r="AG49" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.88</v>
+        <v>1.31</v>
       </c>
       <c r="AI49" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6367,77 +6367,77 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.53</v>
+        <v>2.45</v>
       </c>
       <c r="M50" t="n">
-        <v>3.95</v>
+        <v>3</v>
       </c>
       <c r="N50" t="n">
-        <v>5</v>
+        <v>2.7</v>
       </c>
       <c r="O50" t="n">
-        <v>2.06</v>
+        <v>2.95</v>
       </c>
       <c r="P50" t="n">
-        <v>2.35</v>
+        <v>2.05</v>
       </c>
       <c r="Q50" t="n">
-        <v>5.65</v>
+        <v>3.42</v>
       </c>
       <c r="R50" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="S50" t="n">
-        <v>2.91</v>
+        <v>2.62</v>
       </c>
       <c r="T50" t="n">
-        <v>2.48</v>
+        <v>2.96</v>
       </c>
       <c r="U50" t="n">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="V50" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="W50" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X50" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z50" t="n">
         <v>3.5</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.93</v>
+        <v>1.71</v>
       </c>
       <c r="AC50" t="n">
-        <v>3</v>
+        <v>3.48</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.84</v>
+        <v>1.67</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AG50" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AH50" t="n">
-        <v>2.31</v>
+        <v>1.48</v>
       </c>
       <c r="AI50" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6486,77 +6486,77 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="M51" t="n">
-        <v>3.38</v>
+        <v>3.47</v>
       </c>
       <c r="N51" t="n">
-        <v>3.08</v>
+        <v>2.59</v>
       </c>
       <c r="O51" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U51" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V51" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W51" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X51" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z51" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD51" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG51" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH51" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI51" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,73 +6609,73 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.45</v>
+        <v>1.91</v>
       </c>
       <c r="M52" t="n">
-        <v>3.47</v>
+        <v>3.45</v>
       </c>
       <c r="N52" t="n">
-        <v>2.59</v>
+        <v>3.86</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S52" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="T52" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U52" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V52" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="W52" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC52" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD52" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AG52" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH52" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI52" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,73 +6728,73 @@
         </is>
       </c>
       <c r="L53" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="M53" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N53" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="O53" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P53" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R53" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S53" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V53" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="W53" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X53" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH53" t="n">
         <v>1.53</v>
-      </c>
-      <c r="M53" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="N53" t="n">
-        <v>5.53</v>
-      </c>
-      <c r="O53" t="n">
-        <v>0</v>
-      </c>
-      <c r="P53" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
-      <c r="R53" t="n">
-        <v>0</v>
-      </c>
-      <c r="S53" t="n">
-        <v>0</v>
-      </c>
-      <c r="T53" t="n">
-        <v>0</v>
-      </c>
-      <c r="U53" t="n">
-        <v>0</v>
-      </c>
-      <c r="V53" t="n">
-        <v>0</v>
-      </c>
-      <c r="W53" t="n">
-        <v>0</v>
-      </c>
-      <c r="X53" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y53" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH53" t="n">
-        <v>0</v>
       </c>
       <c r="AI53" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6843,77 +6843,77 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.85</v>
+        <v>2.45</v>
       </c>
       <c r="M54" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="N54" t="n">
-        <v>2.24</v>
+        <v>2.88</v>
       </c>
       <c r="O54" t="n">
-        <v>3.7</v>
+        <v>2.96</v>
       </c>
       <c r="P54" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.1</v>
+        <v>3.67</v>
       </c>
       <c r="R54" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="S54" t="n">
         <v>2.77</v>
       </c>
       <c r="T54" t="n">
-        <v>3.04</v>
+        <v>2.75</v>
       </c>
       <c r="U54" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="V54" t="n">
-        <v>7.6</v>
+        <v>6.75</v>
       </c>
       <c r="W54" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X54" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Z54" t="n">
-        <v>3.14</v>
+        <v>3.6</v>
       </c>
       <c r="AA54" t="n">
-        <v>2.19</v>
+        <v>1.93</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.71</v>
+        <v>1.85</v>
       </c>
       <c r="AC54" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="AD54" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AG54" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AH54" t="n">
-        <v>1.38</v>
+        <v>1.52</v>
       </c>
       <c r="AI54" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6962,77 +6962,77 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="U55" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V55" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W55" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X55" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z55" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="AD55" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF55" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG55" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AI55" s="3" t="n">
         <v>46084.69791666666</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,73 +7085,73 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.45</v>
+        <v>1.53</v>
       </c>
       <c r="M56" t="n">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="N56" t="n">
-        <v>2.72</v>
+        <v>5.53</v>
       </c>
       <c r="O56" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>0</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
+      </c>
+      <c r="V56" t="n">
+        <v>0</v>
+      </c>
+      <c r="W56" t="n">
+        <v>0</v>
+      </c>
+      <c r="X56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB56" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q56" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R56" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S56" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="T56" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U56" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="V56" t="n">
-        <v>6.95</v>
-      </c>
-      <c r="W56" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X56" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="Z56" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AC56" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AD56" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF56" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG56" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH56" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI56" s="3" t="n">
         <v>46084.69791666666</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7200,77 +7200,77 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O57" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S57" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="T57" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U57" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V57" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="W57" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X57" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y57" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z57" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC57" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="AD57" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE57" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF57" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG57" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH57" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI57" s="3" t="n">
         <v>46084.69791666666</v>
@@ -7406,22 +7406,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L59" t="n">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7644,22 +7644,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L61" t="n">

--- a/jogos_2026-03-03.xlsx
+++ b/jogos_2026-03-03.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.47</v>
+        <v>2.65</v>
       </c>
       <c r="M29" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N29" t="n">
-        <v>2.11</v>
+        <v>2.65</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.72</v>
+        <v>1.87</v>
       </c>
       <c r="M30" t="n">
-        <v>3.15</v>
+        <v>3.8</v>
       </c>
       <c r="N30" t="n">
-        <v>2.05</v>
+        <v>2.98</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46084.66666666666</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.65</v>
+        <v>3.72</v>
       </c>
       <c r="M31" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="N31" t="n">
-        <v>2.65</v>
+        <v>2.05</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.87</v>
+        <v>3.47</v>
       </c>
       <c r="M32" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="N32" t="n">
-        <v>2.98</v>
+        <v>2.11</v>
       </c>
       <c r="O32" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46084.66666666666</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4820,77 +4820,77 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46084.6875</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5058,77 +5058,77 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.45</v>
+        <v>2.49</v>
       </c>
       <c r="M39" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="N39" t="n">
-        <v>2.43</v>
+        <v>2.86</v>
       </c>
       <c r="O39" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AB39" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46084.6875</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.75</v>
+        <v>4.28</v>
       </c>
       <c r="M40" t="n">
-        <v>3.91</v>
+        <v>4.2</v>
       </c>
       <c r="N40" t="n">
-        <v>5.33</v>
+        <v>1.66</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,73 +5776,73 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.8</v>
+        <v>2.45</v>
       </c>
       <c r="M45" t="n">
-        <v>3.26</v>
+        <v>3.4</v>
       </c>
       <c r="N45" t="n">
-        <v>4</v>
+        <v>2.88</v>
       </c>
       <c r="O45" t="n">
-        <v>2.46</v>
+        <v>2.96</v>
       </c>
       <c r="P45" t="n">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="Q45" t="n">
-        <v>4.25</v>
+        <v>3.67</v>
       </c>
       <c r="R45" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S45" t="n">
-        <v>2.87</v>
+        <v>2.77</v>
       </c>
       <c r="T45" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="U45" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="V45" t="n">
-        <v>7.5</v>
+        <v>6.75</v>
       </c>
       <c r="W45" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X45" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="Z45" t="n">
-        <v>3.05</v>
+        <v>3.6</v>
       </c>
       <c r="AA45" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF45" t="n">
         <v>2</v>
       </c>
-      <c r="AB45" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE45" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF45" t="n">
-        <v>1.86</v>
-      </c>
       <c r="AG45" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.88</v>
+        <v>1.52</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46084.69791666666</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5891,77 +5891,77 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="M46" t="n">
-        <v>3.38</v>
+        <v>3.45</v>
       </c>
       <c r="N46" t="n">
-        <v>3.08</v>
+        <v>3.86</v>
       </c>
       <c r="O46" t="n">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="P46" t="n">
-        <v>2.19</v>
+        <v>2.11</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.5</v>
+        <v>4.25</v>
       </c>
       <c r="R46" t="n">
         <v>1.38</v>
       </c>
       <c r="S46" t="n">
-        <v>2.81</v>
+        <v>2.69</v>
       </c>
       <c r="T46" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="U46" t="n">
         <v>1.36</v>
       </c>
       <c r="V46" t="n">
-        <v>6.5</v>
+        <v>7.4</v>
       </c>
       <c r="W46" t="n">
         <v>1.03</v>
       </c>
       <c r="X46" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z46" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AB46" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AH46" t="n">
         <v>1.73</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE46" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF46" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG46" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AH46" t="n">
-        <v>1.55</v>
       </c>
       <c r="AI46" s="3" t="n">
         <v>46084.69791666666</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6010,77 +6010,77 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.85</v>
+        <v>2.45</v>
       </c>
       <c r="M47" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N47" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="O47" t="n">
         <v>3.1</v>
       </c>
-      <c r="N47" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="O47" t="n">
-        <v>3.7</v>
-      </c>
       <c r="P47" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="R47" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="S47" t="n">
-        <v>2.77</v>
+        <v>2.69</v>
       </c>
       <c r="T47" t="n">
-        <v>3.04</v>
+        <v>2.65</v>
       </c>
       <c r="U47" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V47" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="W47" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X47" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG47" t="n">
         <v>1.33</v>
       </c>
-      <c r="V47" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="W47" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X47" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AE47" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AF47" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AG47" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AH47" t="n">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="AI47" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6129,77 +6129,77 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.53</v>
+        <v>2.85</v>
       </c>
       <c r="M48" t="n">
-        <v>3.95</v>
+        <v>3.1</v>
       </c>
       <c r="N48" t="n">
-        <v>5</v>
+        <v>2.24</v>
       </c>
       <c r="O48" t="n">
-        <v>2.06</v>
+        <v>3.7</v>
       </c>
       <c r="P48" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="Q48" t="n">
-        <v>5.65</v>
+        <v>3.1</v>
       </c>
       <c r="R48" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S48" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T48" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="U48" t="n">
         <v>1.33</v>
       </c>
-      <c r="S48" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="T48" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="U48" t="n">
-        <v>1.41</v>
-      </c>
       <c r="V48" t="n">
-        <v>6.5</v>
+        <v>7.6</v>
       </c>
       <c r="W48" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="X48" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="Z48" t="n">
-        <v>3.5</v>
+        <v>3.14</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.78</v>
+        <v>2.19</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.93</v>
+        <v>1.71</v>
       </c>
       <c r="AC48" t="n">
-        <v>3</v>
+        <v>3.55</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AG48" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AH48" t="n">
-        <v>2.31</v>
+        <v>1.38</v>
       </c>
       <c r="AI48" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,73 +6252,73 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="M49" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="N49" t="n">
-        <v>2.21</v>
+        <v>3.5</v>
       </c>
       <c r="O49" t="n">
-        <v>3.92</v>
+        <v>2.62</v>
       </c>
       <c r="P49" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.8</v>
+        <v>4.26</v>
       </c>
       <c r="R49" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="S49" t="n">
-        <v>2.77</v>
+        <v>2.87</v>
       </c>
       <c r="T49" t="n">
-        <v>2.73</v>
+        <v>2.91</v>
       </c>
       <c r="U49" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="V49" t="n">
-        <v>6.5</v>
+        <v>7.1</v>
       </c>
       <c r="W49" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X49" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="Z49" t="n">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.88</v>
+        <v>2.07</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="AC49" t="n">
-        <v>3.3</v>
+        <v>3.67</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="AF49" t="n">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="AG49" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.31</v>
+        <v>1.62</v>
       </c>
       <c r="AI49" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,73 +6371,73 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.45</v>
+        <v>3.2</v>
       </c>
       <c r="M50" t="n">
-        <v>3</v>
+        <v>3.24</v>
       </c>
       <c r="N50" t="n">
-        <v>2.7</v>
+        <v>2.21</v>
       </c>
       <c r="O50" t="n">
-        <v>2.95</v>
+        <v>3.92</v>
       </c>
       <c r="P50" t="n">
         <v>2.05</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.42</v>
+        <v>2.8</v>
       </c>
       <c r="R50" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="S50" t="n">
-        <v>2.62</v>
+        <v>2.77</v>
       </c>
       <c r="T50" t="n">
-        <v>2.96</v>
+        <v>2.73</v>
       </c>
       <c r="U50" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="V50" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="W50" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X50" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Z50" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="AA50" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.71</v>
+        <v>1.95</v>
       </c>
       <c r="AC50" t="n">
-        <v>3.48</v>
+        <v>3.3</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AF50" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AG50" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH50" t="n">
-        <v>1.48</v>
+        <v>1.31</v>
       </c>
       <c r="AI50" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,73 +6490,73 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.45</v>
+        <v>1.8</v>
       </c>
       <c r="M51" t="n">
-        <v>3.47</v>
+        <v>3.26</v>
       </c>
       <c r="N51" t="n">
-        <v>2.59</v>
+        <v>4</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S51" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="T51" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U51" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V51" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W51" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC51" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AD51" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG51" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH51" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AI51" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6605,77 +6605,77 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="M52" t="n">
-        <v>3.45</v>
+        <v>3.38</v>
       </c>
       <c r="N52" t="n">
-        <v>3.86</v>
+        <v>3.08</v>
       </c>
       <c r="O52" t="n">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="P52" t="n">
-        <v>2.11</v>
+        <v>2.19</v>
       </c>
       <c r="Q52" t="n">
-        <v>4.25</v>
+        <v>3.5</v>
       </c>
       <c r="R52" t="n">
         <v>1.38</v>
       </c>
       <c r="S52" t="n">
-        <v>2.69</v>
+        <v>2.81</v>
       </c>
       <c r="T52" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="U52" t="n">
         <v>1.36</v>
       </c>
       <c r="V52" t="n">
-        <v>7.4</v>
+        <v>6.5</v>
       </c>
       <c r="W52" t="n">
         <v>1.03</v>
       </c>
       <c r="X52" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z52" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="AA52" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="AC52" t="n">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="AD52" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG52" t="n">
         <v>1.24</v>
       </c>
-      <c r="AE52" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF52" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AG52" t="n">
-        <v>1.34</v>
-      </c>
       <c r="AH52" t="n">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="AI52" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,73 +6728,73 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.45</v>
+        <v>1.53</v>
       </c>
       <c r="M53" t="n">
-        <v>3.2</v>
+        <v>3.95</v>
       </c>
       <c r="N53" t="n">
-        <v>2.72</v>
+        <v>5</v>
       </c>
       <c r="O53" t="n">
-        <v>3.1</v>
+        <v>2.06</v>
       </c>
       <c r="P53" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.5</v>
+        <v>5.65</v>
       </c>
       <c r="R53" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="S53" t="n">
-        <v>2.69</v>
+        <v>2.91</v>
       </c>
       <c r="T53" t="n">
-        <v>2.65</v>
+        <v>2.48</v>
       </c>
       <c r="U53" t="n">
         <v>1.41</v>
       </c>
       <c r="V53" t="n">
-        <v>6.95</v>
+        <v>6.5</v>
       </c>
       <c r="W53" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="X53" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="Z53" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.98</v>
+        <v>1.78</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.75</v>
+        <v>1.93</v>
       </c>
       <c r="AC53" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AD53" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="AF53" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AG53" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AH53" t="n">
-        <v>1.53</v>
+        <v>2.31</v>
       </c>
       <c r="AI53" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,73 +6847,73 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.45</v>
+        <v>1.53</v>
       </c>
       <c r="M54" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="N54" t="n">
-        <v>2.88</v>
+        <v>5.53</v>
       </c>
       <c r="O54" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U54" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V54" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="W54" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X54" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z54" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.93</v>
+        <v>1.65</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AC54" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AD54" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF54" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG54" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH54" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AI54" s="3" t="n">
         <v>46084.69791666666</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.53</v>
+        <v>2.45</v>
       </c>
       <c r="M56" t="n">
-        <v>4.3</v>
+        <v>3.47</v>
       </c>
       <c r="N56" t="n">
-        <v>5.53</v>
+        <v>2.59</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7130,10 +7130,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,73 +7204,73 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="M57" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="N57" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="O57" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="P57" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="R57" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S57" t="n">
         <v>2.62</v>
       </c>
-      <c r="P57" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>4.26</v>
-      </c>
-      <c r="R57" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S57" t="n">
-        <v>2.87</v>
-      </c>
       <c r="T57" t="n">
-        <v>2.91</v>
+        <v>2.96</v>
       </c>
       <c r="U57" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="V57" t="n">
-        <v>7.1</v>
+        <v>8</v>
       </c>
       <c r="W57" t="n">
         <v>1.07</v>
       </c>
       <c r="X57" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="Z57" t="n">
-        <v>2.92</v>
+        <v>3.5</v>
       </c>
       <c r="AA57" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AC57" t="n">
-        <v>3.67</v>
+        <v>3.48</v>
       </c>
       <c r="AD57" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="AF57" t="n">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="AG57" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AH57" t="n">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="AI57" s="3" t="n">
         <v>46084.69791666666</v>
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G60" t="n">

--- a/jogos_2026-03-03.xlsx
+++ b/jogos_2026-03-03.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI61"/>
+  <dimension ref="A1:AI60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1094,12 +1094,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1204,7 +1204,7 @@
         <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
-        <v>46084.4375</v>
+        <v>46084.41666666666</v>
       </c>
     </row>
     <row r="7">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1442,7 +1442,7 @@
         <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
-        <v>46084.45833333334</v>
+        <v>46084.4375</v>
       </c>
     </row>
     <row r="9">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.81</v>
+        <v>2.5</v>
       </c>
       <c r="M9" t="n">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="N9" t="n">
-        <v>4.55</v>
+        <v>2.8</v>
       </c>
       <c r="O9" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.78</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46084.45833333334</v>
@@ -1570,12 +1570,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,76 +1611,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>5.78</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AI10" s="3" t="n">
-        <v>46084.5</v>
+        <v>46084.45833333334</v>
       </c>
     </row>
     <row r="11">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>6.13</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1918,7 +1918,7 @@
         <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
-        <v>46084.5625</v>
+        <v>46084.5</v>
       </c>
     </row>
     <row r="13">
@@ -1927,12 +1927,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>6.13</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2037,7 +2037,7 @@
         <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
-        <v>46084.58333333334</v>
+        <v>46084.5625</v>
       </c>
     </row>
     <row r="14">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2403,12 +2403,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2513,7 +2513,7 @@
         <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
-        <v>46084.60416666666</v>
+        <v>46084.58333333334</v>
       </c>
     </row>
     <row r="18">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2870,7 +2870,7 @@
         <v>0</v>
       </c>
       <c r="AI20" s="3" t="n">
-        <v>46084.625</v>
+        <v>46084.60416666666</v>
       </c>
     </row>
     <row r="21">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3593,12 +3593,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3703,7 +3703,7 @@
         <v>0</v>
       </c>
       <c r="AI27" s="3" t="n">
-        <v>46084.65625</v>
+        <v>46084.625</v>
       </c>
     </row>
     <row r="28">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3831,12 +3831,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3941,7 +3941,7 @@
         <v>0</v>
       </c>
       <c r="AI29" s="3" t="n">
-        <v>46084.66666666666</v>
+        <v>46084.65625</v>
       </c>
     </row>
     <row r="30">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.87</v>
+        <v>2.65</v>
       </c>
       <c r="M30" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="N30" t="n">
-        <v>2.98</v>
+        <v>2.65</v>
       </c>
       <c r="O30" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46084.66666666666</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.72</v>
+        <v>3.47</v>
       </c>
       <c r="M31" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="N31" t="n">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.47</v>
+        <v>1.4</v>
       </c>
       <c r="M32" t="n">
-        <v>3.2</v>
+        <v>4.6</v>
       </c>
       <c r="N32" t="n">
-        <v>2.11</v>
+        <v>7.03</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.4</v>
+        <v>3.72</v>
       </c>
       <c r="M33" t="n">
-        <v>4.6</v>
+        <v>3.15</v>
       </c>
       <c r="N33" t="n">
-        <v>7.03</v>
+        <v>2.05</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4426,12 +4426,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,76 +4467,76 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI34" s="3" t="n">
-        <v>46084.6875</v>
+        <v>46084.66666666666</v>
       </c>
     </row>
     <row r="35">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4701,77 +4701,77 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46084.6875</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4820,77 +4820,77 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.45</v>
+        <v>2.05</v>
       </c>
       <c r="M37" t="n">
-        <v>3.3</v>
+        <v>3.56</v>
       </c>
       <c r="N37" t="n">
-        <v>2.43</v>
+        <v>4.05</v>
       </c>
       <c r="O37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.67</v>
+        <v>2.15</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.1</v>
+        <v>1.63</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46084.6875</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>4.28</v>
+        <v>2.49</v>
       </c>
       <c r="M40" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="N40" t="n">
-        <v>1.66</v>
+        <v>2.86</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>5.33</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.05</v>
+        <v>4.28</v>
       </c>
       <c r="M44" t="n">
-        <v>3.56</v>
+        <v>4.2</v>
       </c>
       <c r="N44" t="n">
-        <v>4.05</v>
+        <v>1.66</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5735,12 +5735,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,76 +5776,76 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AI45" s="3" t="n">
-        <v>46084.69791666666</v>
+        <v>46084.6875</v>
       </c>
     </row>
     <row r="46">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,37 +5895,37 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="M46" t="n">
-        <v>3.45</v>
+        <v>3.26</v>
       </c>
       <c r="N46" t="n">
-        <v>3.86</v>
+        <v>4</v>
       </c>
       <c r="O46" t="n">
-        <v>2.55</v>
+        <v>2.46</v>
       </c>
       <c r="P46" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="Q46" t="n">
         <v>4.25</v>
       </c>
       <c r="R46" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S46" t="n">
-        <v>2.69</v>
+        <v>2.87</v>
       </c>
       <c r="T46" t="n">
-        <v>2.65</v>
+        <v>2.9</v>
       </c>
       <c r="U46" t="n">
         <v>1.36</v>
       </c>
       <c r="V46" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="W46" t="n">
         <v>1.03</v>
@@ -5934,34 +5934,34 @@
         <v>1</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="Z46" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="AA46" t="n">
         <v>2</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="AC46" t="n">
-        <v>3.34</v>
+        <v>3.52</v>
       </c>
       <c r="AD46" t="n">
         <v>1.24</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.99</v>
+        <v>1.86</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.73</v>
+        <v>1.88</v>
       </c>
       <c r="AI46" s="3" t="n">
         <v>46084.69791666666</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6010,77 +6010,77 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.45</v>
+        <v>3.2</v>
       </c>
       <c r="M47" t="n">
-        <v>3.2</v>
+        <v>3.24</v>
       </c>
       <c r="N47" t="n">
-        <v>2.72</v>
+        <v>2.21</v>
       </c>
       <c r="O47" t="n">
-        <v>3.1</v>
+        <v>3.92</v>
       </c>
       <c r="P47" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="R47" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S47" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="U47" t="n">
         <v>1.39</v>
       </c>
-      <c r="S47" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="T47" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U47" t="n">
-        <v>1.41</v>
-      </c>
       <c r="V47" t="n">
-        <v>6.95</v>
+        <v>6.5</v>
       </c>
       <c r="W47" t="n">
         <v>1.04</v>
       </c>
       <c r="X47" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y47" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH47" t="n">
         <v>1.31</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE47" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF47" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG47" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH47" t="n">
-        <v>1.53</v>
       </c>
       <c r="AI47" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,73 +6133,73 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.85</v>
+        <v>2</v>
       </c>
       <c r="M48" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="N48" t="n">
-        <v>2.24</v>
+        <v>3.5</v>
       </c>
       <c r="O48" t="n">
-        <v>3.7</v>
+        <v>2.62</v>
       </c>
       <c r="P48" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.1</v>
+        <v>4.26</v>
       </c>
       <c r="R48" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="S48" t="n">
-        <v>2.77</v>
+        <v>2.87</v>
       </c>
       <c r="T48" t="n">
-        <v>3.04</v>
+        <v>2.91</v>
       </c>
       <c r="U48" t="n">
         <v>1.33</v>
       </c>
       <c r="V48" t="n">
-        <v>7.6</v>
+        <v>7.1</v>
       </c>
       <c r="W48" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X48" t="n">
         <v>1.02</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="Z48" t="n">
-        <v>3.14</v>
+        <v>2.92</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.19</v>
+        <v>2.07</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AC48" t="n">
-        <v>3.55</v>
+        <v>3.67</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AE48" t="n">
         <v>1.81</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="AG48" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.38</v>
+        <v>1.62</v>
       </c>
       <c r="AI48" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,73 +6252,73 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2</v>
+        <v>2.85</v>
       </c>
       <c r="M49" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="N49" t="n">
-        <v>3.5</v>
+        <v>2.24</v>
       </c>
       <c r="O49" t="n">
-        <v>2.62</v>
+        <v>3.7</v>
       </c>
       <c r="P49" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="Q49" t="n">
-        <v>4.26</v>
+        <v>3.1</v>
       </c>
       <c r="R49" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="S49" t="n">
-        <v>2.87</v>
+        <v>2.77</v>
       </c>
       <c r="T49" t="n">
-        <v>2.91</v>
+        <v>3.04</v>
       </c>
       <c r="U49" t="n">
         <v>1.33</v>
       </c>
       <c r="V49" t="n">
-        <v>7.1</v>
+        <v>7.6</v>
       </c>
       <c r="W49" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X49" t="n">
         <v>1.02</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="Z49" t="n">
-        <v>2.92</v>
+        <v>3.14</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.07</v>
+        <v>2.19</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AC49" t="n">
-        <v>3.67</v>
+        <v>3.55</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AE49" t="n">
         <v>1.81</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="AG49" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.62</v>
+        <v>1.38</v>
       </c>
       <c r="AI49" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6367,77 +6367,77 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="U50" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V50" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W50" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X50" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z50" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF50" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AG50" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH50" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AI50" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6486,77 +6486,77 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.8</v>
+        <v>2.45</v>
       </c>
       <c r="M51" t="n">
-        <v>3.26</v>
+        <v>3</v>
       </c>
       <c r="N51" t="n">
-        <v>4</v>
+        <v>2.7</v>
       </c>
       <c r="O51" t="n">
-        <v>2.46</v>
+        <v>2.95</v>
       </c>
       <c r="P51" t="n">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="Q51" t="n">
-        <v>4.25</v>
+        <v>3.42</v>
       </c>
       <c r="R51" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="S51" t="n">
-        <v>2.87</v>
+        <v>2.62</v>
       </c>
       <c r="T51" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="U51" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="V51" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="W51" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X51" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="Z51" t="n">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="AA51" t="n">
         <v>2</v>
       </c>
       <c r="AB51" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE51" t="n">
         <v>1.67</v>
       </c>
-      <c r="AC51" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE51" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AF51" t="n">
-        <v>1.86</v>
+        <v>2.1</v>
       </c>
       <c r="AG51" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AH51" t="n">
-        <v>1.88</v>
+        <v>1.48</v>
       </c>
       <c r="AI51" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6605,77 +6605,77 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L52" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="M52" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N52" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="O52" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P52" t="n">
         <v>2.1</v>
-      </c>
-      <c r="M52" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="N52" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="O52" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="P52" t="n">
-        <v>2.19</v>
       </c>
       <c r="Q52" t="n">
         <v>3.5</v>
       </c>
       <c r="R52" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S52" t="n">
-        <v>2.81</v>
+        <v>2.69</v>
       </c>
       <c r="T52" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="U52" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="V52" t="n">
-        <v>6.5</v>
+        <v>6.95</v>
       </c>
       <c r="W52" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X52" t="n">
         <v>1.06</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Z52" t="n">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="AA52" t="n">
-        <v>2.03</v>
+        <v>1.98</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AC52" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AD52" t="n">
         <v>1.29</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AG52" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AI52" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,73 +6847,73 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.53</v>
+        <v>2.45</v>
       </c>
       <c r="M54" t="n">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="N54" t="n">
-        <v>5.53</v>
+        <v>2.88</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S54" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T54" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U54" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V54" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="W54" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X54" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.65</v>
+        <v>1.93</v>
       </c>
       <c r="AB54" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AD54" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG54" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH54" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AI54" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,73 +6966,73 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S55" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="T55" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U55" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V55" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="W55" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC55" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD55" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AG55" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH55" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI55" s="3" t="n">
         <v>46084.69791666666</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,73 +7204,73 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="M57" t="n">
-        <v>3</v>
+        <v>3.38</v>
       </c>
       <c r="N57" t="n">
-        <v>2.7</v>
+        <v>3.08</v>
       </c>
       <c r="O57" t="n">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="P57" t="n">
-        <v>2.05</v>
+        <v>2.19</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="R57" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="S57" t="n">
-        <v>2.62</v>
+        <v>2.81</v>
       </c>
       <c r="T57" t="n">
-        <v>2.96</v>
+        <v>2.75</v>
       </c>
       <c r="U57" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="V57" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="W57" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X57" t="n">
         <v>1.06</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Z57" t="n">
-        <v>3.5</v>
+        <v>3.24</v>
       </c>
       <c r="AA57" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AC57" t="n">
-        <v>3.48</v>
+        <v>3.3</v>
       </c>
       <c r="AD57" t="n">
         <v>1.29</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AF57" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AG57" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AH57" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AI57" s="3" t="n">
         <v>46084.69791666666</v>
@@ -7282,12 +7282,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>6.24</v>
+        <v>1.53</v>
       </c>
       <c r="M58" t="n">
-        <v>4.72</v>
+        <v>4.3</v>
       </c>
       <c r="N58" t="n">
-        <v>1.55</v>
+        <v>5.53</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,10 +7368,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AB58" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -7392,7 +7392,7 @@
         <v>0</v>
       </c>
       <c r="AI58" s="3" t="n">
-        <v>46084.71875</v>
+        <v>46084.69791666666</v>
       </c>
     </row>
     <row r="59">
@@ -7401,27 +7401,27 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>6.24</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB59" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7511,7 +7511,7 @@
         <v>0</v>
       </c>
       <c r="AI59" s="3" t="n">
-        <v>46084.875</v>
+        <v>46084.71875</v>
       </c>
     </row>
     <row r="60">
@@ -7525,22 +7525,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7557,7 +7557,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L60" t="n">
@@ -7630,125 +7630,6 @@
         <v>0</v>
       </c>
       <c r="AI60" s="3" t="n">
-        <v>46084.875</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="n">
-        <v>46084</v>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Italy Serie C Group B</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>Rimini</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Città di Campobasso</t>
-        </is>
-      </c>
-      <c r="G61" t="n">
-        <v>0</v>
-      </c>
-      <c r="H61" t="n">
-        <v>0</v>
-      </c>
-      <c r="I61" t="n">
-        <v>0</v>
-      </c>
-      <c r="J61" t="n">
-        <v>0</v>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>canceled</t>
-        </is>
-      </c>
-      <c r="L61" t="n">
-        <v>0</v>
-      </c>
-      <c r="M61" t="n">
-        <v>0</v>
-      </c>
-      <c r="N61" t="n">
-        <v>0</v>
-      </c>
-      <c r="O61" t="n">
-        <v>0</v>
-      </c>
-      <c r="P61" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
-      <c r="R61" t="n">
-        <v>0</v>
-      </c>
-      <c r="S61" t="n">
-        <v>0</v>
-      </c>
-      <c r="T61" t="n">
-        <v>0</v>
-      </c>
-      <c r="U61" t="n">
-        <v>0</v>
-      </c>
-      <c r="V61" t="n">
-        <v>0</v>
-      </c>
-      <c r="W61" t="n">
-        <v>0</v>
-      </c>
-      <c r="X61" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y61" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI61" s="3" t="n">
         <v>46084.875</v>
       </c>
     </row>

--- a/jogos_2026-03-03.xlsx
+++ b/jogos_2026-03-03.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.5</v>
+        <v>1.81</v>
       </c>
       <c r="M9" t="n">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="N9" t="n">
-        <v>2.8</v>
+        <v>4.55</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>5.78</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46084.45833333334</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.81</v>
+        <v>2.5</v>
       </c>
       <c r="M10" t="n">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="N10" t="n">
-        <v>4.55</v>
+        <v>2.8</v>
       </c>
       <c r="O10" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.78</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46084.45833333334</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.65</v>
+        <v>1.4</v>
       </c>
       <c r="M30" t="n">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="N30" t="n">
-        <v>2.65</v>
+        <v>7.03</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.47</v>
+        <v>1.87</v>
       </c>
       <c r="M31" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="N31" t="n">
-        <v>2.11</v>
+        <v>2.98</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46084.66666666666</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.4</v>
+        <v>2.65</v>
       </c>
       <c r="M32" t="n">
-        <v>4.6</v>
+        <v>3.1</v>
       </c>
       <c r="N32" t="n">
-        <v>7.03</v>
+        <v>2.65</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.72</v>
+        <v>3.47</v>
       </c>
       <c r="M33" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="N33" t="n">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.87</v>
+        <v>3.72</v>
       </c>
       <c r="M34" t="n">
-        <v>3.8</v>
+        <v>3.15</v>
       </c>
       <c r="N34" t="n">
-        <v>2.98</v>
+        <v>2.05</v>
       </c>
       <c r="O34" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46084.66666666666</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4701,77 +4701,77 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46084.6875</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4820,77 +4820,77 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.05</v>
+        <v>2.45</v>
       </c>
       <c r="M37" t="n">
-        <v>3.56</v>
+        <v>3.3</v>
       </c>
       <c r="N37" t="n">
-        <v>4.05</v>
+        <v>2.43</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.15</v>
+        <v>1.67</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.63</v>
+        <v>2.1</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46084.6875</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.75</v>
+        <v>4.28</v>
       </c>
       <c r="M38" t="n">
-        <v>3.91</v>
+        <v>4.2</v>
       </c>
       <c r="N38" t="n">
-        <v>5.33</v>
+        <v>1.66</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,73 +5895,73 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="M46" t="n">
-        <v>3.26</v>
+        <v>4.3</v>
       </c>
       <c r="N46" t="n">
-        <v>4</v>
+        <v>5.53</v>
       </c>
       <c r="O46" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="AC46" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AI46" s="3" t="n">
         <v>46084.69791666666</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6010,77 +6010,77 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L47" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="M47" t="n">
         <v>3.2</v>
       </c>
-      <c r="M47" t="n">
-        <v>3.24</v>
-      </c>
       <c r="N47" t="n">
-        <v>2.21</v>
+        <v>2.72</v>
       </c>
       <c r="O47" t="n">
-        <v>3.92</v>
+        <v>3.1</v>
       </c>
       <c r="P47" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="R47" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S47" t="n">
-        <v>2.77</v>
+        <v>2.69</v>
       </c>
       <c r="T47" t="n">
-        <v>2.73</v>
+        <v>2.65</v>
       </c>
       <c r="U47" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="V47" t="n">
-        <v>6.5</v>
+        <v>6.95</v>
       </c>
       <c r="W47" t="n">
         <v>1.04</v>
       </c>
       <c r="X47" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="Z47" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC47" t="n">
         <v>3.2</v>
       </c>
-      <c r="AA47" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>3.3</v>
-      </c>
       <c r="AD47" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG47" t="n">
         <v>1.33</v>
       </c>
-      <c r="AE47" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AF47" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AG47" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH47" t="n">
-        <v>1.31</v>
+        <v>1.53</v>
       </c>
       <c r="AI47" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,73 +6252,73 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.85</v>
+        <v>2.45</v>
       </c>
       <c r="M49" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="N49" t="n">
-        <v>2.24</v>
+        <v>2.7</v>
       </c>
       <c r="O49" t="n">
-        <v>3.7</v>
+        <v>2.95</v>
       </c>
       <c r="P49" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.1</v>
+        <v>3.42</v>
       </c>
       <c r="R49" t="n">
         <v>1.44</v>
       </c>
       <c r="S49" t="n">
-        <v>2.77</v>
+        <v>2.62</v>
       </c>
       <c r="T49" t="n">
-        <v>3.04</v>
+        <v>2.96</v>
       </c>
       <c r="U49" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="V49" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="W49" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X49" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z49" t="n">
-        <v>3.14</v>
+        <v>3.5</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.19</v>
+        <v>2</v>
       </c>
       <c r="AB49" t="n">
         <v>1.71</v>
       </c>
       <c r="AC49" t="n">
-        <v>3.55</v>
+        <v>3.48</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AG49" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="AI49" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,73 +6371,73 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AG50" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH50" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI50" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,73 +6490,73 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.45</v>
+        <v>3.2</v>
       </c>
       <c r="M51" t="n">
-        <v>3</v>
+        <v>3.24</v>
       </c>
       <c r="N51" t="n">
-        <v>2.7</v>
+        <v>2.21</v>
       </c>
       <c r="O51" t="n">
-        <v>2.95</v>
+        <v>3.92</v>
       </c>
       <c r="P51" t="n">
         <v>2.05</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.42</v>
+        <v>2.8</v>
       </c>
       <c r="R51" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="S51" t="n">
-        <v>2.62</v>
+        <v>2.77</v>
       </c>
       <c r="T51" t="n">
-        <v>2.96</v>
+        <v>2.73</v>
       </c>
       <c r="U51" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="V51" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="W51" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X51" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Z51" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="AA51" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.71</v>
+        <v>1.95</v>
       </c>
       <c r="AC51" t="n">
-        <v>3.48</v>
+        <v>3.3</v>
       </c>
       <c r="AD51" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AF51" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AG51" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH51" t="n">
-        <v>1.48</v>
+        <v>1.31</v>
       </c>
       <c r="AI51" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,73 +6609,73 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.45</v>
+        <v>1.8</v>
       </c>
       <c r="M52" t="n">
-        <v>3.2</v>
+        <v>3.26</v>
       </c>
       <c r="N52" t="n">
-        <v>2.72</v>
+        <v>4</v>
       </c>
       <c r="O52" t="n">
-        <v>3.1</v>
+        <v>2.46</v>
       </c>
       <c r="P52" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.5</v>
+        <v>4.25</v>
       </c>
       <c r="R52" t="n">
         <v>1.39</v>
       </c>
       <c r="S52" t="n">
-        <v>2.69</v>
+        <v>2.87</v>
       </c>
       <c r="T52" t="n">
-        <v>2.65</v>
+        <v>2.9</v>
       </c>
       <c r="U52" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="V52" t="n">
-        <v>6.95</v>
+        <v>7.5</v>
       </c>
       <c r="W52" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X52" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="Z52" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AC52" t="n">
-        <v>3.2</v>
+        <v>3.52</v>
       </c>
       <c r="AD52" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AF52" t="n">
-        <v>2.05</v>
+        <v>1.86</v>
       </c>
       <c r="AG52" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.53</v>
+        <v>1.88</v>
       </c>
       <c r="AI52" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,73 +6728,73 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.53</v>
+        <v>2.45</v>
       </c>
       <c r="M53" t="n">
-        <v>3.95</v>
+        <v>3.47</v>
       </c>
       <c r="N53" t="n">
-        <v>5</v>
+        <v>2.59</v>
       </c>
       <c r="O53" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="U53" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="V53" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W53" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X53" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD53" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG53" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AH53" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AI53" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6843,77 +6843,77 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="M54" t="n">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="N54" t="n">
-        <v>2.88</v>
+        <v>3.08</v>
       </c>
       <c r="O54" t="n">
-        <v>2.96</v>
+        <v>2.8</v>
       </c>
       <c r="P54" t="n">
-        <v>2.05</v>
+        <v>2.19</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.67</v>
+        <v>3.5</v>
       </c>
       <c r="R54" t="n">
         <v>1.38</v>
       </c>
       <c r="S54" t="n">
-        <v>2.77</v>
+        <v>2.81</v>
       </c>
       <c r="T54" t="n">
         <v>2.75</v>
       </c>
       <c r="U54" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="V54" t="n">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
       <c r="W54" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X54" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Z54" t="n">
-        <v>3.6</v>
+        <v>3.24</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.93</v>
+        <v>2.03</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AC54" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="AD54" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AF54" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG54" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AH54" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="AI54" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,73 +6966,73 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.91</v>
+        <v>2.45</v>
       </c>
       <c r="M55" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="N55" t="n">
-        <v>3.86</v>
+        <v>2.88</v>
       </c>
       <c r="O55" t="n">
-        <v>2.55</v>
+        <v>2.96</v>
       </c>
       <c r="P55" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="Q55" t="n">
-        <v>4.25</v>
+        <v>3.67</v>
       </c>
       <c r="R55" t="n">
         <v>1.38</v>
       </c>
       <c r="S55" t="n">
-        <v>2.69</v>
+        <v>2.77</v>
       </c>
       <c r="T55" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="U55" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="V55" t="n">
-        <v>7.4</v>
+        <v>6.75</v>
       </c>
       <c r="W55" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X55" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="Z55" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="AA55" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF55" t="n">
         <v>2</v>
       </c>
-      <c r="AB55" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE55" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF55" t="n">
-        <v>1.99</v>
-      </c>
       <c r="AG55" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.73</v>
+        <v>1.52</v>
       </c>
       <c r="AI55" s="3" t="n">
         <v>46084.69791666666</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7200,77 +7200,77 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.1</v>
+        <v>1.53</v>
       </c>
       <c r="M57" t="n">
-        <v>3.38</v>
+        <v>3.95</v>
       </c>
       <c r="N57" t="n">
-        <v>3.08</v>
+        <v>5</v>
       </c>
       <c r="O57" t="n">
-        <v>2.8</v>
+        <v>2.06</v>
       </c>
       <c r="P57" t="n">
-        <v>2.19</v>
+        <v>2.35</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.5</v>
+        <v>5.65</v>
       </c>
       <c r="R57" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="S57" t="n">
-        <v>2.81</v>
+        <v>2.91</v>
       </c>
       <c r="T57" t="n">
-        <v>2.75</v>
+        <v>2.48</v>
       </c>
       <c r="U57" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="V57" t="n">
         <v>6.5</v>
       </c>
       <c r="W57" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="X57" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="Z57" t="n">
-        <v>3.24</v>
+        <v>3.5</v>
       </c>
       <c r="AA57" t="n">
-        <v>2.03</v>
+        <v>1.78</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.73</v>
+        <v>1.93</v>
       </c>
       <c r="AC57" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="AD57" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="AF57" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AG57" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AH57" t="n">
-        <v>1.55</v>
+        <v>2.31</v>
       </c>
       <c r="AI57" s="3" t="n">
         <v>46084.69791666666</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7319,77 +7319,77 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.53</v>
+        <v>2.85</v>
       </c>
       <c r="M58" t="n">
-        <v>4.3</v>
+        <v>3.1</v>
       </c>
       <c r="N58" t="n">
-        <v>5.53</v>
+        <v>2.24</v>
       </c>
       <c r="O58" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S58" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T58" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U58" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V58" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="W58" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X58" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y58" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z58" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.65</v>
+        <v>2.19</v>
       </c>
       <c r="AB58" t="n">
-        <v>2.1</v>
+        <v>1.71</v>
       </c>
       <c r="AC58" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AD58" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE58" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF58" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG58" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH58" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI58" s="3" t="n">
         <v>46084.69791666666</v>

--- a/jogos_2026-03-03.xlsx
+++ b/jogos_2026-03-03.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.81</v>
+        <v>2.5</v>
       </c>
       <c r="M9" t="n">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="N9" t="n">
-        <v>4.55</v>
+        <v>2.8</v>
       </c>
       <c r="O9" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.78</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46084.45833333334</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.5</v>
+        <v>1.81</v>
       </c>
       <c r="M10" t="n">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="N10" t="n">
-        <v>2.8</v>
+        <v>4.55</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>5.78</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46084.45833333334</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.4</v>
+        <v>2.65</v>
       </c>
       <c r="M30" t="n">
-        <v>4.6</v>
+        <v>3.1</v>
       </c>
       <c r="N30" t="n">
-        <v>7.03</v>
+        <v>2.65</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.87</v>
+        <v>3.72</v>
       </c>
       <c r="M31" t="n">
-        <v>3.8</v>
+        <v>3.15</v>
       </c>
       <c r="N31" t="n">
-        <v>2.98</v>
+        <v>2.05</v>
       </c>
       <c r="O31" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46084.66666666666</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.65</v>
+        <v>1.87</v>
       </c>
       <c r="M32" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="N32" t="n">
-        <v>2.65</v>
+        <v>2.98</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46084.66666666666</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.47</v>
+        <v>1.4</v>
       </c>
       <c r="M33" t="n">
-        <v>3.2</v>
+        <v>4.6</v>
       </c>
       <c r="N33" t="n">
-        <v>2.11</v>
+        <v>7.03</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.72</v>
+        <v>3.47</v>
       </c>
       <c r="M34" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="N34" t="n">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4820,77 +4820,77 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.45</v>
+        <v>2.49</v>
       </c>
       <c r="M37" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="N37" t="n">
-        <v>2.43</v>
+        <v>2.86</v>
       </c>
       <c r="O37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46084.6875</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5177,77 +5177,77 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.49</v>
+        <v>2.45</v>
       </c>
       <c r="M40" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="N40" t="n">
-        <v>2.86</v>
+        <v>2.43</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46084.6875</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>5.53</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6010,77 +6010,77 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="M47" t="n">
-        <v>3.2</v>
+        <v>3.38</v>
       </c>
       <c r="N47" t="n">
-        <v>2.72</v>
+        <v>3.08</v>
       </c>
       <c r="O47" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="P47" t="n">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="Q47" t="n">
         <v>3.5</v>
       </c>
       <c r="R47" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S47" t="n">
-        <v>2.69</v>
+        <v>2.81</v>
       </c>
       <c r="T47" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="U47" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="V47" t="n">
-        <v>6.95</v>
+        <v>6.5</v>
       </c>
       <c r="W47" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X47" t="n">
         <v>1.06</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z47" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC47" t="n">
         <v>3.3</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>3.2</v>
       </c>
       <c r="AD47" t="n">
         <v>1.29</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AF47" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AG47" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AI47" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6129,77 +6129,77 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="M48" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="N48" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="O48" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P48" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q48" t="n">
         <v>3.5</v>
       </c>
-      <c r="O48" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="P48" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>4.26</v>
-      </c>
       <c r="R48" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S48" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U48" t="n">
         <v>1.41</v>
       </c>
-      <c r="S48" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="T48" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="U48" t="n">
+      <c r="V48" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="W48" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X48" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG48" t="n">
         <v>1.33</v>
       </c>
-      <c r="V48" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W48" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X48" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AE48" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AF48" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AG48" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AH48" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AI48" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,73 +6252,73 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="M49" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="N49" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="O49" t="n">
-        <v>2.95</v>
+        <v>2.62</v>
       </c>
       <c r="P49" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.42</v>
+        <v>4.26</v>
       </c>
       <c r="R49" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="S49" t="n">
-        <v>2.62</v>
+        <v>2.87</v>
       </c>
       <c r="T49" t="n">
-        <v>2.96</v>
+        <v>2.91</v>
       </c>
       <c r="U49" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="V49" t="n">
-        <v>8</v>
+        <v>7.1</v>
       </c>
       <c r="W49" t="n">
         <v>1.07</v>
       </c>
       <c r="X49" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="Z49" t="n">
-        <v>3.5</v>
+        <v>2.92</v>
       </c>
       <c r="AA49" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AC49" t="n">
-        <v>3.48</v>
+        <v>3.67</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.67</v>
+        <v>1.81</v>
       </c>
       <c r="AF49" t="n">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="AG49" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.48</v>
+        <v>1.62</v>
       </c>
       <c r="AI49" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,73 +6371,73 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.91</v>
+        <v>1.53</v>
       </c>
       <c r="M50" t="n">
-        <v>3.45</v>
+        <v>4.3</v>
       </c>
       <c r="N50" t="n">
-        <v>3.86</v>
+        <v>5.53</v>
       </c>
       <c r="O50" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U50" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V50" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="W50" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z50" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.81</v>
+        <v>2.1</v>
       </c>
       <c r="AC50" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AG50" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AH50" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI50" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6486,77 +6486,77 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="M51" t="n">
-        <v>3.24</v>
+        <v>3.26</v>
       </c>
       <c r="N51" t="n">
-        <v>2.21</v>
+        <v>4</v>
       </c>
       <c r="O51" t="n">
-        <v>3.92</v>
+        <v>2.46</v>
       </c>
       <c r="P51" t="n">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="Q51" t="n">
-        <v>2.8</v>
+        <v>4.25</v>
       </c>
       <c r="R51" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S51" t="n">
-        <v>2.77</v>
+        <v>2.87</v>
       </c>
       <c r="T51" t="n">
-        <v>2.73</v>
+        <v>2.9</v>
       </c>
       <c r="U51" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="V51" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="W51" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X51" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="Z51" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="AA51" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AH51" t="n">
         <v>1.88</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE51" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AF51" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AG51" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH51" t="n">
-        <v>1.31</v>
       </c>
       <c r="AI51" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6605,77 +6605,77 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.8</v>
+        <v>3.2</v>
       </c>
       <c r="M52" t="n">
-        <v>3.26</v>
+        <v>3.24</v>
       </c>
       <c r="N52" t="n">
-        <v>4</v>
+        <v>2.21</v>
       </c>
       <c r="O52" t="n">
-        <v>2.46</v>
+        <v>3.92</v>
       </c>
       <c r="P52" t="n">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="Q52" t="n">
-        <v>4.25</v>
+        <v>2.8</v>
       </c>
       <c r="R52" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S52" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="U52" t="n">
         <v>1.39</v>
       </c>
-      <c r="S52" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="T52" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U52" t="n">
-        <v>1.36</v>
-      </c>
       <c r="V52" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="W52" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X52" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="Z52" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="AA52" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="AC52" t="n">
-        <v>3.52</v>
+        <v>3.3</v>
       </c>
       <c r="AD52" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.86</v>
+        <v>2.02</v>
       </c>
       <c r="AG52" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.88</v>
+        <v>1.31</v>
       </c>
       <c r="AI52" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,73 +6728,73 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.45</v>
+        <v>1.53</v>
       </c>
       <c r="M53" t="n">
-        <v>3.47</v>
+        <v>3.95</v>
       </c>
       <c r="N53" t="n">
-        <v>2.59</v>
+        <v>5</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V53" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W53" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD53" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG53" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH53" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AI53" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6843,77 +6843,77 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="M54" t="n">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="N54" t="n">
-        <v>3.08</v>
+        <v>2.88</v>
       </c>
       <c r="O54" t="n">
-        <v>2.8</v>
+        <v>2.96</v>
       </c>
       <c r="P54" t="n">
-        <v>2.19</v>
+        <v>2.05</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.5</v>
+        <v>3.67</v>
       </c>
       <c r="R54" t="n">
         <v>1.38</v>
       </c>
       <c r="S54" t="n">
-        <v>2.81</v>
+        <v>2.77</v>
       </c>
       <c r="T54" t="n">
         <v>2.75</v>
       </c>
       <c r="U54" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="V54" t="n">
-        <v>6.5</v>
+        <v>6.75</v>
       </c>
       <c r="W54" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X54" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Z54" t="n">
-        <v>3.24</v>
+        <v>3.6</v>
       </c>
       <c r="AA54" t="n">
-        <v>2.03</v>
+        <v>1.93</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AC54" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AD54" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG54" t="n">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="AH54" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AI54" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6969,70 +6969,70 @@
         <v>2.45</v>
       </c>
       <c r="M55" t="n">
-        <v>3.4</v>
+        <v>3.47</v>
       </c>
       <c r="N55" t="n">
-        <v>2.88</v>
+        <v>2.59</v>
       </c>
       <c r="O55" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U55" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V55" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="W55" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X55" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z55" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AD55" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF55" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG55" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AI55" s="3" t="n">
         <v>46084.69791666666</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,73 +7085,73 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S56" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="T56" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U56" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V56" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="W56" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC56" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD56" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE56" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF56" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AG56" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH56" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI56" s="3" t="n">
         <v>46084.69791666666</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7200,77 +7200,77 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.53</v>
+        <v>2.45</v>
       </c>
       <c r="M57" t="n">
-        <v>3.95</v>
+        <v>3</v>
       </c>
       <c r="N57" t="n">
-        <v>5</v>
+        <v>2.7</v>
       </c>
       <c r="O57" t="n">
-        <v>2.06</v>
+        <v>2.95</v>
       </c>
       <c r="P57" t="n">
-        <v>2.35</v>
+        <v>2.05</v>
       </c>
       <c r="Q57" t="n">
-        <v>5.65</v>
+        <v>3.42</v>
       </c>
       <c r="R57" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="S57" t="n">
-        <v>2.91</v>
+        <v>2.62</v>
       </c>
       <c r="T57" t="n">
-        <v>2.48</v>
+        <v>2.96</v>
       </c>
       <c r="U57" t="n">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="V57" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="W57" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X57" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z57" t="n">
         <v>3.5</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.93</v>
+        <v>1.71</v>
       </c>
       <c r="AC57" t="n">
-        <v>3</v>
+        <v>3.48</v>
       </c>
       <c r="AD57" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.84</v>
+        <v>1.67</v>
       </c>
       <c r="AF57" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AG57" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AH57" t="n">
-        <v>2.31</v>
+        <v>1.48</v>
       </c>
       <c r="AI57" s="3" t="n">
         <v>46084.69791666666</v>

--- a/jogos_2026-03-03.xlsx
+++ b/jogos_2026-03-03.xlsx
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.8</v>
+        <v>4.5</v>
       </c>
       <c r="M23" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N23" t="n">
-        <v>2.5</v>
+        <v>1.62</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.65</v>
+        <v>1.4</v>
       </c>
       <c r="M30" t="n">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="N30" t="n">
-        <v>2.65</v>
+        <v>7.03</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.4</v>
+        <v>3.47</v>
       </c>
       <c r="M33" t="n">
-        <v>4.6</v>
+        <v>3.2</v>
       </c>
       <c r="N33" t="n">
-        <v>7.03</v>
+        <v>2.11</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.47</v>
+        <v>2.65</v>
       </c>
       <c r="M34" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N34" t="n">
-        <v>2.11</v>
+        <v>2.65</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.75</v>
+        <v>2.49</v>
       </c>
       <c r="M35" t="n">
-        <v>3.91</v>
+        <v>3.8</v>
       </c>
       <c r="N35" t="n">
-        <v>5.33</v>
+        <v>2.86</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5177,77 +5177,77 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46084.6875</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5296,77 +5296,77 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46084.6875</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5891,77 +5891,77 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH46" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI46" s="3" t="n">
         <v>46084.69791666666</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6010,77 +6010,77 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="M47" t="n">
-        <v>3.38</v>
+        <v>3.26</v>
       </c>
       <c r="N47" t="n">
-        <v>3.08</v>
+        <v>4</v>
       </c>
       <c r="O47" t="n">
-        <v>2.8</v>
+        <v>2.46</v>
       </c>
       <c r="P47" t="n">
-        <v>2.19</v>
+        <v>2.09</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.5</v>
+        <v>4.25</v>
       </c>
       <c r="R47" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S47" t="n">
-        <v>2.81</v>
+        <v>2.87</v>
       </c>
       <c r="T47" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="U47" t="n">
         <v>1.36</v>
       </c>
       <c r="V47" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="W47" t="n">
         <v>1.03</v>
       </c>
       <c r="X47" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="Z47" t="n">
-        <v>3.24</v>
+        <v>3.05</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AC47" t="n">
-        <v>3.3</v>
+        <v>3.52</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AG47" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.55</v>
+        <v>1.88</v>
       </c>
       <c r="AI47" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6129,77 +6129,77 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.45</v>
+        <v>3.2</v>
       </c>
       <c r="M48" t="n">
-        <v>3.2</v>
+        <v>3.24</v>
       </c>
       <c r="N48" t="n">
-        <v>2.72</v>
+        <v>2.21</v>
       </c>
       <c r="O48" t="n">
-        <v>3.1</v>
+        <v>3.92</v>
       </c>
       <c r="P48" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="R48" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S48" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="U48" t="n">
         <v>1.39</v>
       </c>
-      <c r="S48" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="T48" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U48" t="n">
-        <v>1.41</v>
-      </c>
       <c r="V48" t="n">
-        <v>6.95</v>
+        <v>6.5</v>
       </c>
       <c r="W48" t="n">
         <v>1.04</v>
       </c>
       <c r="X48" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y48" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH48" t="n">
         <v>1.31</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE48" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF48" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG48" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH48" t="n">
-        <v>1.53</v>
       </c>
       <c r="AI48" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6248,77 +6248,77 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2</v>
+        <v>1.53</v>
       </c>
       <c r="M49" t="n">
-        <v>3.25</v>
+        <v>3.95</v>
       </c>
       <c r="N49" t="n">
+        <v>5</v>
+      </c>
+      <c r="O49" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="P49" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="R49" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S49" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V49" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W49" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z49" t="n">
         <v>3.5</v>
       </c>
-      <c r="O49" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="P49" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>4.26</v>
-      </c>
-      <c r="R49" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S49" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="T49" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="U49" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V49" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W49" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X49" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>2.92</v>
-      </c>
       <c r="AA49" t="n">
-        <v>2.07</v>
+        <v>1.78</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.72</v>
+        <v>1.93</v>
       </c>
       <c r="AC49" t="n">
-        <v>3.67</v>
+        <v>3</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="AG49" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.62</v>
+        <v>2.31</v>
       </c>
       <c r="AI49" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,73 +6371,73 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="M50" t="n">
-        <v>4.3</v>
+        <v>3.45</v>
       </c>
       <c r="N50" t="n">
-        <v>5.53</v>
+        <v>3.86</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="AB50" t="n">
-        <v>2.1</v>
+        <v>1.81</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AG50" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH50" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI50" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,73 +6490,73 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="M51" t="n">
-        <v>3.26</v>
+        <v>4.3</v>
       </c>
       <c r="N51" t="n">
-        <v>4</v>
+        <v>5.53</v>
       </c>
       <c r="O51" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U51" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V51" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="W51" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z51" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="AC51" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="AD51" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG51" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH51" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AI51" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6605,77 +6605,77 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>3.2</v>
+        <v>2.45</v>
       </c>
       <c r="M52" t="n">
-        <v>3.24</v>
+        <v>3.47</v>
       </c>
       <c r="N52" t="n">
-        <v>2.21</v>
+        <v>2.59</v>
       </c>
       <c r="O52" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="U52" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V52" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W52" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X52" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z52" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD52" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF52" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AG52" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AI52" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6724,77 +6724,77 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.53</v>
+        <v>2</v>
       </c>
       <c r="M53" t="n">
-        <v>3.95</v>
+        <v>3.25</v>
       </c>
       <c r="N53" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="O53" t="n">
-        <v>2.06</v>
+        <v>2.62</v>
       </c>
       <c r="P53" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="Q53" t="n">
-        <v>5.65</v>
+        <v>4.26</v>
       </c>
       <c r="R53" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S53" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="U53" t="n">
         <v>1.33</v>
       </c>
-      <c r="S53" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="T53" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="U53" t="n">
-        <v>1.41</v>
-      </c>
       <c r="V53" t="n">
-        <v>6.5</v>
+        <v>7.1</v>
       </c>
       <c r="W53" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X53" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.24</v>
+        <v>1.34</v>
       </c>
       <c r="Z53" t="n">
-        <v>3.5</v>
+        <v>2.92</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.78</v>
+        <v>2.07</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.93</v>
+        <v>1.72</v>
       </c>
       <c r="AC53" t="n">
-        <v>3</v>
+        <v>3.67</v>
       </c>
       <c r="AD53" t="n">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="AG53" t="n">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="AH53" t="n">
-        <v>2.31</v>
+        <v>1.62</v>
       </c>
       <c r="AI53" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6850,70 +6850,70 @@
         <v>2.45</v>
       </c>
       <c r="M54" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="N54" t="n">
-        <v>2.88</v>
+        <v>2.72</v>
       </c>
       <c r="O54" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="P54" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.67</v>
+        <v>3.5</v>
       </c>
       <c r="R54" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S54" t="n">
-        <v>2.77</v>
+        <v>2.69</v>
       </c>
       <c r="T54" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="U54" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="V54" t="n">
-        <v>6.75</v>
+        <v>6.95</v>
       </c>
       <c r="W54" t="n">
         <v>1.04</v>
       </c>
       <c r="X54" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="Z54" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AC54" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="AD54" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AF54" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AG54" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AH54" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AI54" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7081,77 +7081,77 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="M56" t="n">
-        <v>3.45</v>
+        <v>3.38</v>
       </c>
       <c r="N56" t="n">
-        <v>3.86</v>
+        <v>3.08</v>
       </c>
       <c r="O56" t="n">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="P56" t="n">
-        <v>2.11</v>
+        <v>2.19</v>
       </c>
       <c r="Q56" t="n">
-        <v>4.25</v>
+        <v>3.5</v>
       </c>
       <c r="R56" t="n">
         <v>1.38</v>
       </c>
       <c r="S56" t="n">
-        <v>2.69</v>
+        <v>2.81</v>
       </c>
       <c r="T56" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="U56" t="n">
         <v>1.36</v>
       </c>
       <c r="V56" t="n">
-        <v>7.4</v>
+        <v>6.5</v>
       </c>
       <c r="W56" t="n">
         <v>1.03</v>
       </c>
       <c r="X56" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z56" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="AA56" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="AC56" t="n">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="AD56" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG56" t="n">
         <v>1.24</v>
       </c>
-      <c r="AE56" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF56" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AG56" t="n">
-        <v>1.34</v>
-      </c>
       <c r="AH56" t="n">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="AI56" s="3" t="n">
         <v>46084.69791666666</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7319,77 +7319,77 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.85</v>
+        <v>2.45</v>
       </c>
       <c r="M58" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="N58" t="n">
-        <v>2.24</v>
+        <v>2.88</v>
       </c>
       <c r="O58" t="n">
-        <v>3.7</v>
+        <v>2.96</v>
       </c>
       <c r="P58" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.1</v>
+        <v>3.67</v>
       </c>
       <c r="R58" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="S58" t="n">
         <v>2.77</v>
       </c>
       <c r="T58" t="n">
-        <v>3.04</v>
+        <v>2.75</v>
       </c>
       <c r="U58" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="V58" t="n">
-        <v>7.6</v>
+        <v>6.75</v>
       </c>
       <c r="W58" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X58" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Z58" t="n">
-        <v>3.14</v>
+        <v>3.6</v>
       </c>
       <c r="AA58" t="n">
-        <v>2.19</v>
+        <v>1.93</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.71</v>
+        <v>1.85</v>
       </c>
       <c r="AC58" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="AD58" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AE58" t="n">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="AF58" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AG58" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AH58" t="n">
-        <v>1.38</v>
+        <v>1.52</v>
       </c>
       <c r="AI58" s="3" t="n">
         <v>46084.69791666666</v>

--- a/jogos_2026-03-03.xlsx
+++ b/jogos_2026-03-03.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.5</v>
+        <v>1.81</v>
       </c>
       <c r="M9" t="n">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="N9" t="n">
-        <v>2.8</v>
+        <v>4.55</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>5.78</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46084.45833333334</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.81</v>
+        <v>2.5</v>
       </c>
       <c r="M10" t="n">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="N10" t="n">
-        <v>4.55</v>
+        <v>2.8</v>
       </c>
       <c r="O10" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.78</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46084.45833333334</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.4</v>
+        <v>2.65</v>
       </c>
       <c r="M30" t="n">
-        <v>4.6</v>
+        <v>3.1</v>
       </c>
       <c r="N30" t="n">
-        <v>7.03</v>
+        <v>2.65</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.72</v>
+        <v>3.47</v>
       </c>
       <c r="M31" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="N31" t="n">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.87</v>
+        <v>1.4</v>
       </c>
       <c r="M32" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="N32" t="n">
-        <v>2.98</v>
+        <v>7.03</v>
       </c>
       <c r="O32" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46084.66666666666</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.47</v>
+        <v>3.72</v>
       </c>
       <c r="M33" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="N33" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.65</v>
+        <v>1.87</v>
       </c>
       <c r="M34" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="N34" t="n">
-        <v>2.65</v>
+        <v>2.98</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46084.66666666666</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5177,77 +5177,77 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46084.6875</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5296,77 +5296,77 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.45</v>
+        <v>4.28</v>
       </c>
       <c r="M41" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="N41" t="n">
-        <v>2.43</v>
+        <v>1.66</v>
       </c>
       <c r="O41" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46084.6875</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>5.33</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,73 +5895,73 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.85</v>
+        <v>3.2</v>
       </c>
       <c r="M46" t="n">
-        <v>3.1</v>
+        <v>3.24</v>
       </c>
       <c r="N46" t="n">
-        <v>2.24</v>
+        <v>2.21</v>
       </c>
       <c r="O46" t="n">
-        <v>3.7</v>
+        <v>3.92</v>
       </c>
       <c r="P46" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="R46" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="S46" t="n">
         <v>2.77</v>
       </c>
       <c r="T46" t="n">
-        <v>3.04</v>
+        <v>2.73</v>
       </c>
       <c r="U46" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="V46" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W46" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD46" t="n">
         <v>1.33</v>
       </c>
-      <c r="V46" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="W46" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X46" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y46" t="n">
+      <c r="AE46" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AG46" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z46" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AE46" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AF46" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AG46" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AH46" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="AI46" s="3" t="n">
         <v>46084.69791666666</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,73 +6014,73 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AI47" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6129,77 +6129,77 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="M48" t="n">
-        <v>3.24</v>
+        <v>3.26</v>
       </c>
       <c r="N48" t="n">
-        <v>2.21</v>
+        <v>4</v>
       </c>
       <c r="O48" t="n">
-        <v>3.92</v>
+        <v>2.46</v>
       </c>
       <c r="P48" t="n">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.8</v>
+        <v>4.25</v>
       </c>
       <c r="R48" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S48" t="n">
-        <v>2.77</v>
+        <v>2.87</v>
       </c>
       <c r="T48" t="n">
-        <v>2.73</v>
+        <v>2.9</v>
       </c>
       <c r="U48" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="V48" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="W48" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X48" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="Z48" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="AA48" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AH48" t="n">
         <v>1.88</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE48" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AF48" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AG48" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH48" t="n">
-        <v>1.31</v>
       </c>
       <c r="AI48" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,73 +6252,73 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="M49" t="n">
-        <v>3.95</v>
+        <v>3.45</v>
       </c>
       <c r="N49" t="n">
-        <v>5</v>
+        <v>3.86</v>
       </c>
       <c r="O49" t="n">
-        <v>2.06</v>
+        <v>2.55</v>
       </c>
       <c r="P49" t="n">
-        <v>2.35</v>
+        <v>2.11</v>
       </c>
       <c r="Q49" t="n">
-        <v>5.65</v>
+        <v>4.25</v>
       </c>
       <c r="R49" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S49" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V49" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="W49" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X49" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y49" t="n">
         <v>1.33</v>
       </c>
-      <c r="S49" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="T49" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="U49" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="V49" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W49" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X49" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y49" t="n">
+      <c r="Z49" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AD49" t="n">
         <v>1.24</v>
       </c>
-      <c r="Z49" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AE49" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.85</v>
+        <v>1.99</v>
       </c>
       <c r="AG49" t="n">
-        <v>1.17</v>
+        <v>1.34</v>
       </c>
       <c r="AH49" t="n">
-        <v>2.31</v>
+        <v>1.73</v>
       </c>
       <c r="AI49" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6367,77 +6367,77 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="M50" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="N50" t="n">
-        <v>3.86</v>
+        <v>3.5</v>
       </c>
       <c r="O50" t="n">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="P50" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="Q50" t="n">
-        <v>4.25</v>
+        <v>4.26</v>
       </c>
       <c r="R50" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="S50" t="n">
-        <v>2.69</v>
+        <v>2.87</v>
       </c>
       <c r="T50" t="n">
-        <v>2.65</v>
+        <v>2.91</v>
       </c>
       <c r="U50" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V50" t="n">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
       <c r="W50" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X50" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Z50" t="n">
-        <v>3.25</v>
+        <v>2.92</v>
       </c>
       <c r="AA50" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AB50" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AE50" t="n">
         <v>1.81</v>
       </c>
-      <c r="AC50" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE50" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AF50" t="n">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="AG50" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="AH50" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AI50" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,73 +6490,73 @@
         </is>
       </c>
       <c r="L51" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="M51" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N51" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="O51" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P51" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R51" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S51" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V51" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="W51" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X51" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH51" t="n">
         <v>1.53</v>
-      </c>
-      <c r="M51" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="N51" t="n">
-        <v>5.53</v>
-      </c>
-      <c r="O51" t="n">
-        <v>0</v>
-      </c>
-      <c r="P51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
-      <c r="R51" t="n">
-        <v>0</v>
-      </c>
-      <c r="S51" t="n">
-        <v>0</v>
-      </c>
-      <c r="T51" t="n">
-        <v>0</v>
-      </c>
-      <c r="U51" t="n">
-        <v>0</v>
-      </c>
-      <c r="V51" t="n">
-        <v>0</v>
-      </c>
-      <c r="W51" t="n">
-        <v>0</v>
-      </c>
-      <c r="X51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH51" t="n">
-        <v>0</v>
       </c>
       <c r="AI51" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.45</v>
+        <v>1.53</v>
       </c>
       <c r="M52" t="n">
-        <v>3.47</v>
+        <v>4.3</v>
       </c>
       <c r="N52" t="n">
-        <v>2.59</v>
+        <v>5.53</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6724,77 +6724,77 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L53" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="M53" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N53" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="O53" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="P53" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="R53" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S53" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V53" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="W53" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X53" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF53" t="n">
         <v>2</v>
       </c>
-      <c r="M53" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N53" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O53" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="P53" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>4.26</v>
-      </c>
-      <c r="R53" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S53" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="T53" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="U53" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V53" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W53" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X53" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y53" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AE53" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AF53" t="n">
-        <v>1.96</v>
-      </c>
       <c r="AG53" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AH53" t="n">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="AI53" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,73 +6847,73 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.45</v>
+        <v>1.53</v>
       </c>
       <c r="M54" t="n">
-        <v>3.2</v>
+        <v>3.95</v>
       </c>
       <c r="N54" t="n">
-        <v>2.72</v>
+        <v>5</v>
       </c>
       <c r="O54" t="n">
-        <v>3.1</v>
+        <v>2.06</v>
       </c>
       <c r="P54" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.5</v>
+        <v>5.65</v>
       </c>
       <c r="R54" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="S54" t="n">
-        <v>2.69</v>
+        <v>2.91</v>
       </c>
       <c r="T54" t="n">
-        <v>2.65</v>
+        <v>2.48</v>
       </c>
       <c r="U54" t="n">
         <v>1.41</v>
       </c>
       <c r="V54" t="n">
-        <v>6.95</v>
+        <v>6.5</v>
       </c>
       <c r="W54" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="X54" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="Z54" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.98</v>
+        <v>1.78</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.75</v>
+        <v>1.93</v>
       </c>
       <c r="AC54" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AD54" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="AF54" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AG54" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AH54" t="n">
-        <v>1.53</v>
+        <v>2.31</v>
       </c>
       <c r="AI54" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6962,77 +6962,77 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S55" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T55" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U55" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V55" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W55" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X55" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC55" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AD55" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG55" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH55" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AI55" s="3" t="n">
         <v>46084.69791666666</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7081,77 +7081,77 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="M56" t="n">
-        <v>3.38</v>
+        <v>3.47</v>
       </c>
       <c r="N56" t="n">
-        <v>3.08</v>
+        <v>2.59</v>
       </c>
       <c r="O56" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U56" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V56" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W56" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X56" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z56" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC56" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD56" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF56" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG56" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH56" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI56" s="3" t="n">
         <v>46084.69791666666</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,73 +7204,73 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="M57" t="n">
-        <v>3</v>
+        <v>3.38</v>
       </c>
       <c r="N57" t="n">
-        <v>2.7</v>
+        <v>3.08</v>
       </c>
       <c r="O57" t="n">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="P57" t="n">
-        <v>2.05</v>
+        <v>2.19</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="R57" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="S57" t="n">
-        <v>2.62</v>
+        <v>2.81</v>
       </c>
       <c r="T57" t="n">
-        <v>2.96</v>
+        <v>2.75</v>
       </c>
       <c r="U57" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="V57" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="W57" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X57" t="n">
         <v>1.06</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Z57" t="n">
-        <v>3.5</v>
+        <v>3.24</v>
       </c>
       <c r="AA57" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AC57" t="n">
-        <v>3.48</v>
+        <v>3.3</v>
       </c>
       <c r="AD57" t="n">
         <v>1.29</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AF57" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AG57" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AH57" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AI57" s="3" t="n">
         <v>46084.69791666666</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7319,77 +7319,77 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.45</v>
+        <v>2.85</v>
       </c>
       <c r="M58" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="N58" t="n">
-        <v>2.88</v>
+        <v>2.24</v>
       </c>
       <c r="O58" t="n">
-        <v>2.96</v>
+        <v>3.7</v>
       </c>
       <c r="P58" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.67</v>
+        <v>3.1</v>
       </c>
       <c r="R58" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="S58" t="n">
         <v>2.77</v>
       </c>
       <c r="T58" t="n">
-        <v>2.75</v>
+        <v>3.04</v>
       </c>
       <c r="U58" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V58" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="W58" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X58" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE58" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AF58" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AG58" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH58" t="n">
         <v>1.38</v>
-      </c>
-      <c r="V58" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="W58" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X58" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y58" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z58" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AA58" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AB58" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC58" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AD58" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AE58" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AF58" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG58" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AH58" t="n">
-        <v>1.52</v>
       </c>
       <c r="AI58" s="3" t="n">
         <v>46084.69791666666</v>

--- a/jogos_2026-03-03.xlsx
+++ b/jogos_2026-03-03.xlsx
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.81</v>
+        <v>2.5</v>
       </c>
       <c r="M9" t="n">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="N9" t="n">
-        <v>4.55</v>
+        <v>2.8</v>
       </c>
       <c r="O9" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.78</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46084.45833333334</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.5</v>
+        <v>1.81</v>
       </c>
       <c r="M10" t="n">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="N10" t="n">
-        <v>2.8</v>
+        <v>4.55</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>5.78</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46084.45833333334</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.65</v>
+        <v>3.72</v>
       </c>
       <c r="M30" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="N30" t="n">
-        <v>2.65</v>
+        <v>2.05</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.47</v>
+        <v>1.87</v>
       </c>
       <c r="M31" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="N31" t="n">
-        <v>2.11</v>
+        <v>2.98</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46084.66666666666</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.72</v>
+        <v>3.47</v>
       </c>
       <c r="M33" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="N33" t="n">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.87</v>
+        <v>2.65</v>
       </c>
       <c r="M34" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="N34" t="n">
-        <v>2.98</v>
+        <v>2.65</v>
       </c>
       <c r="O34" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46084.66666666666</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>5.33</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4820,77 +4820,77 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.49</v>
+        <v>2.45</v>
       </c>
       <c r="M37" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="N37" t="n">
-        <v>2.86</v>
+        <v>2.43</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46084.6875</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5177,77 +5177,77 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.45</v>
+        <v>1.75</v>
       </c>
       <c r="M40" t="n">
-        <v>3.3</v>
+        <v>3.91</v>
       </c>
       <c r="N40" t="n">
-        <v>2.43</v>
+        <v>5.33</v>
       </c>
       <c r="O40" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46084.6875</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>4.28</v>
+        <v>2.05</v>
       </c>
       <c r="M41" t="n">
-        <v>4.2</v>
+        <v>3.56</v>
       </c>
       <c r="N41" t="n">
-        <v>1.66</v>
+        <v>4.05</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5891,77 +5891,77 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>3.2</v>
+        <v>2.45</v>
       </c>
       <c r="M46" t="n">
-        <v>3.24</v>
+        <v>3.47</v>
       </c>
       <c r="N46" t="n">
-        <v>2.21</v>
+        <v>2.59</v>
       </c>
       <c r="O46" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AI46" s="3" t="n">
         <v>46084.69791666666</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,73 +6014,73 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AI47" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6129,77 +6129,77 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="M48" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="N48" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="O48" t="n">
-        <v>2.46</v>
+        <v>2.62</v>
       </c>
       <c r="P48" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="Q48" t="n">
-        <v>4.25</v>
+        <v>4.26</v>
       </c>
       <c r="R48" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="S48" t="n">
         <v>2.87</v>
       </c>
       <c r="T48" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="U48" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V48" t="n">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
       <c r="W48" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X48" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="Z48" t="n">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="AA48" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AC48" t="n">
-        <v>3.52</v>
+        <v>3.67</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.86</v>
+        <v>1.96</v>
       </c>
       <c r="AG48" t="n">
         <v>1.27</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.88</v>
+        <v>1.62</v>
       </c>
       <c r="AI48" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,73 +6252,73 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U49" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V49" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="W49" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z49" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AG49" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI49" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,73 +6371,73 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="M50" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="N50" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="O50" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="P50" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="R50" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S50" t="n">
         <v>2.62</v>
       </c>
-      <c r="P50" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>4.26</v>
-      </c>
-      <c r="R50" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S50" t="n">
-        <v>2.87</v>
-      </c>
       <c r="T50" t="n">
-        <v>2.91</v>
+        <v>2.96</v>
       </c>
       <c r="U50" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="V50" t="n">
-        <v>7.1</v>
+        <v>8</v>
       </c>
       <c r="W50" t="n">
         <v>1.07</v>
       </c>
       <c r="X50" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="Z50" t="n">
-        <v>2.92</v>
+        <v>3.5</v>
       </c>
       <c r="AA50" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AC50" t="n">
-        <v>3.67</v>
+        <v>3.48</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="AG50" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AH50" t="n">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="AI50" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6486,77 +6486,77 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="M51" t="n">
-        <v>3.2</v>
+        <v>3.38</v>
       </c>
       <c r="N51" t="n">
-        <v>2.72</v>
+        <v>3.08</v>
       </c>
       <c r="O51" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="P51" t="n">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="Q51" t="n">
         <v>3.5</v>
       </c>
       <c r="R51" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S51" t="n">
-        <v>2.69</v>
+        <v>2.81</v>
       </c>
       <c r="T51" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="U51" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="V51" t="n">
-        <v>6.95</v>
+        <v>6.5</v>
       </c>
       <c r="W51" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X51" t="n">
         <v>1.06</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z51" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC51" t="n">
         <v>3.3</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>3.2</v>
       </c>
       <c r="AD51" t="n">
         <v>1.29</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AF51" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AG51" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AH51" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AI51" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6612,70 +6612,70 @@
         <v>1.53</v>
       </c>
       <c r="M52" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="N52" t="n">
-        <v>5.53</v>
+        <v>5</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S52" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="T52" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U52" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V52" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W52" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="AB52" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AC52" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD52" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG52" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH52" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AI52" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,73 +6728,73 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.45</v>
+        <v>1.53</v>
       </c>
       <c r="M53" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="N53" t="n">
-        <v>2.88</v>
+        <v>5.53</v>
       </c>
       <c r="O53" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U53" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V53" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="W53" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X53" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.93</v>
+        <v>1.65</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AC53" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AD53" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG53" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH53" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AI53" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6843,77 +6843,77 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.53</v>
+        <v>3.2</v>
       </c>
       <c r="M54" t="n">
-        <v>3.95</v>
+        <v>3.24</v>
       </c>
       <c r="N54" t="n">
-        <v>5</v>
+        <v>2.21</v>
       </c>
       <c r="O54" t="n">
-        <v>2.06</v>
+        <v>3.92</v>
       </c>
       <c r="P54" t="n">
-        <v>2.35</v>
+        <v>2.05</v>
       </c>
       <c r="Q54" t="n">
-        <v>5.65</v>
+        <v>2.8</v>
       </c>
       <c r="R54" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="S54" t="n">
-        <v>2.91</v>
+        <v>2.77</v>
       </c>
       <c r="T54" t="n">
-        <v>2.48</v>
+        <v>2.73</v>
       </c>
       <c r="U54" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="V54" t="n">
         <v>6.5</v>
       </c>
       <c r="W54" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="X54" t="n">
         <v>1.01</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Z54" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AC54" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="AD54" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.85</v>
+        <v>2.02</v>
       </c>
       <c r="AG54" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AH54" t="n">
-        <v>2.31</v>
+        <v>1.31</v>
       </c>
       <c r="AI54" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6962,77 +6962,77 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L55" t="n">
         <v>2.45</v>
       </c>
       <c r="M55" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="N55" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="O55" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="P55" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="R55" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="S55" t="n">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="T55" t="n">
-        <v>2.96</v>
+        <v>2.65</v>
       </c>
       <c r="U55" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="V55" t="n">
-        <v>8</v>
+        <v>6.95</v>
       </c>
       <c r="W55" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X55" t="n">
         <v>1.06</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="Z55" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AA55" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AC55" t="n">
-        <v>3.48</v>
+        <v>3.2</v>
       </c>
       <c r="AD55" t="n">
         <v>1.29</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AF55" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AG55" t="n">
         <v>1.33</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AI55" s="3" t="n">
         <v>46084.69791666666</v>
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,73 +7085,73 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.45</v>
+        <v>1.91</v>
       </c>
       <c r="M56" t="n">
-        <v>3.47</v>
+        <v>3.45</v>
       </c>
       <c r="N56" t="n">
-        <v>2.59</v>
+        <v>3.86</v>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S56" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="T56" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U56" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V56" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="W56" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC56" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD56" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE56" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF56" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AG56" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH56" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI56" s="3" t="n">
         <v>46084.69791666666</v>
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,73 +7204,73 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.1</v>
+        <v>2.85</v>
       </c>
       <c r="M57" t="n">
-        <v>3.38</v>
+        <v>3.1</v>
       </c>
       <c r="N57" t="n">
-        <v>3.08</v>
+        <v>2.24</v>
       </c>
       <c r="O57" t="n">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="P57" t="n">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="R57" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="S57" t="n">
-        <v>2.81</v>
+        <v>2.77</v>
       </c>
       <c r="T57" t="n">
-        <v>2.75</v>
+        <v>3.04</v>
       </c>
       <c r="U57" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V57" t="n">
-        <v>6.5</v>
+        <v>7.6</v>
       </c>
       <c r="W57" t="n">
         <v>1.03</v>
       </c>
       <c r="X57" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y57" t="n">
         <v>1.3</v>
       </c>
       <c r="Z57" t="n">
-        <v>3.24</v>
+        <v>3.14</v>
       </c>
       <c r="AA57" t="n">
-        <v>2.03</v>
+        <v>2.19</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AC57" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="AD57" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AG57" t="n">
         <v>1.29</v>
       </c>
-      <c r="AE57" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF57" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG57" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AH57" t="n">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="AI57" s="3" t="n">
         <v>46084.69791666666</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7319,77 +7319,77 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.85</v>
+        <v>1.8</v>
       </c>
       <c r="M58" t="n">
-        <v>3.1</v>
+        <v>3.26</v>
       </c>
       <c r="N58" t="n">
-        <v>2.24</v>
+        <v>4</v>
       </c>
       <c r="O58" t="n">
-        <v>3.7</v>
+        <v>2.46</v>
       </c>
       <c r="P58" t="n">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.1</v>
+        <v>4.25</v>
       </c>
       <c r="R58" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="S58" t="n">
-        <v>2.77</v>
+        <v>2.87</v>
       </c>
       <c r="T58" t="n">
-        <v>3.04</v>
+        <v>2.9</v>
       </c>
       <c r="U58" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V58" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="W58" t="n">
         <v>1.03</v>
       </c>
       <c r="X58" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="Z58" t="n">
-        <v>3.14</v>
+        <v>3.05</v>
       </c>
       <c r="AA58" t="n">
-        <v>2.19</v>
+        <v>2</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AC58" t="n">
-        <v>3.55</v>
+        <v>3.52</v>
       </c>
       <c r="AD58" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AE58" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AF58" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AG58" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AH58" t="n">
-        <v>1.38</v>
+        <v>1.88</v>
       </c>
       <c r="AI58" s="3" t="n">
         <v>46084.69791666666</v>

--- a/jogos_2026-03-03.xlsx
+++ b/jogos_2026-03-03.xlsx
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.4</v>
+        <v>3.47</v>
       </c>
       <c r="M32" t="n">
-        <v>4.6</v>
+        <v>3.2</v>
       </c>
       <c r="N32" t="n">
-        <v>7.03</v>
+        <v>2.11</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.47</v>
+        <v>1.4</v>
       </c>
       <c r="M33" t="n">
-        <v>3.2</v>
+        <v>4.6</v>
       </c>
       <c r="N33" t="n">
-        <v>2.11</v>
+        <v>7.03</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4820,77 +4820,77 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46084.6875</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5058,77 +5058,77 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>4.28</v>
+        <v>2.45</v>
       </c>
       <c r="M39" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="N39" t="n">
-        <v>1.66</v>
+        <v>2.43</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46084.6875</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="M40" t="n">
-        <v>3.91</v>
+        <v>3.56</v>
       </c>
       <c r="N40" t="n">
-        <v>5.33</v>
+        <v>4.05</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.85</v>
+        <v>1.63</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5898,70 +5898,70 @@
         <v>2.45</v>
       </c>
       <c r="M46" t="n">
-        <v>3.47</v>
+        <v>3.2</v>
       </c>
       <c r="N46" t="n">
-        <v>2.59</v>
+        <v>2.72</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH46" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI46" s="3" t="n">
         <v>46084.69791666666</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6010,77 +6010,77 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L47" t="n">
         <v>2.45</v>
       </c>
       <c r="M47" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="N47" t="n">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="O47" t="n">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="P47" t="n">
         <v>2.05</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.67</v>
+        <v>3.42</v>
       </c>
       <c r="R47" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="S47" t="n">
-        <v>2.77</v>
+        <v>2.62</v>
       </c>
       <c r="T47" t="n">
-        <v>2.75</v>
+        <v>2.96</v>
       </c>
       <c r="U47" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="V47" t="n">
-        <v>6.75</v>
+        <v>8</v>
       </c>
       <c r="W47" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X47" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z47" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AC47" t="n">
-        <v>3.35</v>
+        <v>3.48</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AF47" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AG47" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="AI47" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6129,77 +6129,77 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2</v>
+        <v>1.53</v>
       </c>
       <c r="M48" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="N48" t="n">
-        <v>3.5</v>
+        <v>5.53</v>
       </c>
       <c r="O48" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>4.26</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X48" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.07</v>
+        <v>1.65</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.72</v>
+        <v>2.1</v>
       </c>
       <c r="AC48" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG48" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI48" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,73 +6252,73 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH49" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AI49" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,73 +6371,73 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.45</v>
+        <v>3.2</v>
       </c>
       <c r="M50" t="n">
-        <v>3</v>
+        <v>3.24</v>
       </c>
       <c r="N50" t="n">
-        <v>2.7</v>
+        <v>2.21</v>
       </c>
       <c r="O50" t="n">
-        <v>2.95</v>
+        <v>3.92</v>
       </c>
       <c r="P50" t="n">
         <v>2.05</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.42</v>
+        <v>2.8</v>
       </c>
       <c r="R50" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="S50" t="n">
-        <v>2.62</v>
+        <v>2.77</v>
       </c>
       <c r="T50" t="n">
-        <v>2.96</v>
+        <v>2.73</v>
       </c>
       <c r="U50" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="V50" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="W50" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X50" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Z50" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="AA50" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.71</v>
+        <v>1.95</v>
       </c>
       <c r="AC50" t="n">
-        <v>3.48</v>
+        <v>3.3</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AF50" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AG50" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH50" t="n">
-        <v>1.48</v>
+        <v>1.31</v>
       </c>
       <c r="AI50" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6486,77 +6486,77 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="M51" t="n">
-        <v>3.38</v>
+        <v>3.45</v>
       </c>
       <c r="N51" t="n">
-        <v>3.08</v>
+        <v>3.86</v>
       </c>
       <c r="O51" t="n">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="P51" t="n">
-        <v>2.19</v>
+        <v>2.11</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.5</v>
+        <v>4.25</v>
       </c>
       <c r="R51" t="n">
         <v>1.38</v>
       </c>
       <c r="S51" t="n">
-        <v>2.81</v>
+        <v>2.69</v>
       </c>
       <c r="T51" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="U51" t="n">
         <v>1.36</v>
       </c>
       <c r="V51" t="n">
-        <v>6.5</v>
+        <v>7.4</v>
       </c>
       <c r="W51" t="n">
         <v>1.03</v>
       </c>
       <c r="X51" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z51" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="AA51" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AB51" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AH51" t="n">
         <v>1.73</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE51" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF51" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG51" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AH51" t="n">
-        <v>1.55</v>
       </c>
       <c r="AI51" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,73 +6609,73 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="U52" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="V52" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W52" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X52" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Z52" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD52" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG52" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AH52" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AI52" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6731,70 +6731,70 @@
         <v>1.53</v>
       </c>
       <c r="M53" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="N53" t="n">
-        <v>5.53</v>
+        <v>5</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V53" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W53" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="AB53" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD53" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG53" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH53" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AI53" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,73 +6847,73 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="M54" t="n">
-        <v>3.24</v>
+        <v>3.38</v>
       </c>
       <c r="N54" t="n">
-        <v>2.21</v>
+        <v>3.08</v>
       </c>
       <c r="O54" t="n">
-        <v>3.92</v>
+        <v>2.8</v>
       </c>
       <c r="P54" t="n">
-        <v>2.05</v>
+        <v>2.19</v>
       </c>
       <c r="Q54" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="R54" t="n">
         <v>1.38</v>
       </c>
       <c r="S54" t="n">
-        <v>2.77</v>
+        <v>2.81</v>
       </c>
       <c r="T54" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="U54" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="V54" t="n">
         <v>6.5</v>
       </c>
       <c r="W54" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X54" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z54" t="n">
-        <v>3.2</v>
+        <v>3.24</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.88</v>
+        <v>2.03</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="AC54" t="n">
         <v>3.3</v>
       </c>
       <c r="AD54" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AF54" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="AG54" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AH54" t="n">
-        <v>1.31</v>
+        <v>1.55</v>
       </c>
       <c r="AI54" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6962,77 +6962,77 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.45</v>
+        <v>2.85</v>
       </c>
       <c r="M55" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N55" t="n">
-        <v>2.72</v>
+        <v>2.24</v>
       </c>
       <c r="O55" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="P55" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q55" t="n">
         <v>3.1</v>
       </c>
-      <c r="P55" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>3.5</v>
-      </c>
       <c r="R55" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="S55" t="n">
-        <v>2.69</v>
+        <v>2.77</v>
       </c>
       <c r="T55" t="n">
-        <v>2.65</v>
+        <v>3.04</v>
       </c>
       <c r="U55" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="V55" t="n">
-        <v>6.95</v>
+        <v>7.6</v>
       </c>
       <c r="W55" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X55" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z55" t="n">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.98</v>
+        <v>2.19</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AC55" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="AD55" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AG55" t="n">
         <v>1.29</v>
       </c>
-      <c r="AE55" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF55" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG55" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH55" t="n">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="AI55" s="3" t="n">
         <v>46084.69791666666</v>
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,73 +7085,73 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.91</v>
+        <v>2.45</v>
       </c>
       <c r="M56" t="n">
-        <v>3.45</v>
+        <v>3.47</v>
       </c>
       <c r="N56" t="n">
-        <v>3.86</v>
+        <v>2.59</v>
       </c>
       <c r="O56" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U56" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V56" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="W56" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z56" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC56" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD56" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF56" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AG56" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AH56" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI56" s="3" t="n">
         <v>46084.69791666666</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,73 +7204,73 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.85</v>
+        <v>2</v>
       </c>
       <c r="M57" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="N57" t="n">
-        <v>2.24</v>
+        <v>3.5</v>
       </c>
       <c r="O57" t="n">
-        <v>3.7</v>
+        <v>2.62</v>
       </c>
       <c r="P57" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.1</v>
+        <v>4.26</v>
       </c>
       <c r="R57" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="S57" t="n">
-        <v>2.77</v>
+        <v>2.87</v>
       </c>
       <c r="T57" t="n">
-        <v>3.04</v>
+        <v>2.91</v>
       </c>
       <c r="U57" t="n">
         <v>1.33</v>
       </c>
       <c r="V57" t="n">
-        <v>7.6</v>
+        <v>7.1</v>
       </c>
       <c r="W57" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X57" t="n">
         <v>1.02</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="Z57" t="n">
-        <v>3.14</v>
+        <v>2.92</v>
       </c>
       <c r="AA57" t="n">
-        <v>2.19</v>
+        <v>2.07</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AC57" t="n">
-        <v>3.55</v>
+        <v>3.67</v>
       </c>
       <c r="AD57" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AE57" t="n">
         <v>1.81</v>
       </c>
       <c r="AF57" t="n">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="AG57" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AH57" t="n">
-        <v>1.38</v>
+        <v>1.62</v>
       </c>
       <c r="AI57" s="3" t="n">
         <v>46084.69791666666</v>

--- a/jogos_2026-03-03.xlsx
+++ b/jogos_2026-03-03.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.5</v>
+        <v>1.81</v>
       </c>
       <c r="M9" t="n">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="N9" t="n">
-        <v>2.8</v>
+        <v>4.55</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>5.78</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46084.45833333334</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.81</v>
+        <v>2.5</v>
       </c>
       <c r="M10" t="n">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="N10" t="n">
-        <v>4.55</v>
+        <v>2.8</v>
       </c>
       <c r="O10" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.78</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46084.45833333334</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.72</v>
+        <v>1.87</v>
       </c>
       <c r="M30" t="n">
-        <v>3.15</v>
+        <v>3.8</v>
       </c>
       <c r="N30" t="n">
-        <v>2.05</v>
+        <v>2.98</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46084.66666666666</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.87</v>
+        <v>3.72</v>
       </c>
       <c r="M31" t="n">
-        <v>3.8</v>
+        <v>3.15</v>
       </c>
       <c r="N31" t="n">
-        <v>2.98</v>
+        <v>2.05</v>
       </c>
       <c r="O31" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46084.66666666666</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.47</v>
+        <v>1.4</v>
       </c>
       <c r="M32" t="n">
-        <v>3.2</v>
+        <v>4.6</v>
       </c>
       <c r="N32" t="n">
-        <v>2.11</v>
+        <v>7.03</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.4</v>
+        <v>2.65</v>
       </c>
       <c r="M33" t="n">
-        <v>4.6</v>
+        <v>3.1</v>
       </c>
       <c r="N33" t="n">
-        <v>7.03</v>
+        <v>2.65</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.65</v>
+        <v>3.47</v>
       </c>
       <c r="M34" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N34" t="n">
-        <v>2.65</v>
+        <v>2.11</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4820,77 +4820,77 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46084.6875</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.49</v>
+        <v>2.05</v>
       </c>
       <c r="M38" t="n">
-        <v>3.8</v>
+        <v>3.56</v>
       </c>
       <c r="N38" t="n">
-        <v>2.86</v>
+        <v>4.05</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.68</v>
+        <v>2.15</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.05</v>
+        <v>1.63</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5058,77 +5058,77 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.45</v>
+        <v>2.49</v>
       </c>
       <c r="M39" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="N39" t="n">
-        <v>2.43</v>
+        <v>2.86</v>
       </c>
       <c r="O39" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AB39" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46084.6875</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.05</v>
+        <v>4.28</v>
       </c>
       <c r="M40" t="n">
-        <v>3.56</v>
+        <v>4.2</v>
       </c>
       <c r="N40" t="n">
-        <v>4.05</v>
+        <v>1.66</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>5.33</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5891,77 +5891,77 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.45</v>
+        <v>3.2</v>
       </c>
       <c r="M46" t="n">
-        <v>3.2</v>
+        <v>3.24</v>
       </c>
       <c r="N46" t="n">
-        <v>2.72</v>
+        <v>2.21</v>
       </c>
       <c r="O46" t="n">
-        <v>3.1</v>
+        <v>3.92</v>
       </c>
       <c r="P46" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="R46" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S46" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="U46" t="n">
         <v>1.39</v>
       </c>
-      <c r="S46" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="T46" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U46" t="n">
-        <v>1.41</v>
-      </c>
       <c r="V46" t="n">
-        <v>6.95</v>
+        <v>6.5</v>
       </c>
       <c r="W46" t="n">
         <v>1.04</v>
       </c>
       <c r="X46" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y46" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH46" t="n">
         <v>1.31</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE46" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF46" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG46" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH46" t="n">
-        <v>1.53</v>
       </c>
       <c r="AI46" s="3" t="n">
         <v>46084.69791666666</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6010,77 +6010,77 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L47" t="n">
         <v>2.45</v>
       </c>
       <c r="M47" t="n">
-        <v>3</v>
+        <v>3.47</v>
       </c>
       <c r="N47" t="n">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="O47" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AI47" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,73 +6133,73 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.53</v>
+        <v>2.45</v>
       </c>
       <c r="M48" t="n">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="N48" t="n">
-        <v>5.53</v>
+        <v>2.88</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.65</v>
+        <v>1.93</v>
       </c>
       <c r="AB48" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH48" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AI48" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,73 +6252,73 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.45</v>
+        <v>1.91</v>
       </c>
       <c r="M49" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="N49" t="n">
-        <v>2.88</v>
+        <v>3.86</v>
       </c>
       <c r="O49" t="n">
-        <v>2.96</v>
+        <v>2.55</v>
       </c>
       <c r="P49" t="n">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.67</v>
+        <v>4.25</v>
       </c>
       <c r="R49" t="n">
         <v>1.38</v>
       </c>
       <c r="S49" t="n">
-        <v>2.77</v>
+        <v>2.69</v>
       </c>
       <c r="T49" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="U49" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="V49" t="n">
-        <v>6.75</v>
+        <v>7.4</v>
       </c>
       <c r="W49" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X49" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="Z49" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AC49" t="n">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AF49" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AG49" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.52</v>
+        <v>1.73</v>
       </c>
       <c r="AI49" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6367,77 +6367,77 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>3.2</v>
+        <v>1.53</v>
       </c>
       <c r="M50" t="n">
-        <v>3.24</v>
+        <v>3.95</v>
       </c>
       <c r="N50" t="n">
-        <v>2.21</v>
+        <v>5</v>
       </c>
       <c r="O50" t="n">
-        <v>3.92</v>
+        <v>2.06</v>
       </c>
       <c r="P50" t="n">
-        <v>2.05</v>
+        <v>2.35</v>
       </c>
       <c r="Q50" t="n">
-        <v>2.8</v>
+        <v>5.65</v>
       </c>
       <c r="R50" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="S50" t="n">
-        <v>2.77</v>
+        <v>2.91</v>
       </c>
       <c r="T50" t="n">
-        <v>2.73</v>
+        <v>2.48</v>
       </c>
       <c r="U50" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="V50" t="n">
         <v>6.5</v>
       </c>
       <c r="W50" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="X50" t="n">
         <v>1.01</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="Z50" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AC50" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.7</v>
+        <v>1.84</v>
       </c>
       <c r="AF50" t="n">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="AG50" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AH50" t="n">
-        <v>1.31</v>
+        <v>2.31</v>
       </c>
       <c r="AI50" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6486,77 +6486,77 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.91</v>
+        <v>2.85</v>
       </c>
       <c r="M51" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="N51" t="n">
-        <v>3.86</v>
+        <v>2.24</v>
       </c>
       <c r="O51" t="n">
-        <v>2.55</v>
+        <v>3.7</v>
       </c>
       <c r="P51" t="n">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="Q51" t="n">
-        <v>4.25</v>
+        <v>3.1</v>
       </c>
       <c r="R51" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="S51" t="n">
-        <v>2.69</v>
+        <v>2.77</v>
       </c>
       <c r="T51" t="n">
-        <v>2.65</v>
+        <v>3.04</v>
       </c>
       <c r="U51" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V51" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="W51" t="n">
         <v>1.03</v>
       </c>
       <c r="X51" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z51" t="n">
-        <v>3.25</v>
+        <v>3.14</v>
       </c>
       <c r="AA51" t="n">
-        <v>2</v>
+        <v>2.19</v>
       </c>
       <c r="AB51" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE51" t="n">
         <v>1.81</v>
       </c>
-      <c r="AC51" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE51" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AF51" t="n">
-        <v>1.99</v>
+        <v>1.9</v>
       </c>
       <c r="AG51" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AH51" t="n">
-        <v>1.73</v>
+        <v>1.38</v>
       </c>
       <c r="AI51" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,73 +6609,73 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S52" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="T52" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U52" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V52" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W52" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC52" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AD52" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG52" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH52" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AI52" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6724,77 +6724,77 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.53</v>
+        <v>2.1</v>
       </c>
       <c r="M53" t="n">
-        <v>3.95</v>
+        <v>3.38</v>
       </c>
       <c r="N53" t="n">
-        <v>5</v>
+        <v>3.08</v>
       </c>
       <c r="O53" t="n">
-        <v>2.06</v>
+        <v>2.8</v>
       </c>
       <c r="P53" t="n">
-        <v>2.35</v>
+        <v>2.19</v>
       </c>
       <c r="Q53" t="n">
-        <v>5.65</v>
+        <v>3.5</v>
       </c>
       <c r="R53" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="S53" t="n">
-        <v>2.91</v>
+        <v>2.81</v>
       </c>
       <c r="T53" t="n">
-        <v>2.48</v>
+        <v>2.75</v>
       </c>
       <c r="U53" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="V53" t="n">
         <v>6.5</v>
       </c>
       <c r="W53" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="X53" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y53" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG53" t="n">
         <v>1.24</v>
       </c>
-      <c r="Z53" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AE53" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AF53" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG53" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AH53" t="n">
-        <v>2.31</v>
+        <v>1.55</v>
       </c>
       <c r="AI53" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6843,77 +6843,77 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U54" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V54" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W54" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X54" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z54" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD54" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG54" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH54" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI54" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,73 +6966,73 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.85</v>
+        <v>2.45</v>
       </c>
       <c r="M55" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="N55" t="n">
-        <v>2.24</v>
+        <v>2.7</v>
       </c>
       <c r="O55" t="n">
-        <v>3.7</v>
+        <v>2.95</v>
       </c>
       <c r="P55" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.1</v>
+        <v>3.42</v>
       </c>
       <c r="R55" t="n">
         <v>1.44</v>
       </c>
       <c r="S55" t="n">
-        <v>2.77</v>
+        <v>2.62</v>
       </c>
       <c r="T55" t="n">
-        <v>3.04</v>
+        <v>2.96</v>
       </c>
       <c r="U55" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="V55" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="W55" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X55" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z55" t="n">
-        <v>3.14</v>
+        <v>3.5</v>
       </c>
       <c r="AA55" t="n">
-        <v>2.19</v>
+        <v>2</v>
       </c>
       <c r="AB55" t="n">
         <v>1.71</v>
       </c>
       <c r="AC55" t="n">
-        <v>3.55</v>
+        <v>3.48</v>
       </c>
       <c r="AD55" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AG55" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="AI55" s="3" t="n">
         <v>46084.69791666666</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7081,77 +7081,77 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="M56" t="n">
-        <v>3.47</v>
+        <v>3.25</v>
       </c>
       <c r="N56" t="n">
-        <v>2.59</v>
+        <v>3.5</v>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S56" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="T56" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U56" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V56" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="W56" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X56" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC56" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="AD56" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE56" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF56" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG56" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH56" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI56" s="3" t="n">
         <v>46084.69791666666</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7200,77 +7200,77 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="M57" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="N57" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="O57" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P57" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q57" t="n">
         <v>3.5</v>
       </c>
-      <c r="O57" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="P57" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>4.26</v>
-      </c>
       <c r="R57" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S57" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U57" t="n">
         <v>1.41</v>
       </c>
-      <c r="S57" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="T57" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="U57" t="n">
+      <c r="V57" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="W57" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X57" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG57" t="n">
         <v>1.33</v>
       </c>
-      <c r="V57" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W57" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X57" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y57" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Z57" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AA57" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AB57" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AC57" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="AD57" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AE57" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AF57" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AG57" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AH57" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AI57" s="3" t="n">
         <v>46084.69791666666</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,73 +7323,73 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="M58" t="n">
-        <v>3.26</v>
+        <v>4.3</v>
       </c>
       <c r="N58" t="n">
-        <v>4</v>
+        <v>5.53</v>
       </c>
       <c r="O58" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="T58" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U58" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V58" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="W58" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z58" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="AC58" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="AD58" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF58" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG58" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH58" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AI58" s="3" t="n">
         <v>46084.69791666666</v>

--- a/jogos_2026-03-03.xlsx
+++ b/jogos_2026-03-03.xlsx
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.81</v>
+        <v>2.5</v>
       </c>
       <c r="M9" t="n">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="N9" t="n">
-        <v>4.55</v>
+        <v>2.8</v>
       </c>
       <c r="O9" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.78</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46084.45833333334</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.5</v>
+        <v>1.81</v>
       </c>
       <c r="M10" t="n">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="N10" t="n">
-        <v>2.8</v>
+        <v>4.55</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>5.78</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46084.45833333334</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="M36" t="n">
-        <v>3.91</v>
+        <v>3.56</v>
       </c>
       <c r="N36" t="n">
-        <v>5.33</v>
+        <v>4.05</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.85</v>
+        <v>1.63</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4820,77 +4820,77 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.45</v>
+        <v>1.75</v>
       </c>
       <c r="M37" t="n">
-        <v>3.3</v>
+        <v>3.91</v>
       </c>
       <c r="N37" t="n">
-        <v>2.43</v>
+        <v>5.33</v>
       </c>
       <c r="O37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46084.6875</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,55 +4943,55 @@
         </is>
       </c>
       <c r="L38" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="M38" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N38" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AB38" t="n">
         <v>2.05</v>
-      </c>
-      <c r="M38" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="N38" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
-      <c r="R38" t="n">
-        <v>0</v>
-      </c>
-      <c r="S38" t="n">
-        <v>0</v>
-      </c>
-      <c r="T38" t="n">
-        <v>0</v>
-      </c>
-      <c r="U38" t="n">
-        <v>0</v>
-      </c>
-      <c r="V38" t="n">
-        <v>0</v>
-      </c>
-      <c r="W38" t="n">
-        <v>0</v>
-      </c>
-      <c r="X38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.63</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5653,77 +5653,77 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46084.6875</v>
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6010,77 +6010,77 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.45</v>
+        <v>2.85</v>
       </c>
       <c r="M47" t="n">
-        <v>3.47</v>
+        <v>3.1</v>
       </c>
       <c r="N47" t="n">
-        <v>2.59</v>
+        <v>2.24</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI47" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,73 +6133,73 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.45</v>
+        <v>1.8</v>
       </c>
       <c r="M48" t="n">
-        <v>3.4</v>
+        <v>3.26</v>
       </c>
       <c r="N48" t="n">
-        <v>2.88</v>
+        <v>4</v>
       </c>
       <c r="O48" t="n">
-        <v>2.96</v>
+        <v>2.46</v>
       </c>
       <c r="P48" t="n">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.67</v>
+        <v>4.25</v>
       </c>
       <c r="R48" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S48" t="n">
-        <v>2.77</v>
+        <v>2.87</v>
       </c>
       <c r="T48" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="U48" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="V48" t="n">
-        <v>6.75</v>
+        <v>7.5</v>
       </c>
       <c r="W48" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X48" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="Z48" t="n">
-        <v>3.6</v>
+        <v>3.05</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AB48" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE48" t="n">
         <v>1.85</v>
       </c>
-      <c r="AC48" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AE48" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AF48" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AG48" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.52</v>
+        <v>1.88</v>
       </c>
       <c r="AI48" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,73 +6252,73 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.91</v>
+        <v>2.45</v>
       </c>
       <c r="M49" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="N49" t="n">
-        <v>3.86</v>
+        <v>2.88</v>
       </c>
       <c r="O49" t="n">
-        <v>2.55</v>
+        <v>2.96</v>
       </c>
       <c r="P49" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="Q49" t="n">
-        <v>4.25</v>
+        <v>3.67</v>
       </c>
       <c r="R49" t="n">
         <v>1.38</v>
       </c>
       <c r="S49" t="n">
-        <v>2.69</v>
+        <v>2.77</v>
       </c>
       <c r="T49" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="U49" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="V49" t="n">
-        <v>7.4</v>
+        <v>6.75</v>
       </c>
       <c r="W49" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X49" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="Z49" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="AA49" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF49" t="n">
         <v>2</v>
       </c>
-      <c r="AB49" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE49" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF49" t="n">
-        <v>1.99</v>
-      </c>
       <c r="AG49" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.73</v>
+        <v>1.52</v>
       </c>
       <c r="AI49" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,73 +6371,73 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.53</v>
+        <v>2.45</v>
       </c>
       <c r="M50" t="n">
-        <v>3.95</v>
+        <v>3.47</v>
       </c>
       <c r="N50" t="n">
-        <v>5</v>
+        <v>2.59</v>
       </c>
       <c r="O50" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="U50" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="V50" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W50" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X50" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Z50" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG50" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AH50" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AI50" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6486,77 +6486,77 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.85</v>
+        <v>1.53</v>
       </c>
       <c r="M51" t="n">
-        <v>3.1</v>
+        <v>3.95</v>
       </c>
       <c r="N51" t="n">
-        <v>2.24</v>
+        <v>5</v>
       </c>
       <c r="O51" t="n">
-        <v>3.7</v>
+        <v>2.06</v>
       </c>
       <c r="P51" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.1</v>
+        <v>5.65</v>
       </c>
       <c r="R51" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="S51" t="n">
-        <v>2.77</v>
+        <v>2.91</v>
       </c>
       <c r="T51" t="n">
-        <v>3.04</v>
+        <v>2.48</v>
       </c>
       <c r="U51" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="V51" t="n">
-        <v>7.6</v>
+        <v>6.5</v>
       </c>
       <c r="W51" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="X51" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="Z51" t="n">
-        <v>3.14</v>
+        <v>3.5</v>
       </c>
       <c r="AA51" t="n">
-        <v>2.19</v>
+        <v>1.78</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.71</v>
+        <v>1.93</v>
       </c>
       <c r="AC51" t="n">
-        <v>3.55</v>
+        <v>3</v>
       </c>
       <c r="AD51" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AG51" t="n">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="AH51" t="n">
-        <v>1.38</v>
+        <v>2.31</v>
       </c>
       <c r="AI51" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,37 +6609,37 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="M52" t="n">
-        <v>3.26</v>
+        <v>3.45</v>
       </c>
       <c r="N52" t="n">
-        <v>4</v>
+        <v>3.86</v>
       </c>
       <c r="O52" t="n">
-        <v>2.46</v>
+        <v>2.55</v>
       </c>
       <c r="P52" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="Q52" t="n">
         <v>4.25</v>
       </c>
       <c r="R52" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S52" t="n">
-        <v>2.87</v>
+        <v>2.69</v>
       </c>
       <c r="T52" t="n">
-        <v>2.9</v>
+        <v>2.65</v>
       </c>
       <c r="U52" t="n">
         <v>1.36</v>
       </c>
       <c r="V52" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="W52" t="n">
         <v>1.03</v>
@@ -6648,34 +6648,34 @@
         <v>1</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="Z52" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="AA52" t="n">
         <v>2</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.67</v>
+        <v>1.81</v>
       </c>
       <c r="AC52" t="n">
-        <v>3.52</v>
+        <v>3.34</v>
       </c>
       <c r="AD52" t="n">
         <v>1.24</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.86</v>
+        <v>1.99</v>
       </c>
       <c r="AG52" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.88</v>
+        <v>1.73</v>
       </c>
       <c r="AI52" s="3" t="n">
         <v>46084.69791666666</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,73 +7204,73 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.45</v>
+        <v>1.53</v>
       </c>
       <c r="M57" t="n">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="N57" t="n">
-        <v>2.72</v>
+        <v>5.53</v>
       </c>
       <c r="O57" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>0</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
+      </c>
+      <c r="V57" t="n">
+        <v>0</v>
+      </c>
+      <c r="W57" t="n">
+        <v>0</v>
+      </c>
+      <c r="X57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB57" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q57" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R57" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S57" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="T57" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U57" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="V57" t="n">
-        <v>6.95</v>
-      </c>
-      <c r="W57" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X57" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y57" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="Z57" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA57" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB57" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AC57" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AD57" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF57" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG57" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH57" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI57" s="3" t="n">
         <v>46084.69791666666</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,73 +7323,73 @@
         </is>
       </c>
       <c r="L58" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="M58" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N58" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="O58" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P58" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R58" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S58" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V58" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="W58" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X58" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE58" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF58" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG58" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH58" t="n">
         <v>1.53</v>
-      </c>
-      <c r="M58" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="N58" t="n">
-        <v>5.53</v>
-      </c>
-      <c r="O58" t="n">
-        <v>0</v>
-      </c>
-      <c r="P58" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
-      <c r="R58" t="n">
-        <v>0</v>
-      </c>
-      <c r="S58" t="n">
-        <v>0</v>
-      </c>
-      <c r="T58" t="n">
-        <v>0</v>
-      </c>
-      <c r="U58" t="n">
-        <v>0</v>
-      </c>
-      <c r="V58" t="n">
-        <v>0</v>
-      </c>
-      <c r="W58" t="n">
-        <v>0</v>
-      </c>
-      <c r="X58" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y58" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA58" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB58" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH58" t="n">
-        <v>0</v>
       </c>
       <c r="AI58" s="3" t="n">
         <v>46084.69791666666</v>

--- a/jogos_2026-03-03.xlsx
+++ b/jogos_2026-03-03.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.72</v>
+        <v>1.4</v>
       </c>
       <c r="M31" t="n">
-        <v>3.15</v>
+        <v>4.6</v>
       </c>
       <c r="N31" t="n">
-        <v>2.05</v>
+        <v>7.03</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.4</v>
+        <v>3.47</v>
       </c>
       <c r="M32" t="n">
-        <v>4.6</v>
+        <v>3.2</v>
       </c>
       <c r="N32" t="n">
-        <v>7.03</v>
+        <v>2.11</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.47</v>
+        <v>3.72</v>
       </c>
       <c r="M34" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="N34" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4582,77 +4582,77 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46084.6875</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.75</v>
+        <v>2.49</v>
       </c>
       <c r="M37" t="n">
-        <v>3.91</v>
+        <v>3.8</v>
       </c>
       <c r="N37" t="n">
-        <v>5.33</v>
+        <v>2.86</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5653,77 +5653,77 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46084.6875</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5891,77 +5891,77 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>3.2</v>
+        <v>1.53</v>
       </c>
       <c r="M46" t="n">
-        <v>3.24</v>
+        <v>3.95</v>
       </c>
       <c r="N46" t="n">
-        <v>2.21</v>
+        <v>5</v>
       </c>
       <c r="O46" t="n">
-        <v>3.92</v>
+        <v>2.06</v>
       </c>
       <c r="P46" t="n">
-        <v>2.05</v>
+        <v>2.35</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.8</v>
+        <v>5.65</v>
       </c>
       <c r="R46" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="S46" t="n">
-        <v>2.77</v>
+        <v>2.91</v>
       </c>
       <c r="T46" t="n">
-        <v>2.73</v>
+        <v>2.48</v>
       </c>
       <c r="U46" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="V46" t="n">
         <v>6.5</v>
       </c>
       <c r="W46" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="X46" t="n">
         <v>1.01</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="Z46" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AC46" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.7</v>
+        <v>1.84</v>
       </c>
       <c r="AF46" t="n">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.31</v>
+        <v>2.31</v>
       </c>
       <c r="AI46" s="3" t="n">
         <v>46084.69791666666</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6010,77 +6010,77 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.85</v>
+        <v>2.45</v>
       </c>
       <c r="M47" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N47" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="O47" t="n">
         <v>3.1</v>
       </c>
-      <c r="N47" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="O47" t="n">
-        <v>3.7</v>
-      </c>
       <c r="P47" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="R47" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="S47" t="n">
-        <v>2.77</v>
+        <v>2.69</v>
       </c>
       <c r="T47" t="n">
-        <v>3.04</v>
+        <v>2.65</v>
       </c>
       <c r="U47" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V47" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="W47" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X47" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG47" t="n">
         <v>1.33</v>
       </c>
-      <c r="V47" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="W47" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X47" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AE47" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AF47" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AG47" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AH47" t="n">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="AI47" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6129,77 +6129,77 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.8</v>
+        <v>2.45</v>
       </c>
       <c r="M48" t="n">
-        <v>3.26</v>
+        <v>3</v>
       </c>
       <c r="N48" t="n">
-        <v>4</v>
+        <v>2.7</v>
       </c>
       <c r="O48" t="n">
-        <v>2.46</v>
+        <v>2.95</v>
       </c>
       <c r="P48" t="n">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="Q48" t="n">
-        <v>4.25</v>
+        <v>3.42</v>
       </c>
       <c r="R48" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="S48" t="n">
-        <v>2.87</v>
+        <v>2.62</v>
       </c>
       <c r="T48" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="U48" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="V48" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="W48" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X48" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="Z48" t="n">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="AA48" t="n">
         <v>2</v>
       </c>
       <c r="AB48" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE48" t="n">
         <v>1.67</v>
       </c>
-      <c r="AC48" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE48" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AF48" t="n">
-        <v>1.86</v>
+        <v>2.1</v>
       </c>
       <c r="AG48" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.88</v>
+        <v>1.48</v>
       </c>
       <c r="AI48" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,73 +6252,73 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.45</v>
+        <v>1.8</v>
       </c>
       <c r="M49" t="n">
-        <v>3.4</v>
+        <v>3.26</v>
       </c>
       <c r="N49" t="n">
-        <v>2.88</v>
+        <v>4</v>
       </c>
       <c r="O49" t="n">
-        <v>2.96</v>
+        <v>2.46</v>
       </c>
       <c r="P49" t="n">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.67</v>
+        <v>4.25</v>
       </c>
       <c r="R49" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S49" t="n">
-        <v>2.77</v>
+        <v>2.87</v>
       </c>
       <c r="T49" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="U49" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="V49" t="n">
-        <v>6.75</v>
+        <v>7.5</v>
       </c>
       <c r="W49" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X49" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="Z49" t="n">
-        <v>3.6</v>
+        <v>3.05</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AB49" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE49" t="n">
         <v>1.85</v>
       </c>
-      <c r="AC49" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AE49" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AF49" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AG49" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.52</v>
+        <v>1.88</v>
       </c>
       <c r="AI49" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6367,77 +6367,77 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.45</v>
+        <v>2.85</v>
       </c>
       <c r="M50" t="n">
-        <v>3.47</v>
+        <v>3.1</v>
       </c>
       <c r="N50" t="n">
-        <v>2.59</v>
+        <v>2.24</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG50" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH50" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI50" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6486,77 +6486,77 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.53</v>
+        <v>2</v>
       </c>
       <c r="M51" t="n">
-        <v>3.95</v>
+        <v>3.25</v>
       </c>
       <c r="N51" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="O51" t="n">
-        <v>2.06</v>
+        <v>2.62</v>
       </c>
       <c r="P51" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="Q51" t="n">
-        <v>5.65</v>
+        <v>4.26</v>
       </c>
       <c r="R51" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S51" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="U51" t="n">
         <v>1.33</v>
       </c>
-      <c r="S51" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="T51" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="U51" t="n">
-        <v>1.41</v>
-      </c>
       <c r="V51" t="n">
-        <v>6.5</v>
+        <v>7.1</v>
       </c>
       <c r="W51" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X51" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.24</v>
+        <v>1.34</v>
       </c>
       <c r="Z51" t="n">
-        <v>3.5</v>
+        <v>2.92</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.78</v>
+        <v>2.07</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.93</v>
+        <v>1.72</v>
       </c>
       <c r="AC51" t="n">
-        <v>3</v>
+        <v>3.67</v>
       </c>
       <c r="AD51" t="n">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="AG51" t="n">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="AH51" t="n">
-        <v>2.31</v>
+        <v>1.62</v>
       </c>
       <c r="AI51" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,73 +6609,73 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.91</v>
+        <v>1.53</v>
       </c>
       <c r="M52" t="n">
-        <v>3.45</v>
+        <v>4.3</v>
       </c>
       <c r="N52" t="n">
-        <v>3.86</v>
+        <v>5.53</v>
       </c>
       <c r="O52" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U52" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V52" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="W52" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z52" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.81</v>
+        <v>2.1</v>
       </c>
       <c r="AC52" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD52" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AG52" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI52" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6724,77 +6724,77 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="M53" t="n">
-        <v>3.38</v>
+        <v>3.47</v>
       </c>
       <c r="N53" t="n">
-        <v>3.08</v>
+        <v>2.59</v>
       </c>
       <c r="O53" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U53" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V53" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W53" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X53" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD53" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG53" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH53" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI53" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,73 +6847,73 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S54" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="T54" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U54" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V54" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="W54" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD54" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AG54" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH54" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI54" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6962,77 +6962,77 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L55" t="n">
         <v>2.45</v>
       </c>
       <c r="M55" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="N55" t="n">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="O55" t="n">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="P55" t="n">
         <v>2.05</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.42</v>
+        <v>3.67</v>
       </c>
       <c r="R55" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="S55" t="n">
-        <v>2.62</v>
+        <v>2.77</v>
       </c>
       <c r="T55" t="n">
-        <v>2.96</v>
+        <v>2.75</v>
       </c>
       <c r="U55" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V55" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="W55" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X55" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AD55" t="n">
         <v>1.32</v>
       </c>
-      <c r="V55" t="n">
-        <v>8</v>
-      </c>
-      <c r="W55" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X55" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA55" t="n">
+      <c r="AE55" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF55" t="n">
         <v>2</v>
       </c>
-      <c r="AB55" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE55" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF55" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AG55" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="AI55" s="3" t="n">
         <v>46084.69791666666</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,73 +7085,73 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="M56" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="N56" t="n">
-        <v>3.5</v>
+        <v>2.21</v>
       </c>
       <c r="O56" t="n">
-        <v>2.62</v>
+        <v>3.92</v>
       </c>
       <c r="P56" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q56" t="n">
-        <v>4.26</v>
+        <v>2.8</v>
       </c>
       <c r="R56" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="S56" t="n">
-        <v>2.87</v>
+        <v>2.77</v>
       </c>
       <c r="T56" t="n">
-        <v>2.91</v>
+        <v>2.73</v>
       </c>
       <c r="U56" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="V56" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W56" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X56" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD56" t="n">
         <v>1.33</v>
       </c>
-      <c r="V56" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W56" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X56" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Z56" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AC56" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="AD56" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AE56" t="n">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="AF56" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="AG56" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AH56" t="n">
-        <v>1.62</v>
+        <v>1.31</v>
       </c>
       <c r="AI56" s="3" t="n">
         <v>46084.69791666666</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7200,77 +7200,77 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.53</v>
+        <v>2.1</v>
       </c>
       <c r="M57" t="n">
-        <v>4.3</v>
+        <v>3.38</v>
       </c>
       <c r="N57" t="n">
-        <v>5.53</v>
+        <v>3.08</v>
       </c>
       <c r="O57" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S57" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="T57" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U57" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V57" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W57" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X57" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y57" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z57" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.65</v>
+        <v>2.03</v>
       </c>
       <c r="AB57" t="n">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="AC57" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD57" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE57" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF57" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG57" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH57" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI57" s="3" t="n">
         <v>46084.69791666666</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,73 +7323,73 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="T58" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U58" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="V58" t="n">
-        <v>6.95</v>
+        <v>0</v>
       </c>
       <c r="W58" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X58" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z58" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC58" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AD58" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF58" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG58" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH58" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI58" s="3" t="n">
         <v>46084.69791666666</v>

--- a/jogos_2026-03-03.xlsx
+++ b/jogos_2026-03-03.xlsx
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.5</v>
+        <v>1.81</v>
       </c>
       <c r="M9" t="n">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="N9" t="n">
-        <v>2.8</v>
+        <v>4.55</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>5.78</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46084.45833333334</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.81</v>
+        <v>2.5</v>
       </c>
       <c r="M10" t="n">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="N10" t="n">
-        <v>4.55</v>
+        <v>2.8</v>
       </c>
       <c r="O10" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.78</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46084.45833333334</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.8</v>
+        <v>4.5</v>
       </c>
       <c r="M23" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N23" t="n">
-        <v>2.5</v>
+        <v>1.62</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.87</v>
+        <v>3.72</v>
       </c>
       <c r="M30" t="n">
-        <v>3.8</v>
+        <v>3.15</v>
       </c>
       <c r="N30" t="n">
-        <v>2.98</v>
+        <v>2.05</v>
       </c>
       <c r="O30" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46084.66666666666</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.47</v>
+        <v>2.65</v>
       </c>
       <c r="M32" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N32" t="n">
-        <v>2.11</v>
+        <v>2.65</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.65</v>
+        <v>1.87</v>
       </c>
       <c r="M33" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="N33" t="n">
-        <v>2.65</v>
+        <v>2.98</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46084.66666666666</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.72</v>
+        <v>3.47</v>
       </c>
       <c r="M34" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="N34" t="n">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4582,77 +4582,77 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46084.6875</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.49</v>
+        <v>1.75</v>
       </c>
       <c r="M37" t="n">
-        <v>3.8</v>
+        <v>3.91</v>
       </c>
       <c r="N37" t="n">
-        <v>2.86</v>
+        <v>5.33</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5177,77 +5177,77 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.05</v>
+        <v>2.45</v>
       </c>
       <c r="M40" t="n">
-        <v>3.56</v>
+        <v>3.3</v>
       </c>
       <c r="N40" t="n">
-        <v>4.05</v>
+        <v>2.43</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.15</v>
+        <v>1.67</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.63</v>
+        <v>2.1</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46084.6875</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>5.33</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,73 +6014,73 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.45</v>
+        <v>1.53</v>
       </c>
       <c r="M47" t="n">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="N47" t="n">
-        <v>2.72</v>
+        <v>5.53</v>
       </c>
       <c r="O47" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>0</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
+      </c>
+      <c r="V47" t="n">
+        <v>0</v>
+      </c>
+      <c r="W47" t="n">
+        <v>0</v>
+      </c>
+      <c r="X47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB47" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q47" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R47" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S47" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="T47" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U47" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="V47" t="n">
-        <v>6.95</v>
-      </c>
-      <c r="W47" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X47" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AC47" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI47" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6129,77 +6129,77 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L48" t="n">
         <v>2.45</v>
       </c>
       <c r="M48" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="N48" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="O48" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="P48" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="R48" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="S48" t="n">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="T48" t="n">
-        <v>2.96</v>
+        <v>2.65</v>
       </c>
       <c r="U48" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="V48" t="n">
-        <v>8</v>
+        <v>6.95</v>
       </c>
       <c r="W48" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X48" t="n">
         <v>1.06</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="Z48" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AA48" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AC48" t="n">
-        <v>3.48</v>
+        <v>3.2</v>
       </c>
       <c r="AD48" t="n">
         <v>1.29</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AF48" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AG48" t="n">
         <v>1.33</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AI48" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6248,77 +6248,77 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.8</v>
+        <v>3.2</v>
       </c>
       <c r="M49" t="n">
-        <v>3.26</v>
+        <v>3.24</v>
       </c>
       <c r="N49" t="n">
-        <v>4</v>
+        <v>2.21</v>
       </c>
       <c r="O49" t="n">
-        <v>2.46</v>
+        <v>3.92</v>
       </c>
       <c r="P49" t="n">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="Q49" t="n">
-        <v>4.25</v>
+        <v>2.8</v>
       </c>
       <c r="R49" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S49" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="U49" t="n">
         <v>1.39</v>
       </c>
-      <c r="S49" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="T49" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U49" t="n">
-        <v>1.36</v>
-      </c>
       <c r="V49" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="W49" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X49" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="Z49" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="AA49" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="AC49" t="n">
-        <v>3.52</v>
+        <v>3.3</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.86</v>
+        <v>2.02</v>
       </c>
       <c r="AG49" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.88</v>
+        <v>1.31</v>
       </c>
       <c r="AI49" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6367,77 +6367,77 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.85</v>
+        <v>1.8</v>
       </c>
       <c r="M50" t="n">
-        <v>3.1</v>
+        <v>3.26</v>
       </c>
       <c r="N50" t="n">
-        <v>2.24</v>
+        <v>4</v>
       </c>
       <c r="O50" t="n">
-        <v>3.7</v>
+        <v>2.46</v>
       </c>
       <c r="P50" t="n">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.1</v>
+        <v>4.25</v>
       </c>
       <c r="R50" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="S50" t="n">
-        <v>2.77</v>
+        <v>2.87</v>
       </c>
       <c r="T50" t="n">
-        <v>3.04</v>
+        <v>2.9</v>
       </c>
       <c r="U50" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V50" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="W50" t="n">
         <v>1.03</v>
       </c>
       <c r="X50" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="Z50" t="n">
-        <v>3.14</v>
+        <v>3.05</v>
       </c>
       <c r="AA50" t="n">
-        <v>2.19</v>
+        <v>2</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AC50" t="n">
-        <v>3.55</v>
+        <v>3.52</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AG50" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AH50" t="n">
-        <v>1.38</v>
+        <v>1.88</v>
       </c>
       <c r="AI50" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6486,77 +6486,77 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>4.26</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="U51" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V51" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="W51" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X51" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z51" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="AD51" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG51" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH51" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI51" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6605,77 +6605,77 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.53</v>
+        <v>2.1</v>
       </c>
       <c r="M52" t="n">
-        <v>4.3</v>
+        <v>3.38</v>
       </c>
       <c r="N52" t="n">
-        <v>5.53</v>
+        <v>3.08</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S52" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="T52" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U52" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V52" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W52" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X52" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.65</v>
+        <v>2.03</v>
       </c>
       <c r="AB52" t="n">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="AC52" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD52" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG52" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH52" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI52" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,73 +6728,73 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.45</v>
+        <v>1.91</v>
       </c>
       <c r="M53" t="n">
-        <v>3.47</v>
+        <v>3.45</v>
       </c>
       <c r="N53" t="n">
-        <v>2.59</v>
+        <v>3.86</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V53" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="W53" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD53" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AG53" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH53" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI53" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,73 +6847,73 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.91</v>
+        <v>2.45</v>
       </c>
       <c r="M54" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="N54" t="n">
-        <v>3.86</v>
+        <v>2.88</v>
       </c>
       <c r="O54" t="n">
-        <v>2.55</v>
+        <v>2.96</v>
       </c>
       <c r="P54" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="Q54" t="n">
-        <v>4.25</v>
+        <v>3.67</v>
       </c>
       <c r="R54" t="n">
         <v>1.38</v>
       </c>
       <c r="S54" t="n">
-        <v>2.69</v>
+        <v>2.77</v>
       </c>
       <c r="T54" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="U54" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="V54" t="n">
-        <v>7.4</v>
+        <v>6.75</v>
       </c>
       <c r="W54" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X54" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="Z54" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="AA54" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF54" t="n">
         <v>2</v>
       </c>
-      <c r="AB54" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AC54" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AD54" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE54" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF54" t="n">
-        <v>1.99</v>
-      </c>
       <c r="AG54" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="AH54" t="n">
-        <v>1.73</v>
+        <v>1.52</v>
       </c>
       <c r="AI54" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6962,77 +6962,77 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="M55" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="N55" t="n">
-        <v>2.88</v>
+        <v>3.5</v>
       </c>
       <c r="O55" t="n">
-        <v>2.96</v>
+        <v>2.62</v>
       </c>
       <c r="P55" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q55" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="R55" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S55" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V55" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W55" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X55" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC55" t="n">
         <v>3.67</v>
       </c>
-      <c r="R55" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S55" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T55" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U55" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V55" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="W55" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X55" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AA55" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>3.35</v>
-      </c>
       <c r="AD55" t="n">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="AF55" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AG55" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="AI55" s="3" t="n">
         <v>46084.69791666666</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,73 +7085,73 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>3.2</v>
+        <v>2.85</v>
       </c>
       <c r="M56" t="n">
-        <v>3.24</v>
+        <v>3.1</v>
       </c>
       <c r="N56" t="n">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="O56" t="n">
-        <v>3.92</v>
+        <v>3.7</v>
       </c>
       <c r="P56" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="Q56" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="R56" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="S56" t="n">
         <v>2.77</v>
       </c>
       <c r="T56" t="n">
-        <v>2.73</v>
+        <v>3.04</v>
       </c>
       <c r="U56" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="V56" t="n">
-        <v>6.5</v>
+        <v>7.6</v>
       </c>
       <c r="W56" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X56" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z56" t="n">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.88</v>
+        <v>2.19</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.95</v>
+        <v>1.71</v>
       </c>
       <c r="AC56" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="AD56" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AE56" t="n">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="AF56" t="n">
-        <v>2.02</v>
+        <v>1.9</v>
       </c>
       <c r="AG56" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AH56" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="AI56" s="3" t="n">
         <v>46084.69791666666</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7200,77 +7200,77 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="M57" t="n">
-        <v>3.38</v>
+        <v>3.47</v>
       </c>
       <c r="N57" t="n">
-        <v>3.08</v>
+        <v>2.59</v>
       </c>
       <c r="O57" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="T57" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U57" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V57" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W57" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X57" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z57" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC57" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD57" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF57" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG57" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH57" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI57" s="3" t="n">
         <v>46084.69791666666</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7319,77 +7319,77 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O58" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S58" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T58" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U58" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V58" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W58" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X58" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y58" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z58" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC58" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AD58" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE58" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF58" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG58" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH58" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AI58" s="3" t="n">
         <v>46084.69791666666</v>

--- a/jogos_2026-03-03.xlsx
+++ b/jogos_2026-03-03.xlsx
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.81</v>
+        <v>2.5</v>
       </c>
       <c r="M9" t="n">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="N9" t="n">
-        <v>4.55</v>
+        <v>2.8</v>
       </c>
       <c r="O9" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.78</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46084.45833333334</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.5</v>
+        <v>1.81</v>
       </c>
       <c r="M10" t="n">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="N10" t="n">
-        <v>2.8</v>
+        <v>4.55</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>5.78</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46084.45833333334</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.4</v>
+        <v>2.65</v>
       </c>
       <c r="M31" t="n">
-        <v>4.6</v>
+        <v>3.1</v>
       </c>
       <c r="N31" t="n">
-        <v>7.03</v>
+        <v>2.65</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.65</v>
+        <v>1.4</v>
       </c>
       <c r="M32" t="n">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="N32" t="n">
-        <v>2.65</v>
+        <v>7.03</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.87</v>
+        <v>3.47</v>
       </c>
       <c r="M33" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="N33" t="n">
-        <v>2.98</v>
+        <v>2.11</v>
       </c>
       <c r="O33" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46084.66666666666</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.47</v>
+        <v>1.87</v>
       </c>
       <c r="M34" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="N34" t="n">
-        <v>2.11</v>
+        <v>2.98</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46084.66666666666</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>5.33</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5058,77 +5058,77 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46084.6875</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5177,77 +5177,77 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46084.6875</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="M41" t="n">
-        <v>3.56</v>
+        <v>3.91</v>
       </c>
       <c r="N41" t="n">
-        <v>4.05</v>
+        <v>5.33</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.63</v>
+        <v>1.85</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>

--- a/jogos_2026-03-03.xlsx
+++ b/jogos_2026-03-03.xlsx
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.72</v>
+        <v>1.4</v>
       </c>
       <c r="M30" t="n">
-        <v>3.15</v>
+        <v>4.6</v>
       </c>
       <c r="N30" t="n">
-        <v>2.05</v>
+        <v>7.03</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.65</v>
+        <v>1.87</v>
       </c>
       <c r="M31" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="N31" t="n">
-        <v>2.65</v>
+        <v>2.98</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46084.66666666666</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.4</v>
+        <v>2.65</v>
       </c>
       <c r="M32" t="n">
-        <v>4.6</v>
+        <v>3.1</v>
       </c>
       <c r="N32" t="n">
-        <v>7.03</v>
+        <v>2.65</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.47</v>
+        <v>3.72</v>
       </c>
       <c r="M33" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="N33" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.87</v>
+        <v>3.47</v>
       </c>
       <c r="M34" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="N34" t="n">
-        <v>2.98</v>
+        <v>2.11</v>
       </c>
       <c r="O34" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46084.66666666666</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4701,77 +4701,77 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.05</v>
+        <v>2.45</v>
       </c>
       <c r="M36" t="n">
-        <v>3.56</v>
+        <v>3.3</v>
       </c>
       <c r="N36" t="n">
-        <v>4.05</v>
+        <v>2.43</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.15</v>
+        <v>1.67</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.63</v>
+        <v>2.1</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46084.6875</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5058,77 +5058,77 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.45</v>
+        <v>2.05</v>
       </c>
       <c r="M39" t="n">
-        <v>3.3</v>
+        <v>3.56</v>
       </c>
       <c r="N39" t="n">
-        <v>2.43</v>
+        <v>4.05</v>
       </c>
       <c r="O39" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.67</v>
+        <v>2.15</v>
       </c>
       <c r="AB39" t="n">
-        <v>2.1</v>
+        <v>1.63</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46084.6875</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>5.33</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.49</v>
+        <v>4.28</v>
       </c>
       <c r="M45" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="N45" t="n">
-        <v>2.86</v>
+        <v>1.66</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6129,77 +6129,77 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.45</v>
+        <v>2.85</v>
       </c>
       <c r="M48" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N48" t="n">
-        <v>2.72</v>
+        <v>2.24</v>
       </c>
       <c r="O48" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="P48" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q48" t="n">
         <v>3.1</v>
       </c>
-      <c r="P48" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>3.5</v>
-      </c>
       <c r="R48" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="S48" t="n">
-        <v>2.69</v>
+        <v>2.77</v>
       </c>
       <c r="T48" t="n">
-        <v>2.65</v>
+        <v>3.04</v>
       </c>
       <c r="U48" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="V48" t="n">
-        <v>6.95</v>
+        <v>7.6</v>
       </c>
       <c r="W48" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X48" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z48" t="n">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.98</v>
+        <v>2.19</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AC48" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="AD48" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AG48" t="n">
         <v>1.29</v>
       </c>
-      <c r="AE48" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF48" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG48" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH48" t="n">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="AI48" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,73 +6371,73 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.8</v>
+        <v>2.45</v>
       </c>
       <c r="M50" t="n">
-        <v>3.26</v>
+        <v>3.2</v>
       </c>
       <c r="N50" t="n">
-        <v>4</v>
+        <v>2.72</v>
       </c>
       <c r="O50" t="n">
-        <v>2.46</v>
+        <v>3.1</v>
       </c>
       <c r="P50" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="Q50" t="n">
-        <v>4.25</v>
+        <v>3.5</v>
       </c>
       <c r="R50" t="n">
         <v>1.39</v>
       </c>
       <c r="S50" t="n">
-        <v>2.87</v>
+        <v>2.69</v>
       </c>
       <c r="T50" t="n">
-        <v>2.9</v>
+        <v>2.65</v>
       </c>
       <c r="U50" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="V50" t="n">
-        <v>7.5</v>
+        <v>6.95</v>
       </c>
       <c r="W50" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X50" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="Z50" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="AA50" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AC50" t="n">
-        <v>3.52</v>
+        <v>3.2</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.86</v>
+        <v>2.05</v>
       </c>
       <c r="AG50" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AH50" t="n">
-        <v>1.88</v>
+        <v>1.53</v>
       </c>
       <c r="AI50" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6486,77 +6486,77 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S51" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="T51" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U51" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V51" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W51" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X51" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC51" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD51" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG51" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH51" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI51" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6605,77 +6605,77 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U52" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V52" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W52" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X52" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z52" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD52" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG52" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI52" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,37 +6728,37 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="M53" t="n">
-        <v>3.45</v>
+        <v>3.26</v>
       </c>
       <c r="N53" t="n">
-        <v>3.86</v>
+        <v>4</v>
       </c>
       <c r="O53" t="n">
-        <v>2.55</v>
+        <v>2.46</v>
       </c>
       <c r="P53" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="Q53" t="n">
         <v>4.25</v>
       </c>
       <c r="R53" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S53" t="n">
-        <v>2.69</v>
+        <v>2.87</v>
       </c>
       <c r="T53" t="n">
-        <v>2.65</v>
+        <v>2.9</v>
       </c>
       <c r="U53" t="n">
         <v>1.36</v>
       </c>
       <c r="V53" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="W53" t="n">
         <v>1.03</v>
@@ -6767,34 +6767,34 @@
         <v>1</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="Z53" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="AA53" t="n">
         <v>2</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="AC53" t="n">
-        <v>3.34</v>
+        <v>3.52</v>
       </c>
       <c r="AD53" t="n">
         <v>1.24</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.99</v>
+        <v>1.86</v>
       </c>
       <c r="AG53" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="AH53" t="n">
-        <v>1.73</v>
+        <v>1.88</v>
       </c>
       <c r="AI53" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6843,77 +6843,77 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L54" t="n">
         <v>2.45</v>
       </c>
       <c r="M54" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="N54" t="n">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="O54" t="n">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="P54" t="n">
         <v>2.05</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.67</v>
+        <v>3.42</v>
       </c>
       <c r="R54" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="S54" t="n">
-        <v>2.77</v>
+        <v>2.62</v>
       </c>
       <c r="T54" t="n">
-        <v>2.75</v>
+        <v>2.96</v>
       </c>
       <c r="U54" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="V54" t="n">
-        <v>6.75</v>
+        <v>8</v>
       </c>
       <c r="W54" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X54" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z54" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AC54" t="n">
-        <v>3.35</v>
+        <v>3.48</v>
       </c>
       <c r="AD54" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AF54" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AG54" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AH54" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="AI54" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6962,77 +6962,77 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L55" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="M55" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N55" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="O55" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="P55" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="R55" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S55" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V55" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="W55" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X55" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA55" t="n">
         <v>2</v>
       </c>
-      <c r="M55" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N55" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O55" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="P55" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>4.26</v>
-      </c>
-      <c r="R55" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S55" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="T55" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="U55" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V55" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W55" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X55" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y55" t="n">
+      <c r="AB55" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AG55" t="n">
         <v>1.34</v>
       </c>
-      <c r="Z55" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AA55" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AE55" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AF55" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AG55" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AH55" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AI55" s="3" t="n">
         <v>46084.69791666666</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7081,77 +7081,77 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.85</v>
+        <v>2.45</v>
       </c>
       <c r="M56" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="N56" t="n">
-        <v>2.24</v>
+        <v>2.88</v>
       </c>
       <c r="O56" t="n">
-        <v>3.7</v>
+        <v>2.96</v>
       </c>
       <c r="P56" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.1</v>
+        <v>3.67</v>
       </c>
       <c r="R56" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="S56" t="n">
         <v>2.77</v>
       </c>
       <c r="T56" t="n">
-        <v>3.04</v>
+        <v>2.75</v>
       </c>
       <c r="U56" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="V56" t="n">
-        <v>7.6</v>
+        <v>6.75</v>
       </c>
       <c r="W56" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X56" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Z56" t="n">
-        <v>3.14</v>
+        <v>3.6</v>
       </c>
       <c r="AA56" t="n">
-        <v>2.19</v>
+        <v>1.93</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.71</v>
+        <v>1.85</v>
       </c>
       <c r="AC56" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="AD56" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AE56" t="n">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="AF56" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AG56" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AH56" t="n">
-        <v>1.38</v>
+        <v>1.52</v>
       </c>
       <c r="AI56" s="3" t="n">
         <v>46084.69791666666</v>
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,73 +7323,73 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="M58" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="N58" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="O58" t="n">
-        <v>2.95</v>
+        <v>2.62</v>
       </c>
       <c r="P58" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.42</v>
+        <v>4.26</v>
       </c>
       <c r="R58" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="S58" t="n">
-        <v>2.62</v>
+        <v>2.87</v>
       </c>
       <c r="T58" t="n">
-        <v>2.96</v>
+        <v>2.91</v>
       </c>
       <c r="U58" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="V58" t="n">
-        <v>8</v>
+        <v>7.1</v>
       </c>
       <c r="W58" t="n">
         <v>1.07</v>
       </c>
       <c r="X58" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="Z58" t="n">
-        <v>3.5</v>
+        <v>2.92</v>
       </c>
       <c r="AA58" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AC58" t="n">
-        <v>3.48</v>
+        <v>3.67</v>
       </c>
       <c r="AD58" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AE58" t="n">
-        <v>1.67</v>
+        <v>1.81</v>
       </c>
       <c r="AF58" t="n">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="AG58" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AH58" t="n">
-        <v>1.48</v>
+        <v>1.62</v>
       </c>
       <c r="AI58" s="3" t="n">
         <v>46084.69791666666</v>

--- a/jogos_2026-03-03.xlsx
+++ b/jogos_2026-03-03.xlsx
@@ -668,64 +668,64 @@
         <v>3.49</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46084.35416666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>5.48</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46084.4375</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46084.4375</v>
@@ -1501,64 +1501,64 @@
         <v>2.8</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46084.45833333334</v>
@@ -1977,40 +1977,40 @@
         <v>6.13</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA13" t="n">
         <v>2.03</v>
@@ -2019,22 +2019,22 @@
         <v>1.78</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46084.5625</v>
@@ -2920,22 +2920,22 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -2944,10 +2944,10 @@
         <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2959,34 +2959,34 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46084.625</v>
@@ -3039,22 +3039,22 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -3063,10 +3063,10 @@
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -3078,34 +3078,34 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46084.625</v>
@@ -3158,22 +3158,22 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -3182,10 +3182,10 @@
         <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -3197,34 +3197,34 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46084.625</v>
@@ -3396,22 +3396,22 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -3420,10 +3420,10 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -3435,34 +3435,34 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46084.625</v>
@@ -3634,22 +3634,22 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -3658,10 +3658,10 @@
         <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -3673,34 +3673,34 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46084.625</v>
@@ -4701,7 +4701,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L36" t="n">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,55 +5062,55 @@
         </is>
       </c>
       <c r="L39" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="M39" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N39" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AB39" t="n">
         <v>2.05</v>
-      </c>
-      <c r="M39" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="N39" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
-      <c r="R39" t="n">
-        <v>0</v>
-      </c>
-      <c r="S39" t="n">
-        <v>0</v>
-      </c>
-      <c r="T39" t="n">
-        <v>0</v>
-      </c>
-      <c r="U39" t="n">
-        <v>0</v>
-      </c>
-      <c r="V39" t="n">
-        <v>0</v>
-      </c>
-      <c r="W39" t="n">
-        <v>0</v>
-      </c>
-      <c r="X39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.63</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.49</v>
+        <v>2.05</v>
       </c>
       <c r="M40" t="n">
-        <v>3.8</v>
+        <v>3.56</v>
       </c>
       <c r="N40" t="n">
-        <v>2.86</v>
+        <v>4.05</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.68</v>
+        <v>2.15</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.05</v>
+        <v>1.63</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -6486,7 +6486,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L51" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>

--- a/jogos_2026-03-03.xlsx
+++ b/jogos_2026-03-03.xlsx
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.62</v>
+        <v>3.15</v>
       </c>
       <c r="M7" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="N7" t="n">
-        <v>4.75</v>
+        <v>1.95</v>
       </c>
       <c r="O7" t="n">
-        <v>2.2</v>
+        <v>3.86</v>
       </c>
       <c r="P7" t="n">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.48</v>
+        <v>2.5</v>
       </c>
       <c r="R7" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="S7" t="n">
-        <v>2.99</v>
+        <v>3.2</v>
       </c>
       <c r="T7" t="n">
-        <v>2.38</v>
+        <v>2.47</v>
       </c>
       <c r="U7" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V7" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AD7" t="n">
         <v>1.37</v>
       </c>
-      <c r="V7" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AE7" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.91</v>
+        <v>2.15</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.1</v>
+        <v>1.28</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46084.4375</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.15</v>
+        <v>1.62</v>
       </c>
       <c r="M8" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="N8" t="n">
-        <v>1.95</v>
+        <v>4.75</v>
       </c>
       <c r="O8" t="n">
-        <v>3.86</v>
+        <v>2.2</v>
       </c>
       <c r="P8" t="n">
-        <v>2.14</v>
+        <v>2.33</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.5</v>
+        <v>5.48</v>
       </c>
       <c r="R8" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="S8" t="n">
-        <v>3.2</v>
+        <v>2.99</v>
       </c>
       <c r="T8" t="n">
-        <v>2.47</v>
+        <v>2.38</v>
       </c>
       <c r="U8" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="V8" t="n">
-        <v>5.9</v>
+        <v>6.75</v>
       </c>
       <c r="W8" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.84</v>
+        <v>3.3</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.07</v>
+        <v>1.8</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.74</v>
+        <v>3.08</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.28</v>
+        <v>2.1</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46084.4375</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,22 +2920,22 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.75</v>
+        <v>4.5</v>
       </c>
       <c r="M21" t="n">
-        <v>3.65</v>
+        <v>3.2</v>
       </c>
       <c r="N21" t="n">
-        <v>2.24</v>
+        <v>1.62</v>
       </c>
       <c r="O21" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -2944,10 +2944,10 @@
         <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2959,34 +2959,34 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.48</v>
+        <v>2.3</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.28</v>
+        <v>1.53</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46084.625</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,22 +3039,22 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.86</v>
+        <v>2.75</v>
       </c>
       <c r="M22" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="N22" t="n">
-        <v>3.7</v>
+        <v>2.24</v>
       </c>
       <c r="O22" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="P22" t="n">
         <v>2.4</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.8</v>
+        <v>2.7</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -3063,10 +3063,10 @@
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="U22" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -3078,34 +3078,34 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.17</v>
+        <v>2.28</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.25</v>
+        <v>2.48</v>
       </c>
       <c r="AG22" t="n">
         <v>1.2</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.74</v>
+        <v>1.33</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46084.625</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.54</v>
+        <v>2.43</v>
       </c>
       <c r="M23" t="n">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="N23" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="O23" t="n">
-        <v>1.96</v>
+        <v>2.75</v>
       </c>
       <c r="P23" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF23" t="n">
         <v>2.55</v>
       </c>
-      <c r="Q23" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V23" t="n">
-        <v>0</v>
-      </c>
-      <c r="W23" t="n">
-        <v>0</v>
-      </c>
-      <c r="X23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>2.14</v>
-      </c>
       <c r="AG23" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.17</v>
+        <v>1.44</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46084.625</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,22 +3277,22 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.8</v>
+        <v>1.86</v>
       </c>
       <c r="M24" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="N24" t="n">
-        <v>2.5</v>
+        <v>3.7</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3301,10 +3301,10 @@
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -3316,34 +3316,34 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46084.625</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>4.5</v>
+        <v>2.8</v>
       </c>
       <c r="M26" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N26" t="n">
-        <v>1.62</v>
+        <v>2.5</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,22 +3634,22 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.43</v>
+        <v>1.54</v>
       </c>
       <c r="M27" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="N27" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="O27" t="n">
-        <v>2.75</v>
+        <v>1.96</v>
       </c>
       <c r="P27" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.9</v>
+        <v>4.8</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -3658,10 +3658,10 @@
         <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>2.02</v>
+        <v>2.07</v>
       </c>
       <c r="U27" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -3673,34 +3673,34 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Z27" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.36</v>
+        <v>1.52</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.55</v>
+        <v>2.14</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.44</v>
+        <v>2.17</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46084.625</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.4</v>
+        <v>3.47</v>
       </c>
       <c r="M30" t="n">
-        <v>4.6</v>
+        <v>3.2</v>
       </c>
       <c r="N30" t="n">
-        <v>7.03</v>
+        <v>2.11</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.87</v>
+        <v>2.65</v>
       </c>
       <c r="M31" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="N31" t="n">
-        <v>2.98</v>
+        <v>2.65</v>
       </c>
       <c r="O31" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46084.66666666666</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.65</v>
+        <v>1.4</v>
       </c>
       <c r="M32" t="n">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="N32" t="n">
-        <v>2.65</v>
+        <v>7.03</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.47</v>
+        <v>1.87</v>
       </c>
       <c r="M34" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="N34" t="n">
-        <v>2.11</v>
+        <v>2.98</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46084.66666666666</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46084.6875</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.75</v>
+        <v>4.28</v>
       </c>
       <c r="M38" t="n">
-        <v>3.91</v>
+        <v>4.2</v>
       </c>
       <c r="N38" t="n">
-        <v>5.33</v>
+        <v>1.66</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,73 +5419,73 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI42" s="3" t="n">
         <v>46084.6875</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,73 +5895,73 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.53</v>
+        <v>2.85</v>
       </c>
       <c r="M46" t="n">
-        <v>3.95</v>
+        <v>3.1</v>
       </c>
       <c r="N46" t="n">
-        <v>5</v>
+        <v>2.24</v>
       </c>
       <c r="O46" t="n">
-        <v>2.06</v>
+        <v>3.7</v>
       </c>
       <c r="P46" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="Q46" t="n">
-        <v>5.65</v>
+        <v>3.1</v>
       </c>
       <c r="R46" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S46" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T46" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="U46" t="n">
         <v>1.33</v>
       </c>
-      <c r="S46" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="T46" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="U46" t="n">
-        <v>1.41</v>
-      </c>
       <c r="V46" t="n">
-        <v>6.5</v>
+        <v>7.6</v>
       </c>
       <c r="W46" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="X46" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="Z46" t="n">
-        <v>3.5</v>
+        <v>3.14</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.78</v>
+        <v>2.19</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.93</v>
+        <v>1.71</v>
       </c>
       <c r="AC46" t="n">
-        <v>3</v>
+        <v>3.55</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AH46" t="n">
-        <v>2.31</v>
+        <v>1.38</v>
       </c>
       <c r="AI46" s="3" t="n">
         <v>46084.69791666666</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,73 +6014,73 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.53</v>
+        <v>2.1</v>
       </c>
       <c r="M47" t="n">
-        <v>4.3</v>
+        <v>3.38</v>
       </c>
       <c r="N47" t="n">
-        <v>5.53</v>
+        <v>3.08</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.65</v>
+        <v>2.03</v>
       </c>
       <c r="AB47" t="n">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI47" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6129,77 +6129,77 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.85</v>
+        <v>1.53</v>
       </c>
       <c r="M48" t="n">
-        <v>3.1</v>
+        <v>4.3</v>
       </c>
       <c r="N48" t="n">
-        <v>2.24</v>
+        <v>5.53</v>
       </c>
       <c r="O48" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X48" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.19</v>
+        <v>1.65</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.71</v>
+        <v>2.1</v>
       </c>
       <c r="AC48" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG48" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AI48" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6248,77 +6248,77 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>3.2</v>
+        <v>2.45</v>
       </c>
       <c r="M49" t="n">
-        <v>3.24</v>
+        <v>3.47</v>
       </c>
       <c r="N49" t="n">
-        <v>2.21</v>
+        <v>2.59</v>
       </c>
       <c r="O49" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="U49" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V49" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W49" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X49" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z49" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF49" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AG49" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AI49" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,73 +6490,73 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="M51" t="n">
-        <v>3.38</v>
+        <v>3.45</v>
       </c>
       <c r="N51" t="n">
-        <v>3.08</v>
+        <v>3.86</v>
       </c>
       <c r="O51" t="n">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="P51" t="n">
-        <v>2.19</v>
+        <v>2.11</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.5</v>
+        <v>4.25</v>
       </c>
       <c r="R51" t="n">
         <v>1.38</v>
       </c>
       <c r="S51" t="n">
-        <v>2.81</v>
+        <v>2.69</v>
       </c>
       <c r="T51" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="U51" t="n">
         <v>1.36</v>
       </c>
       <c r="V51" t="n">
-        <v>6.5</v>
+        <v>7.4</v>
       </c>
       <c r="W51" t="n">
         <v>1.03</v>
       </c>
       <c r="X51" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z51" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="AA51" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AB51" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AH51" t="n">
         <v>1.73</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE51" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF51" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG51" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AH51" t="n">
-        <v>1.55</v>
       </c>
       <c r="AI51" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6605,77 +6605,77 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="M52" t="n">
-        <v>3.54</v>
+        <v>3</v>
       </c>
       <c r="N52" t="n">
-        <v>2.47</v>
+        <v>2.7</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S52" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T52" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U52" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V52" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W52" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X52" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC52" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AD52" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG52" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH52" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AI52" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6724,77 +6724,77 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="M53" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="N53" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="O53" t="n">
-        <v>2.46</v>
+        <v>2.62</v>
       </c>
       <c r="P53" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="Q53" t="n">
-        <v>4.25</v>
+        <v>4.26</v>
       </c>
       <c r="R53" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="S53" t="n">
         <v>2.87</v>
       </c>
       <c r="T53" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="U53" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V53" t="n">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
       <c r="W53" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X53" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="Z53" t="n">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="AA53" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AC53" t="n">
-        <v>3.52</v>
+        <v>3.67</v>
       </c>
       <c r="AD53" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.86</v>
+        <v>1.96</v>
       </c>
       <c r="AG53" t="n">
         <v>1.27</v>
       </c>
       <c r="AH53" t="n">
-        <v>1.88</v>
+        <v>1.62</v>
       </c>
       <c r="AI53" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,73 +6847,73 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.45</v>
+        <v>3.2</v>
       </c>
       <c r="M54" t="n">
-        <v>3</v>
+        <v>3.24</v>
       </c>
       <c r="N54" t="n">
-        <v>2.7</v>
+        <v>2.21</v>
       </c>
       <c r="O54" t="n">
-        <v>2.95</v>
+        <v>3.92</v>
       </c>
       <c r="P54" t="n">
         <v>2.05</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.42</v>
+        <v>2.8</v>
       </c>
       <c r="R54" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="S54" t="n">
-        <v>2.62</v>
+        <v>2.77</v>
       </c>
       <c r="T54" t="n">
-        <v>2.96</v>
+        <v>2.73</v>
       </c>
       <c r="U54" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="V54" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="W54" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X54" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Z54" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="AA54" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.71</v>
+        <v>1.95</v>
       </c>
       <c r="AC54" t="n">
-        <v>3.48</v>
+        <v>3.3</v>
       </c>
       <c r="AD54" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AF54" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AG54" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH54" t="n">
-        <v>1.48</v>
+        <v>1.31</v>
       </c>
       <c r="AI54" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,73 +6966,73 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.91</v>
+        <v>2.45</v>
       </c>
       <c r="M55" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="N55" t="n">
-        <v>3.86</v>
+        <v>2.88</v>
       </c>
       <c r="O55" t="n">
-        <v>2.55</v>
+        <v>2.96</v>
       </c>
       <c r="P55" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="Q55" t="n">
-        <v>4.25</v>
+        <v>3.67</v>
       </c>
       <c r="R55" t="n">
         <v>1.38</v>
       </c>
       <c r="S55" t="n">
-        <v>2.69</v>
+        <v>2.77</v>
       </c>
       <c r="T55" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="U55" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="V55" t="n">
-        <v>7.4</v>
+        <v>6.75</v>
       </c>
       <c r="W55" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X55" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="Z55" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="AA55" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF55" t="n">
         <v>2</v>
       </c>
-      <c r="AB55" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE55" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF55" t="n">
-        <v>1.99</v>
-      </c>
       <c r="AG55" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.73</v>
+        <v>1.52</v>
       </c>
       <c r="AI55" s="3" t="n">
         <v>46084.69791666666</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,73 +7085,73 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="M56" t="n">
-        <v>3.4</v>
+        <v>3.54</v>
       </c>
       <c r="N56" t="n">
-        <v>2.88</v>
+        <v>2.47</v>
       </c>
       <c r="O56" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U56" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V56" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="W56" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X56" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z56" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC56" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AD56" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG56" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH56" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AI56" s="3" t="n">
         <v>46084.69791666666</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,73 +7204,73 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.45</v>
+        <v>1.53</v>
       </c>
       <c r="M57" t="n">
-        <v>3.47</v>
+        <v>3.95</v>
       </c>
       <c r="N57" t="n">
-        <v>2.59</v>
+        <v>5</v>
       </c>
       <c r="O57" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S57" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="T57" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U57" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V57" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W57" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X57" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y57" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z57" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC57" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD57" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE57" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF57" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG57" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH57" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AI57" s="3" t="n">
         <v>46084.69791666666</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7319,77 +7319,77 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="M58" t="n">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="N58" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="O58" t="n">
-        <v>2.62</v>
+        <v>2.46</v>
       </c>
       <c r="P58" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="Q58" t="n">
-        <v>4.26</v>
+        <v>4.25</v>
       </c>
       <c r="R58" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="S58" t="n">
         <v>2.87</v>
       </c>
       <c r="T58" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="U58" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V58" t="n">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="W58" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X58" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="Z58" t="n">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="AA58" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AC58" t="n">
-        <v>3.67</v>
+        <v>3.52</v>
       </c>
       <c r="AD58" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AE58" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AF58" t="n">
-        <v>1.96</v>
+        <v>1.86</v>
       </c>
       <c r="AG58" t="n">
         <v>1.27</v>
       </c>
       <c r="AH58" t="n">
-        <v>1.62</v>
+        <v>1.88</v>
       </c>
       <c r="AI58" s="3" t="n">
         <v>46084.69791666666</v>

--- a/jogos_2026-03-03.xlsx
+++ b/jogos_2026-03-03.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>4.5</v>
+        <v>2.8</v>
       </c>
       <c r="M21" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N21" t="n">
-        <v>1.62</v>
+        <v>2.5</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,22 +3039,22 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.75</v>
+        <v>1.86</v>
       </c>
       <c r="M22" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="N22" t="n">
-        <v>2.24</v>
+        <v>3.7</v>
       </c>
       <c r="O22" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="P22" t="n">
         <v>2.4</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.7</v>
+        <v>3.8</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -3063,10 +3063,10 @@
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.08</v>
+        <v>2.17</v>
       </c>
       <c r="U22" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -3078,34 +3078,34 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.28</v>
+        <v>2.17</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.48</v>
+        <v>2.25</v>
       </c>
       <c r="AG22" t="n">
         <v>1.2</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.33</v>
+        <v>1.74</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46084.625</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,22 +3158,22 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.43</v>
+        <v>1.54</v>
       </c>
       <c r="M23" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="N23" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="O23" t="n">
-        <v>2.75</v>
+        <v>1.96</v>
       </c>
       <c r="P23" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.9</v>
+        <v>4.8</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -3182,10 +3182,10 @@
         <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.02</v>
+        <v>2.07</v>
       </c>
       <c r="U23" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -3197,34 +3197,34 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.36</v>
+        <v>1.52</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.55</v>
+        <v>2.14</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.44</v>
+        <v>2.17</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46084.625</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,22 +3277,22 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.86</v>
+        <v>2.43</v>
       </c>
       <c r="M24" t="n">
         <v>3.7</v>
       </c>
       <c r="N24" t="n">
-        <v>3.7</v>
+        <v>2.5</v>
       </c>
       <c r="O24" t="n">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="P24" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3301,10 +3301,10 @@
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.17</v>
+        <v>2.02</v>
       </c>
       <c r="U24" t="n">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -3316,34 +3316,34 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.54</v>
+        <v>1.45</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.17</v>
+        <v>2.38</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.25</v>
+        <v>2.55</v>
       </c>
       <c r="AG24" t="n">
         <v>1.2</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.74</v>
+        <v>1.44</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46084.625</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,22 +3396,22 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.81</v>
+        <v>2.75</v>
       </c>
       <c r="M25" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="N25" t="n">
-        <v>3.95</v>
+        <v>2.24</v>
       </c>
       <c r="O25" t="n">
-        <v>2.25</v>
+        <v>3.1</v>
       </c>
       <c r="P25" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="Q25" t="n">
-        <v>4</v>
+        <v>2.7</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -3420,49 +3420,49 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AB25" t="n">
         <v>2.28</v>
       </c>
-      <c r="U25" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="V25" t="n">
-        <v>0</v>
-      </c>
-      <c r="W25" t="n">
-        <v>0</v>
-      </c>
-      <c r="X25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>2</v>
-      </c>
       <c r="AC25" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.38</v>
+        <v>1.52</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.08</v>
+        <v>2.48</v>
       </c>
       <c r="AG25" t="n">
         <v>1.2</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.8</v>
+        <v>1.33</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46084.625</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.8</v>
+        <v>4.5</v>
       </c>
       <c r="M26" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N26" t="n">
-        <v>2.5</v>
+        <v>1.62</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,22 +3634,22 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.54</v>
+        <v>1.81</v>
       </c>
       <c r="M27" t="n">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="N27" t="n">
-        <v>5</v>
+        <v>3.95</v>
       </c>
       <c r="O27" t="n">
-        <v>1.96</v>
+        <v>2.25</v>
       </c>
       <c r="P27" t="n">
-        <v>2.55</v>
+        <v>2.38</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -3658,10 +3658,10 @@
         <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>2.07</v>
+        <v>2.28</v>
       </c>
       <c r="U27" t="n">
-        <v>1.6</v>
+        <v>1.49</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -3673,34 +3673,34 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="Z27" t="n">
-        <v>4.4</v>
+        <v>3.75</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.47</v>
+        <v>1.64</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.32</v>
+        <v>2</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.17</v>
+        <v>2.6</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.54</v>
+        <v>1.38</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AH27" t="n">
-        <v>2.17</v>
+        <v>1.8</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46084.625</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.47</v>
+        <v>1.4</v>
       </c>
       <c r="M30" t="n">
-        <v>3.2</v>
+        <v>4.6</v>
       </c>
       <c r="N30" t="n">
-        <v>2.11</v>
+        <v>7.03</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.4</v>
+        <v>3.47</v>
       </c>
       <c r="M32" t="n">
-        <v>4.6</v>
+        <v>3.2</v>
       </c>
       <c r="N32" t="n">
-        <v>7.03</v>
+        <v>2.11</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.72</v>
+        <v>1.87</v>
       </c>
       <c r="M33" t="n">
-        <v>3.15</v>
+        <v>3.8</v>
       </c>
       <c r="N33" t="n">
-        <v>2.05</v>
+        <v>2.98</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46084.66666666666</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.87</v>
+        <v>3.72</v>
       </c>
       <c r="M34" t="n">
-        <v>3.8</v>
+        <v>3.15</v>
       </c>
       <c r="N34" t="n">
-        <v>2.98</v>
+        <v>2.05</v>
       </c>
       <c r="O34" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46084.66666666666</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,73 +5419,73 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.45</v>
+        <v>2.05</v>
       </c>
       <c r="M42" t="n">
-        <v>3.3</v>
+        <v>3.56</v>
       </c>
       <c r="N42" t="n">
-        <v>2.43</v>
+        <v>4.05</v>
       </c>
       <c r="O42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.67</v>
+        <v>2.15</v>
       </c>
       <c r="AB42" t="n">
-        <v>2.1</v>
+        <v>1.63</v>
       </c>
       <c r="AC42" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI42" s="3" t="n">
         <v>46084.6875</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,73 +5776,73 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46084.6875</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5891,77 +5891,77 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.85</v>
+        <v>2.45</v>
       </c>
       <c r="M46" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="N46" t="n">
-        <v>2.24</v>
+        <v>2.7</v>
       </c>
       <c r="O46" t="n">
-        <v>3.7</v>
+        <v>2.95</v>
       </c>
       <c r="P46" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.1</v>
+        <v>3.42</v>
       </c>
       <c r="R46" t="n">
         <v>1.44</v>
       </c>
       <c r="S46" t="n">
-        <v>2.77</v>
+        <v>2.62</v>
       </c>
       <c r="T46" t="n">
-        <v>3.04</v>
+        <v>2.96</v>
       </c>
       <c r="U46" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="V46" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="W46" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X46" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z46" t="n">
-        <v>3.14</v>
+        <v>3.5</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.19</v>
+        <v>2</v>
       </c>
       <c r="AB46" t="n">
         <v>1.71</v>
       </c>
       <c r="AC46" t="n">
-        <v>3.55</v>
+        <v>3.48</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="AI46" s="3" t="n">
         <v>46084.69791666666</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6010,77 +6010,77 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="M47" t="n">
-        <v>3.38</v>
+        <v>3.24</v>
       </c>
       <c r="N47" t="n">
-        <v>3.08</v>
+        <v>2.21</v>
       </c>
       <c r="O47" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="P47" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q47" t="n">
         <v>2.8</v>
-      </c>
-      <c r="P47" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>3.5</v>
       </c>
       <c r="R47" t="n">
         <v>1.38</v>
       </c>
       <c r="S47" t="n">
-        <v>2.81</v>
+        <v>2.77</v>
       </c>
       <c r="T47" t="n">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="U47" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="V47" t="n">
         <v>6.5</v>
       </c>
       <c r="W47" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X47" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z47" t="n">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.03</v>
+        <v>1.88</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="AC47" t="n">
         <v>3.3</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="AG47" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.55</v>
+        <v>1.31</v>
       </c>
       <c r="AI47" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6129,77 +6129,77 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.53</v>
+        <v>2</v>
       </c>
       <c r="M48" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="N48" t="n">
-        <v>5.53</v>
+        <v>3.5</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.65</v>
+        <v>2.07</v>
       </c>
       <c r="AB48" t="n">
-        <v>2.1</v>
+        <v>1.72</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH48" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI48" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="M49" t="n">
-        <v>3.47</v>
+        <v>3.54</v>
       </c>
       <c r="N49" t="n">
-        <v>2.59</v>
+        <v>2.47</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,73 +6371,73 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.45</v>
+        <v>1.53</v>
       </c>
       <c r="M50" t="n">
-        <v>3.2</v>
+        <v>3.95</v>
       </c>
       <c r="N50" t="n">
-        <v>2.72</v>
+        <v>5</v>
       </c>
       <c r="O50" t="n">
-        <v>3.1</v>
+        <v>2.06</v>
       </c>
       <c r="P50" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.5</v>
+        <v>5.65</v>
       </c>
       <c r="R50" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="S50" t="n">
-        <v>2.69</v>
+        <v>2.91</v>
       </c>
       <c r="T50" t="n">
-        <v>2.65</v>
+        <v>2.48</v>
       </c>
       <c r="U50" t="n">
         <v>1.41</v>
       </c>
       <c r="V50" t="n">
-        <v>6.95</v>
+        <v>6.5</v>
       </c>
       <c r="W50" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="X50" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="Z50" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.98</v>
+        <v>1.78</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.75</v>
+        <v>1.93</v>
       </c>
       <c r="AC50" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="AF50" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AG50" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AH50" t="n">
-        <v>1.53</v>
+        <v>2.31</v>
       </c>
       <c r="AI50" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,73 +6490,73 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.91</v>
+        <v>2.45</v>
       </c>
       <c r="M51" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="N51" t="n">
-        <v>3.86</v>
+        <v>2.88</v>
       </c>
       <c r="O51" t="n">
-        <v>2.55</v>
+        <v>2.96</v>
       </c>
       <c r="P51" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="Q51" t="n">
-        <v>4.25</v>
+        <v>3.67</v>
       </c>
       <c r="R51" t="n">
         <v>1.38</v>
       </c>
       <c r="S51" t="n">
-        <v>2.69</v>
+        <v>2.77</v>
       </c>
       <c r="T51" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="U51" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="V51" t="n">
-        <v>7.4</v>
+        <v>6.75</v>
       </c>
       <c r="W51" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X51" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="Z51" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="AA51" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF51" t="n">
         <v>2</v>
       </c>
-      <c r="AB51" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE51" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF51" t="n">
-        <v>1.99</v>
-      </c>
       <c r="AG51" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="AH51" t="n">
-        <v>1.73</v>
+        <v>1.52</v>
       </c>
       <c r="AI51" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6605,77 +6605,77 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="M52" t="n">
-        <v>3</v>
+        <v>3.38</v>
       </c>
       <c r="N52" t="n">
-        <v>2.7</v>
+        <v>3.08</v>
       </c>
       <c r="O52" t="n">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="P52" t="n">
-        <v>2.05</v>
+        <v>2.19</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="R52" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="S52" t="n">
-        <v>2.62</v>
+        <v>2.81</v>
       </c>
       <c r="T52" t="n">
-        <v>2.96</v>
+        <v>2.75</v>
       </c>
       <c r="U52" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="V52" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="W52" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X52" t="n">
         <v>1.06</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Z52" t="n">
-        <v>3.5</v>
+        <v>3.24</v>
       </c>
       <c r="AA52" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AC52" t="n">
-        <v>3.48</v>
+        <v>3.3</v>
       </c>
       <c r="AD52" t="n">
         <v>1.29</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AF52" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AG52" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AI52" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6724,77 +6724,77 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2</v>
+        <v>1.53</v>
       </c>
       <c r="M53" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="N53" t="n">
-        <v>3.5</v>
+        <v>5.53</v>
       </c>
       <c r="O53" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>4.26</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="U53" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V53" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="W53" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X53" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>2.07</v>
+        <v>1.65</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.72</v>
+        <v>2.1</v>
       </c>
       <c r="AC53" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="AD53" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG53" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH53" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI53" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6843,77 +6843,77 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>3.2</v>
+        <v>2.45</v>
       </c>
       <c r="M54" t="n">
-        <v>3.24</v>
+        <v>3.47</v>
       </c>
       <c r="N54" t="n">
-        <v>2.21</v>
+        <v>2.59</v>
       </c>
       <c r="O54" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="U54" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V54" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W54" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X54" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z54" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD54" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF54" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AG54" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH54" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AI54" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,73 +6966,73 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.45</v>
+        <v>1.8</v>
       </c>
       <c r="M55" t="n">
-        <v>3.4</v>
+        <v>3.26</v>
       </c>
       <c r="N55" t="n">
-        <v>2.88</v>
+        <v>4</v>
       </c>
       <c r="O55" t="n">
-        <v>2.96</v>
+        <v>2.46</v>
       </c>
       <c r="P55" t="n">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.67</v>
+        <v>4.25</v>
       </c>
       <c r="R55" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S55" t="n">
-        <v>2.77</v>
+        <v>2.87</v>
       </c>
       <c r="T55" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="U55" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="V55" t="n">
-        <v>6.75</v>
+        <v>7.5</v>
       </c>
       <c r="W55" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X55" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="Z55" t="n">
-        <v>3.6</v>
+        <v>3.05</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AB55" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE55" t="n">
         <v>1.85</v>
       </c>
-      <c r="AC55" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AE55" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AF55" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AG55" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.52</v>
+        <v>1.88</v>
       </c>
       <c r="AI55" s="3" t="n">
         <v>46084.69791666666</v>
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,73 +7085,73 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.6</v>
+        <v>2.85</v>
       </c>
       <c r="M56" t="n">
-        <v>3.54</v>
+        <v>3.1</v>
       </c>
       <c r="N56" t="n">
-        <v>2.47</v>
+        <v>2.24</v>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S56" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T56" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U56" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V56" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="W56" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X56" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC56" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AD56" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE56" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF56" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG56" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH56" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI56" s="3" t="n">
         <v>46084.69791666666</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,73 +7204,73 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.53</v>
+        <v>2.45</v>
       </c>
       <c r="M57" t="n">
-        <v>3.95</v>
+        <v>3.2</v>
       </c>
       <c r="N57" t="n">
-        <v>5</v>
+        <v>2.72</v>
       </c>
       <c r="O57" t="n">
-        <v>2.06</v>
+        <v>3.1</v>
       </c>
       <c r="P57" t="n">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="Q57" t="n">
-        <v>5.65</v>
+        <v>3.5</v>
       </c>
       <c r="R57" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="S57" t="n">
-        <v>2.91</v>
+        <v>2.69</v>
       </c>
       <c r="T57" t="n">
-        <v>2.48</v>
+        <v>2.65</v>
       </c>
       <c r="U57" t="n">
         <v>1.41</v>
       </c>
       <c r="V57" t="n">
-        <v>6.5</v>
+        <v>6.95</v>
       </c>
       <c r="W57" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="X57" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="Z57" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.78</v>
+        <v>1.98</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.93</v>
+        <v>1.75</v>
       </c>
       <c r="AC57" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="AD57" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.84</v>
+        <v>1.73</v>
       </c>
       <c r="AF57" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AG57" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AH57" t="n">
-        <v>2.31</v>
+        <v>1.53</v>
       </c>
       <c r="AI57" s="3" t="n">
         <v>46084.69791666666</v>
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,37 +7323,37 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="M58" t="n">
-        <v>3.26</v>
+        <v>3.45</v>
       </c>
       <c r="N58" t="n">
-        <v>4</v>
+        <v>3.86</v>
       </c>
       <c r="O58" t="n">
-        <v>2.46</v>
+        <v>2.55</v>
       </c>
       <c r="P58" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="Q58" t="n">
         <v>4.25</v>
       </c>
       <c r="R58" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S58" t="n">
-        <v>2.87</v>
+        <v>2.69</v>
       </c>
       <c r="T58" t="n">
-        <v>2.9</v>
+        <v>2.65</v>
       </c>
       <c r="U58" t="n">
         <v>1.36</v>
       </c>
       <c r="V58" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="W58" t="n">
         <v>1.03</v>
@@ -7362,34 +7362,34 @@
         <v>1</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="Z58" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="AA58" t="n">
         <v>2</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.67</v>
+        <v>1.81</v>
       </c>
       <c r="AC58" t="n">
-        <v>3.52</v>
+        <v>3.34</v>
       </c>
       <c r="AD58" t="n">
         <v>1.24</v>
       </c>
       <c r="AE58" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AF58" t="n">
-        <v>1.86</v>
+        <v>1.99</v>
       </c>
       <c r="AG58" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="AH58" t="n">
-        <v>1.88</v>
+        <v>1.73</v>
       </c>
       <c r="AI58" s="3" t="n">
         <v>46084.69791666666</v>

--- a/jogos_2026-03-03.xlsx
+++ b/jogos_2026-03-03.xlsx
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.8</v>
+        <v>4.5</v>
       </c>
       <c r="M21" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N21" t="n">
-        <v>2.5</v>
+        <v>1.62</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,22 +3039,22 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.86</v>
+        <v>2.43</v>
       </c>
       <c r="M22" t="n">
         <v>3.7</v>
       </c>
       <c r="N22" t="n">
-        <v>3.7</v>
+        <v>2.5</v>
       </c>
       <c r="O22" t="n">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="P22" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -3063,10 +3063,10 @@
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.17</v>
+        <v>2.02</v>
       </c>
       <c r="U22" t="n">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -3078,34 +3078,34 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.54</v>
+        <v>1.45</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.17</v>
+        <v>2.38</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.25</v>
+        <v>2.55</v>
       </c>
       <c r="AG22" t="n">
         <v>1.2</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.74</v>
+        <v>1.44</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46084.625</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,22 +3277,22 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.43</v>
+        <v>1.86</v>
       </c>
       <c r="M24" t="n">
         <v>3.7</v>
       </c>
       <c r="N24" t="n">
-        <v>2.5</v>
+        <v>3.7</v>
       </c>
       <c r="O24" t="n">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="P24" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3301,10 +3301,10 @@
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.02</v>
+        <v>2.17</v>
       </c>
       <c r="U24" t="n">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -3316,34 +3316,34 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.45</v>
+        <v>1.54</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.38</v>
+        <v>2.17</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.1</v>
+        <v>2.33</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.57</v>
+        <v>1.46</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.55</v>
+        <v>2.25</v>
       </c>
       <c r="AG24" t="n">
         <v>1.2</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.44</v>
+        <v>1.74</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46084.625</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,22 +3515,22 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>4.5</v>
+        <v>1.81</v>
       </c>
       <c r="M26" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="N26" t="n">
-        <v>1.62</v>
+        <v>3.95</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -3539,10 +3539,10 @@
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -3554,34 +3554,34 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.3</v>
+        <v>1.64</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.53</v>
+        <v>2</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46084.625</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,22 +3634,22 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.81</v>
+        <v>2.8</v>
       </c>
       <c r="M27" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="N27" t="n">
-        <v>3.95</v>
+        <v>2.5</v>
       </c>
       <c r="O27" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -3658,10 +3658,10 @@
         <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -3673,34 +3673,34 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46084.625</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.65</v>
+        <v>3.72</v>
       </c>
       <c r="M31" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="N31" t="n">
-        <v>2.65</v>
+        <v>2.05</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.72</v>
+        <v>2.65</v>
       </c>
       <c r="M34" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="N34" t="n">
-        <v>2.05</v>
+        <v>2.65</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="M42" t="n">
-        <v>3.56</v>
+        <v>3.91</v>
       </c>
       <c r="N42" t="n">
-        <v>4.05</v>
+        <v>5.33</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.63</v>
+        <v>1.85</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,73 +5538,73 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>46084.6875</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>5.33</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,73 +5776,73 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.45</v>
+        <v>2.49</v>
       </c>
       <c r="M45" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="N45" t="n">
-        <v>2.43</v>
+        <v>2.86</v>
       </c>
       <c r="O45" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AB45" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC45" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46084.6875</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5891,77 +5891,77 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.45</v>
+        <v>1.53</v>
       </c>
       <c r="M46" t="n">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="N46" t="n">
-        <v>2.7</v>
+        <v>5.53</v>
       </c>
       <c r="O46" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.71</v>
+        <v>2.1</v>
       </c>
       <c r="AC46" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AI46" s="3" t="n">
         <v>46084.69791666666</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6010,77 +6010,77 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="M47" t="n">
-        <v>3.24</v>
+        <v>3.38</v>
       </c>
       <c r="N47" t="n">
-        <v>2.21</v>
+        <v>3.08</v>
       </c>
       <c r="O47" t="n">
-        <v>3.92</v>
+        <v>2.8</v>
       </c>
       <c r="P47" t="n">
-        <v>2.05</v>
+        <v>2.19</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="R47" t="n">
         <v>1.38</v>
       </c>
       <c r="S47" t="n">
-        <v>2.77</v>
+        <v>2.81</v>
       </c>
       <c r="T47" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="U47" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="V47" t="n">
         <v>6.5</v>
       </c>
       <c r="W47" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X47" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z47" t="n">
-        <v>3.2</v>
+        <v>3.24</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.88</v>
+        <v>2.03</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="AC47" t="n">
         <v>3.3</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AF47" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="AG47" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.31</v>
+        <v>1.55</v>
       </c>
       <c r="AI47" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6129,77 +6129,77 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="M48" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="N48" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="O48" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P48" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q48" t="n">
         <v>3.5</v>
       </c>
-      <c r="O48" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="P48" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>4.26</v>
-      </c>
       <c r="R48" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S48" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U48" t="n">
         <v>1.41</v>
       </c>
-      <c r="S48" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="T48" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="U48" t="n">
+      <c r="V48" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="W48" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X48" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG48" t="n">
         <v>1.33</v>
       </c>
-      <c r="V48" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W48" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X48" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AE48" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AF48" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AG48" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AH48" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AI48" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,73 +6252,73 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.6</v>
+        <v>1.91</v>
       </c>
       <c r="M49" t="n">
-        <v>3.54</v>
+        <v>3.45</v>
       </c>
       <c r="N49" t="n">
-        <v>2.47</v>
+        <v>3.86</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH49" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI49" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,73 +6371,73 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.53</v>
+        <v>2.45</v>
       </c>
       <c r="M50" t="n">
-        <v>3.95</v>
+        <v>3.47</v>
       </c>
       <c r="N50" t="n">
-        <v>5</v>
+        <v>2.59</v>
       </c>
       <c r="O50" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="U50" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="V50" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W50" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X50" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Z50" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG50" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AH50" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AI50" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,73 +6609,73 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="M52" t="n">
-        <v>3.38</v>
+        <v>3.54</v>
       </c>
       <c r="N52" t="n">
-        <v>3.08</v>
+        <v>2.47</v>
       </c>
       <c r="O52" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U52" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V52" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W52" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X52" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z52" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD52" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG52" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI52" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6724,77 +6724,77 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.53</v>
+        <v>3.2</v>
       </c>
       <c r="M53" t="n">
-        <v>4.3</v>
+        <v>3.24</v>
       </c>
       <c r="N53" t="n">
-        <v>5.53</v>
+        <v>2.21</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V53" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W53" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.65</v>
+        <v>1.88</v>
       </c>
       <c r="AB53" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD53" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AG53" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH53" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AI53" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,73 +6847,73 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.45</v>
+        <v>1.53</v>
       </c>
       <c r="M54" t="n">
-        <v>3.47</v>
+        <v>3.95</v>
       </c>
       <c r="N54" t="n">
-        <v>2.59</v>
+        <v>5</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S54" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="T54" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U54" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V54" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W54" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X54" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD54" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG54" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH54" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AI54" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6962,77 +6962,77 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="M55" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="N55" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="O55" t="n">
-        <v>2.46</v>
+        <v>2.62</v>
       </c>
       <c r="P55" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="Q55" t="n">
-        <v>4.25</v>
+        <v>4.26</v>
       </c>
       <c r="R55" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="S55" t="n">
         <v>2.87</v>
       </c>
       <c r="T55" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="U55" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V55" t="n">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
       <c r="W55" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X55" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="Z55" t="n">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="AA55" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AC55" t="n">
-        <v>3.52</v>
+        <v>3.67</v>
       </c>
       <c r="AD55" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.86</v>
+        <v>1.96</v>
       </c>
       <c r="AG55" t="n">
         <v>1.27</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.88</v>
+        <v>1.62</v>
       </c>
       <c r="AI55" s="3" t="n">
         <v>46084.69791666666</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7200,77 +7200,77 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L57" t="n">
         <v>2.45</v>
       </c>
       <c r="M57" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="N57" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="O57" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="P57" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="R57" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="S57" t="n">
-        <v>2.69</v>
+        <v>2.62</v>
       </c>
       <c r="T57" t="n">
-        <v>2.65</v>
+        <v>2.96</v>
       </c>
       <c r="U57" t="n">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="V57" t="n">
-        <v>6.95</v>
+        <v>8</v>
       </c>
       <c r="W57" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X57" t="n">
         <v>1.06</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="Z57" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AC57" t="n">
-        <v>3.2</v>
+        <v>3.48</v>
       </c>
       <c r="AD57" t="n">
         <v>1.29</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AF57" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AG57" t="n">
         <v>1.33</v>
       </c>
       <c r="AH57" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AI57" s="3" t="n">
         <v>46084.69791666666</v>
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,37 +7323,37 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="M58" t="n">
-        <v>3.45</v>
+        <v>3.26</v>
       </c>
       <c r="N58" t="n">
-        <v>3.86</v>
+        <v>4</v>
       </c>
       <c r="O58" t="n">
-        <v>2.55</v>
+        <v>2.46</v>
       </c>
       <c r="P58" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="Q58" t="n">
         <v>4.25</v>
       </c>
       <c r="R58" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S58" t="n">
-        <v>2.69</v>
+        <v>2.87</v>
       </c>
       <c r="T58" t="n">
-        <v>2.65</v>
+        <v>2.9</v>
       </c>
       <c r="U58" t="n">
         <v>1.36</v>
       </c>
       <c r="V58" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="W58" t="n">
         <v>1.03</v>
@@ -7362,34 +7362,34 @@
         <v>1</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="Z58" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="AA58" t="n">
         <v>2</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="AC58" t="n">
-        <v>3.34</v>
+        <v>3.52</v>
       </c>
       <c r="AD58" t="n">
         <v>1.24</v>
       </c>
       <c r="AE58" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AF58" t="n">
-        <v>1.99</v>
+        <v>1.86</v>
       </c>
       <c r="AG58" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="AH58" t="n">
-        <v>1.73</v>
+        <v>1.88</v>
       </c>
       <c r="AI58" s="3" t="n">
         <v>46084.69791666666</v>

--- a/jogos_2026-03-03.xlsx
+++ b/jogos_2026-03-03.xlsx
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.15</v>
+        <v>1.62</v>
       </c>
       <c r="M7" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="N7" t="n">
-        <v>1.95</v>
+        <v>4.75</v>
       </c>
       <c r="O7" t="n">
-        <v>3.86</v>
+        <v>2.2</v>
       </c>
       <c r="P7" t="n">
-        <v>2.14</v>
+        <v>2.33</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.5</v>
+        <v>5.48</v>
       </c>
       <c r="R7" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="S7" t="n">
-        <v>3.2</v>
+        <v>2.99</v>
       </c>
       <c r="T7" t="n">
-        <v>2.47</v>
+        <v>2.38</v>
       </c>
       <c r="U7" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="V7" t="n">
-        <v>5.9</v>
+        <v>6.75</v>
       </c>
       <c r="W7" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X7" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.84</v>
+        <v>3.3</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.07</v>
+        <v>1.8</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.74</v>
+        <v>3.08</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.28</v>
+        <v>2.1</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46084.4375</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.62</v>
+        <v>3.15</v>
       </c>
       <c r="M8" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="N8" t="n">
-        <v>4.75</v>
+        <v>1.95</v>
       </c>
       <c r="O8" t="n">
-        <v>2.2</v>
+        <v>3.86</v>
       </c>
       <c r="P8" t="n">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.48</v>
+        <v>2.5</v>
       </c>
       <c r="R8" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="S8" t="n">
-        <v>2.99</v>
+        <v>3.2</v>
       </c>
       <c r="T8" t="n">
-        <v>2.38</v>
+        <v>2.47</v>
       </c>
       <c r="U8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V8" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AD8" t="n">
         <v>1.37</v>
       </c>
-      <c r="V8" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AE8" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.91</v>
+        <v>2.15</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.1</v>
+        <v>1.28</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46084.4375</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,22 +2920,22 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>4.5</v>
+        <v>2.75</v>
       </c>
       <c r="M21" t="n">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="N21" t="n">
-        <v>1.62</v>
+        <v>2.24</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -2944,10 +2944,10 @@
         <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2959,34 +2959,34 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.3</v>
+        <v>1.48</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.53</v>
+        <v>2.28</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46084.625</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,22 +3039,22 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.43</v>
+        <v>4.5</v>
       </c>
       <c r="M22" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="N22" t="n">
-        <v>2.5</v>
+        <v>1.62</v>
       </c>
       <c r="O22" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -3063,10 +3063,10 @@
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -3078,34 +3078,34 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.45</v>
+        <v>2.3</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.38</v>
+        <v>1.53</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46084.625</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,35 +3158,35 @@
         </is>
       </c>
       <c r="L23" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N23" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O23" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="U23" t="n">
         <v>1.54</v>
       </c>
-      <c r="M23" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="N23" t="n">
-        <v>5</v>
-      </c>
-      <c r="O23" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.6</v>
-      </c>
       <c r="V23" t="n">
         <v>0</v>
       </c>
@@ -3197,34 +3197,34 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="AA23" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AE23" t="n">
         <v>1.47</v>
       </c>
-      <c r="AB23" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.52</v>
-      </c>
       <c r="AF23" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.17</v>
+        <v>1.74</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46084.625</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,22 +3277,22 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.86</v>
+        <v>1.54</v>
       </c>
       <c r="M24" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="N24" t="n">
-        <v>3.7</v>
+        <v>5</v>
       </c>
       <c r="O24" t="n">
-        <v>2.3</v>
+        <v>1.96</v>
       </c>
       <c r="P24" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3301,49 +3301,49 @@
         <v>0</v>
       </c>
       <c r="T24" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AC24" t="n">
         <v>2.17</v>
       </c>
-      <c r="U24" t="n">
+      <c r="AD24" t="n">
         <v>1.54</v>
       </c>
-      <c r="V24" t="n">
-        <v>0</v>
-      </c>
-      <c r="W24" t="n">
-        <v>0</v>
-      </c>
-      <c r="X24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AB24" t="n">
+      <c r="AE24" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AH24" t="n">
         <v>2.17</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.74</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46084.625</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,22 +3396,22 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.75</v>
+        <v>1.81</v>
       </c>
       <c r="M25" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="N25" t="n">
-        <v>2.24</v>
+        <v>3.95</v>
       </c>
       <c r="O25" t="n">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="P25" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.7</v>
+        <v>4</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -3420,49 +3420,49 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AF25" t="n">
         <v>2.08</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="V25" t="n">
-        <v>0</v>
-      </c>
-      <c r="W25" t="n">
-        <v>0</v>
-      </c>
-      <c r="X25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>2.48</v>
       </c>
       <c r="AG25" t="n">
         <v>1.2</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.33</v>
+        <v>1.8</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46084.625</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.81</v>
+        <v>2.43</v>
       </c>
       <c r="M26" t="n">
         <v>3.7</v>
       </c>
       <c r="N26" t="n">
-        <v>3.95</v>
+        <v>2.5</v>
       </c>
       <c r="O26" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="P26" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AB26" t="n">
         <v>2.38</v>
       </c>
-      <c r="Q26" t="n">
-        <v>4</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="V26" t="n">
-        <v>0</v>
-      </c>
-      <c r="W26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>2</v>
-      </c>
       <c r="AC26" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.38</v>
+        <v>1.57</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.55</v>
+        <v>1.36</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.08</v>
+        <v>2.55</v>
       </c>
       <c r="AG26" t="n">
         <v>1.2</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.8</v>
+        <v>1.44</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46084.625</v>
@@ -3643,25 +3643,25 @@
         <v>2.5</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -3673,34 +3673,34 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46084.625</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,34 +3991,34 @@
         </is>
       </c>
       <c r="L30" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="M30" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N30" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="O30" t="n">
+        <v>4</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R30" t="n">
         <v>1.4</v>
       </c>
-      <c r="M30" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="N30" t="n">
-        <v>7.03</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V30" t="n">
         <v>0</v>
@@ -4030,34 +4030,34 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46084.66666666666</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.72</v>
+        <v>1.87</v>
       </c>
       <c r="M31" t="n">
-        <v>3.15</v>
+        <v>3.8</v>
       </c>
       <c r="N31" t="n">
-        <v>2.05</v>
+        <v>2.98</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46084.66666666666</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,34 +4229,34 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.47</v>
+        <v>2.65</v>
       </c>
       <c r="M32" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N32" t="n">
-        <v>2.11</v>
+        <v>2.65</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
@@ -4268,34 +4268,34 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46084.66666666666</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.87</v>
+        <v>3.72</v>
       </c>
       <c r="M33" t="n">
-        <v>3.8</v>
+        <v>3.15</v>
       </c>
       <c r="N33" t="n">
-        <v>2.98</v>
+        <v>2.05</v>
       </c>
       <c r="O33" t="n">
-        <v>2.38</v>
+        <v>4.2</v>
       </c>
       <c r="P33" t="n">
-        <v>2.38</v>
+        <v>2.08</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.3</v>
+        <v>2.75</v>
       </c>
       <c r="R33" t="n">
-        <v>1.21</v>
+        <v>1.44</v>
       </c>
       <c r="S33" t="n">
-        <v>3.68</v>
+        <v>2.55</v>
       </c>
       <c r="T33" t="n">
-        <v>2.08</v>
+        <v>3.1</v>
       </c>
       <c r="U33" t="n">
-        <v>1.69</v>
+        <v>1.3</v>
       </c>
       <c r="V33" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.08</v>
+        <v>1.38</v>
       </c>
       <c r="Z33" t="n">
-        <v>5.5</v>
+        <v>2.7</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.44</v>
+        <v>2.23</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.63</v>
+        <v>1.57</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.1</v>
+        <v>4</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.67</v>
+        <v>1.19</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.4</v>
+        <v>1.94</v>
       </c>
       <c r="AF33" t="n">
-        <v>2.75</v>
+        <v>1.75</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.7</v>
+        <v>1.22</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46084.66666666666</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,22 +4467,22 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.65</v>
+        <v>1.4</v>
       </c>
       <c r="M34" t="n">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="N34" t="n">
-        <v>2.65</v>
+        <v>7.03</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -4491,10 +4491,10 @@
         <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V34" t="n">
         <v>0</v>
@@ -4506,34 +4506,34 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46084.66666666666</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,22 +4705,22 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -4729,49 +4729,49 @@
         <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X36" t="n">
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46084.6875</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,73 +5062,73 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46084.6875</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,73 +5181,73 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46084.6875</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,73 +5300,73 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="M41" t="n">
-        <v>3.56</v>
+        <v>3.91</v>
       </c>
       <c r="N41" t="n">
-        <v>4.05</v>
+        <v>5.33</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.63</v>
+        <v>1.85</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46084.6875</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>5.33</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,73 +5538,73 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF43" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>46084.6875</v>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5785,40 +5785,40 @@
         <v>2.86</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA45" t="n">
         <v>1.68</v>
@@ -5827,22 +5827,22 @@
         <v>2.05</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46084.6875</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5891,77 +5891,77 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.53</v>
+        <v>2.45</v>
       </c>
       <c r="M46" t="n">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="N46" t="n">
-        <v>5.53</v>
+        <v>2.7</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="AB46" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF46" t="n">
         <v>2.1</v>
       </c>
-      <c r="AC46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF46" t="n">
-        <v>0</v>
-      </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH46" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AI46" s="3" t="n">
         <v>46084.69791666666</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,73 +6014,73 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="M47" t="n">
-        <v>3.38</v>
+        <v>3.26</v>
       </c>
       <c r="N47" t="n">
-        <v>3.08</v>
+        <v>4</v>
       </c>
       <c r="O47" t="n">
-        <v>2.8</v>
+        <v>2.46</v>
       </c>
       <c r="P47" t="n">
-        <v>2.19</v>
+        <v>2.09</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.5</v>
+        <v>4.25</v>
       </c>
       <c r="R47" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S47" t="n">
-        <v>2.81</v>
+        <v>2.87</v>
       </c>
       <c r="T47" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="U47" t="n">
         <v>1.36</v>
       </c>
       <c r="V47" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="W47" t="n">
         <v>1.03</v>
       </c>
       <c r="X47" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="Z47" t="n">
-        <v>3.24</v>
+        <v>3.05</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AC47" t="n">
-        <v>3.3</v>
+        <v>3.52</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AG47" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.55</v>
+        <v>1.88</v>
       </c>
       <c r="AI47" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6136,70 +6136,70 @@
         <v>2.45</v>
       </c>
       <c r="M48" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="N48" t="n">
-        <v>2.72</v>
+        <v>2.88</v>
       </c>
       <c r="O48" t="n">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="P48" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.5</v>
+        <v>3.67</v>
       </c>
       <c r="R48" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S48" t="n">
-        <v>2.69</v>
+        <v>2.77</v>
       </c>
       <c r="T48" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="U48" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="V48" t="n">
-        <v>6.95</v>
+        <v>6.75</v>
       </c>
       <c r="W48" t="n">
         <v>1.04</v>
       </c>
       <c r="X48" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y48" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG48" t="n">
         <v>1.31</v>
       </c>
-      <c r="Z48" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE48" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF48" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG48" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH48" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AI48" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6486,77 +6486,77 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="M51" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="N51" t="n">
-        <v>2.88</v>
+        <v>3.5</v>
       </c>
       <c r="O51" t="n">
-        <v>2.96</v>
+        <v>2.62</v>
       </c>
       <c r="P51" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q51" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="R51" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S51" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V51" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W51" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X51" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC51" t="n">
         <v>3.67</v>
       </c>
-      <c r="R51" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S51" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T51" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U51" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V51" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="W51" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X51" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>3.35</v>
-      </c>
       <c r="AD51" t="n">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="AF51" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AG51" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AH51" t="n">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="AI51" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.6</v>
+        <v>1.53</v>
       </c>
       <c r="M52" t="n">
-        <v>3.54</v>
+        <v>4.3</v>
       </c>
       <c r="N52" t="n">
-        <v>2.47</v>
+        <v>5.53</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6724,77 +6724,77 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L53" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="M53" t="n">
         <v>3.2</v>
       </c>
-      <c r="M53" t="n">
-        <v>3.24</v>
-      </c>
       <c r="N53" t="n">
-        <v>2.21</v>
+        <v>2.72</v>
       </c>
       <c r="O53" t="n">
-        <v>3.92</v>
+        <v>3.1</v>
       </c>
       <c r="P53" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q53" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="R53" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S53" t="n">
-        <v>2.77</v>
+        <v>2.69</v>
       </c>
       <c r="T53" t="n">
-        <v>2.73</v>
+        <v>2.65</v>
       </c>
       <c r="U53" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="V53" t="n">
-        <v>6.5</v>
+        <v>6.95</v>
       </c>
       <c r="W53" t="n">
         <v>1.04</v>
       </c>
       <c r="X53" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="Z53" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC53" t="n">
         <v>3.2</v>
       </c>
-      <c r="AA53" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>3.3</v>
-      </c>
       <c r="AD53" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG53" t="n">
         <v>1.33</v>
       </c>
-      <c r="AE53" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AF53" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AG53" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH53" t="n">
-        <v>1.31</v>
+        <v>1.53</v>
       </c>
       <c r="AI53" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,73 +6847,73 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.53</v>
+        <v>2.6</v>
       </c>
       <c r="M54" t="n">
-        <v>3.95</v>
+        <v>3.54</v>
       </c>
       <c r="N54" t="n">
-        <v>5</v>
+        <v>2.47</v>
       </c>
       <c r="O54" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="U54" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="V54" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W54" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X54" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Z54" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD54" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG54" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AH54" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AI54" s="3" t="n">
         <v>46084.69791666666</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,73 +6966,73 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="M55" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="N55" t="n">
-        <v>3.5</v>
+        <v>2.21</v>
       </c>
       <c r="O55" t="n">
-        <v>2.62</v>
+        <v>3.92</v>
       </c>
       <c r="P55" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q55" t="n">
-        <v>4.26</v>
+        <v>2.8</v>
       </c>
       <c r="R55" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="S55" t="n">
-        <v>2.87</v>
+        <v>2.77</v>
       </c>
       <c r="T55" t="n">
-        <v>2.91</v>
+        <v>2.73</v>
       </c>
       <c r="U55" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="V55" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W55" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X55" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD55" t="n">
         <v>1.33</v>
       </c>
-      <c r="V55" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W55" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X55" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AA55" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AE55" t="n">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="AG55" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.62</v>
+        <v>1.31</v>
       </c>
       <c r="AI55" s="3" t="n">
         <v>46084.69791666666</v>
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,73 +7085,73 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.85</v>
+        <v>2.1</v>
       </c>
       <c r="M56" t="n">
-        <v>3.1</v>
+        <v>3.38</v>
       </c>
       <c r="N56" t="n">
-        <v>2.24</v>
+        <v>3.08</v>
       </c>
       <c r="O56" t="n">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="P56" t="n">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="R56" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="S56" t="n">
-        <v>2.77</v>
+        <v>2.81</v>
       </c>
       <c r="T56" t="n">
-        <v>3.04</v>
+        <v>2.75</v>
       </c>
       <c r="U56" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V56" t="n">
-        <v>7.6</v>
+        <v>6.5</v>
       </c>
       <c r="W56" t="n">
         <v>1.03</v>
       </c>
       <c r="X56" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y56" t="n">
         <v>1.3</v>
       </c>
       <c r="Z56" t="n">
-        <v>3.14</v>
+        <v>3.24</v>
       </c>
       <c r="AA56" t="n">
-        <v>2.19</v>
+        <v>2.03</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AC56" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="AD56" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AE56" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AF56" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AG56" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AH56" t="n">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="AI56" s="3" t="n">
         <v>46084.69791666666</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7200,77 +7200,77 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.45</v>
+        <v>1.53</v>
       </c>
       <c r="M57" t="n">
-        <v>3</v>
+        <v>3.95</v>
       </c>
       <c r="N57" t="n">
-        <v>2.7</v>
+        <v>5</v>
       </c>
       <c r="O57" t="n">
-        <v>2.95</v>
+        <v>2.06</v>
       </c>
       <c r="P57" t="n">
-        <v>2.05</v>
+        <v>2.35</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.42</v>
+        <v>5.65</v>
       </c>
       <c r="R57" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="S57" t="n">
-        <v>2.62</v>
+        <v>2.91</v>
       </c>
       <c r="T57" t="n">
-        <v>2.96</v>
+        <v>2.48</v>
       </c>
       <c r="U57" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="V57" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="W57" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X57" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z57" t="n">
         <v>3.5</v>
       </c>
       <c r="AA57" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.71</v>
+        <v>1.93</v>
       </c>
       <c r="AC57" t="n">
-        <v>3.48</v>
+        <v>3</v>
       </c>
       <c r="AD57" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.67</v>
+        <v>1.84</v>
       </c>
       <c r="AF57" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AG57" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AH57" t="n">
-        <v>1.48</v>
+        <v>2.31</v>
       </c>
       <c r="AI57" s="3" t="n">
         <v>46084.69791666666</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,73 +7323,73 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.8</v>
+        <v>2.85</v>
       </c>
       <c r="M58" t="n">
-        <v>3.26</v>
+        <v>3.1</v>
       </c>
       <c r="N58" t="n">
-        <v>4</v>
+        <v>2.24</v>
       </c>
       <c r="O58" t="n">
-        <v>2.46</v>
+        <v>3.7</v>
       </c>
       <c r="P58" t="n">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="Q58" t="n">
-        <v>4.25</v>
+        <v>3.1</v>
       </c>
       <c r="R58" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="S58" t="n">
-        <v>2.87</v>
+        <v>2.77</v>
       </c>
       <c r="T58" t="n">
-        <v>2.9</v>
+        <v>3.04</v>
       </c>
       <c r="U58" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V58" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="W58" t="n">
         <v>1.03</v>
       </c>
       <c r="X58" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="Z58" t="n">
-        <v>3.05</v>
+        <v>3.14</v>
       </c>
       <c r="AA58" t="n">
-        <v>2</v>
+        <v>2.19</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AC58" t="n">
-        <v>3.52</v>
+        <v>3.55</v>
       </c>
       <c r="AD58" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AE58" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AF58" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AG58" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AH58" t="n">
-        <v>1.88</v>
+        <v>1.38</v>
       </c>
       <c r="AI58" s="3" t="n">
         <v>46084.69791666666</v>
@@ -7451,40 +7451,40 @@
         <v>1.55</v>
       </c>
       <c r="O59" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S59" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="T59" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U59" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V59" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="W59" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X59" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y59" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z59" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA59" t="n">
         <v>1.55</v>
@@ -7493,22 +7493,22 @@
         <v>2.3</v>
       </c>
       <c r="AC59" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD59" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE59" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF59" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AG59" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH59" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AI59" s="3" t="n">
         <v>46084.71875</v>

--- a/jogos_2026-03-03.xlsx
+++ b/jogos_2026-03-03.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.5</v>
+        <v>1.81</v>
       </c>
       <c r="M9" t="n">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="N9" t="n">
-        <v>2.8</v>
+        <v>4.55</v>
       </c>
       <c r="O9" t="n">
-        <v>3.22</v>
+        <v>2.62</v>
       </c>
       <c r="P9" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.74</v>
+        <v>5.78</v>
       </c>
       <c r="R9" t="n">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="S9" t="n">
-        <v>2.47</v>
+        <v>2.25</v>
       </c>
       <c r="T9" t="n">
-        <v>2.88</v>
+        <v>3.78</v>
       </c>
       <c r="U9" t="n">
-        <v>1.35</v>
+        <v>1.19</v>
       </c>
       <c r="V9" t="n">
-        <v>8.699999999999999</v>
+        <v>11</v>
       </c>
       <c r="W9" t="n">
         <v>1.01</v>
       </c>
       <c r="X9" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.33</v>
+        <v>1.59</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.25</v>
+        <v>2.62</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>4</v>
+        <v>5.3</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.87</v>
+        <v>2.31</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.8</v>
+        <v>1.52</v>
       </c>
       <c r="AG9" t="n">
         <v>1.3</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.48</v>
+        <v>1.77</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46084.45833333334</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.81</v>
+        <v>2.5</v>
       </c>
       <c r="M10" t="n">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="N10" t="n">
-        <v>4.55</v>
+        <v>2.8</v>
       </c>
       <c r="O10" t="n">
-        <v>2.62</v>
+        <v>3.22</v>
       </c>
       <c r="P10" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.78</v>
+        <v>3.74</v>
       </c>
       <c r="R10" t="n">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="S10" t="n">
-        <v>2.25</v>
+        <v>2.47</v>
       </c>
       <c r="T10" t="n">
-        <v>3.78</v>
+        <v>2.88</v>
       </c>
       <c r="U10" t="n">
-        <v>1.19</v>
+        <v>1.35</v>
       </c>
       <c r="V10" t="n">
-        <v>11</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W10" t="n">
         <v>1.01</v>
       </c>
       <c r="X10" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.59</v>
+        <v>1.33</v>
       </c>
       <c r="Z10" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA10" t="n">
         <v>2.25</v>
       </c>
-      <c r="AA10" t="n">
-        <v>2.62</v>
-      </c>
       <c r="AB10" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AC10" t="n">
-        <v>5.3</v>
+        <v>4</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.09</v>
+        <v>1.2</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.31</v>
+        <v>1.87</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.52</v>
+        <v>1.8</v>
       </c>
       <c r="AG10" t="n">
         <v>1.3</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.77</v>
+        <v>1.48</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46084.45833333334</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,22 +2920,22 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.75</v>
+        <v>1.86</v>
       </c>
       <c r="M21" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="N21" t="n">
-        <v>2.24</v>
+        <v>3.7</v>
       </c>
       <c r="O21" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="P21" t="n">
         <v>2.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.7</v>
+        <v>3.8</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -2944,10 +2944,10 @@
         <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.08</v>
+        <v>2.17</v>
       </c>
       <c r="U21" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2959,34 +2959,34 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.28</v>
+        <v>2.17</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.48</v>
+        <v>2.25</v>
       </c>
       <c r="AG21" t="n">
         <v>1.2</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.33</v>
+        <v>1.74</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46084.625</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,22 +3039,22 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>4.5</v>
+        <v>1.81</v>
       </c>
       <c r="M22" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="N22" t="n">
-        <v>1.62</v>
+        <v>3.95</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -3063,10 +3063,10 @@
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -3078,34 +3078,34 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.3</v>
+        <v>1.64</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.53</v>
+        <v>2</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46084.625</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,22 +3158,22 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.86</v>
+        <v>2.75</v>
       </c>
       <c r="M23" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="N23" t="n">
-        <v>3.7</v>
+        <v>2.24</v>
       </c>
       <c r="O23" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="P23" t="n">
         <v>2.4</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.8</v>
+        <v>2.7</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -3182,10 +3182,10 @@
         <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="U23" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -3197,34 +3197,34 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.17</v>
+        <v>2.28</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.25</v>
+        <v>2.48</v>
       </c>
       <c r="AG23" t="n">
         <v>1.2</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.74</v>
+        <v>1.33</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46084.625</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,22 +3396,22 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.81</v>
+        <v>4.5</v>
       </c>
       <c r="M25" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="N25" t="n">
-        <v>3.95</v>
+        <v>1.62</v>
       </c>
       <c r="O25" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -3420,10 +3420,10 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -3435,34 +3435,34 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.64</v>
+        <v>2.3</v>
       </c>
       <c r="AB25" t="n">
-        <v>2</v>
+        <v>1.53</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46084.625</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G30